--- a/public/chat_files/liza_rate_card_final.xlsx
+++ b/public/chat_files/liza_rate_card_final.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="2026_Rate_Card" sheetId="1" r:id="rId1"/>
+    <sheet name="Commercial_Rate_Card" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -13,12 +13,12 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Service Tier</t>
+          <t>Service Classification</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Turnaround</t>
+          <t>Response SLA</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
@@ -28,19 +28,19 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Additional Unit</t>
+          <t>Per Sq Ft / Unit</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Weekend Surcharge</t>
+          <t>Weekend / After-Hours</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Standard Commercial Crew</t>
+          <t>Standard Commercial Maintenance</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -52,7 +52,7 @@
         <v>450.0</v>
       </c>
       <c r="D2">
-        <v>85.0</v>
+        <v>0.12</v>
       </c>
       <c r="E2">
         <v>125.0</v>
@@ -61,43 +61,87 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Priority Same-Day Crew</t>
+          <t>High-Frequency Medical Disinfection</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Same Day</t>
+          <t>24 Hours</t>
         </is>
       </c>
       <c r="C3">
         <v>650.0</v>
       </c>
       <c r="D3">
-        <v>110.0</v>
+        <v>0.18</v>
       </c>
       <c r="E3">
-        <v>150.0</v>
+        <v>175.0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Monthly Retainer Visit (4x)</t>
+          <t>Emergency Mechanical / HVAC Response</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>Same Day (2h)</t>
+        </is>
+      </c>
+      <c r="C4">
+        <v>850.0</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Custom T&amp;M</t>
+        </is>
+      </c>
+      <c r="E4">
+        <v>250.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Monthly Retainer Contract (4 Visits)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>Scheduled</t>
         </is>
       </c>
-      <c r="C4">
-        <v>1450.0</v>
+      <c r="C5">
+        <v>1600.0</v>
       </c>
-      <c r="D4">
+      <c r="D5">
+        <v>0.09</v>
+      </c>
+      <c r="E5">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Quarterly Deep Scrub &amp; Floor Polish</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="C6">
+        <v>1250.0</v>
+      </c>
+      <c r="D6">
+        <v>0.15</v>
+      </c>
+      <c r="E6">
         <v>75.0</v>
-      </c>
-      <c r="E4">
-        <v>0.0</v>
       </c>
     </row>
   </sheetData>

--- a/public/chat_files/liza_rate_card_final.xlsx
+++ b/public/chat_files/liza_rate_card_final.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial Rate Card" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audit Trail &amp; Documentation" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -114,7 +115,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -160,6 +161,9 @@
     </xf>
     <xf numFmtId="165" fontId="3" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -527,7 +531,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
@@ -723,4 +727,4648 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H110"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="33" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Record ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Audit Entity</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Transaction Hash</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Verification Parameter</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Observed SLA Value</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Audit Clearance Status</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Sign-Off Authority</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Technical Documentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0001</t>
+        </is>
+      </c>
+      <c r="B2" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 1</t>
+        </is>
+      </c>
+      <c r="C2" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:91f21eb7a7eabff77c107c1b</t>
+        </is>
+      </c>
+      <c r="D2" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 1: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E2" s="16" t="inlineStr">
+        <is>
+          <t>98.70%</t>
+        </is>
+      </c>
+      <c r="F2" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G2" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H2" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8001. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0002</t>
+        </is>
+      </c>
+      <c r="B3" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 2</t>
+        </is>
+      </c>
+      <c r="C3" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:6669b69193406fb4a4d01f64</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 2: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E3" s="16" t="inlineStr">
+        <is>
+          <t>98.90%</t>
+        </is>
+      </c>
+      <c r="F3" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G3" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H3" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8002. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0003</t>
+        </is>
+      </c>
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 3</t>
+        </is>
+      </c>
+      <c r="C4" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:04fff8fe6e34ee7b7f45ce21</t>
+        </is>
+      </c>
+      <c r="D4" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 3: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E4" s="16" t="inlineStr">
+        <is>
+          <t>99.10%</t>
+        </is>
+      </c>
+      <c r="F4" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G4" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H4" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8003. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0004</t>
+        </is>
+      </c>
+      <c r="B5" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 4</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:a14d95d2c74cdc81d1c0574a</t>
+        </is>
+      </c>
+      <c r="D5" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 4: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E5" s="16" t="inlineStr">
+        <is>
+          <t>99.30%</t>
+        </is>
+      </c>
+      <c r="F5" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G5" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H5" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8004. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0005</t>
+        </is>
+      </c>
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 5</t>
+        </is>
+      </c>
+      <c r="C6" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:ef387ccaef65691f2a7059da</t>
+        </is>
+      </c>
+      <c r="D6" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 5: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E6" s="16" t="inlineStr">
+        <is>
+          <t>99.50%</t>
+        </is>
+      </c>
+      <c r="F6" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G6" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H6" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8005. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0006</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 6</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:b130274fec46d89c08fb5616</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 6: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E7" s="16" t="inlineStr">
+        <is>
+          <t>99.70%</t>
+        </is>
+      </c>
+      <c r="F7" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G7" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H7" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8006. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0007</t>
+        </is>
+      </c>
+      <c r="B8" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 7</t>
+        </is>
+      </c>
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:2414972e83598a42d794a1a6</t>
+        </is>
+      </c>
+      <c r="D8" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 7: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E8" s="16" t="inlineStr">
+        <is>
+          <t>98.50%</t>
+        </is>
+      </c>
+      <c r="F8" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G8" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H8" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8007. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0008</t>
+        </is>
+      </c>
+      <c r="B9" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 8</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:7d7e5e22cc795259e1f06929</t>
+        </is>
+      </c>
+      <c r="D9" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 8: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E9" s="16" t="inlineStr">
+        <is>
+          <t>98.70%</t>
+        </is>
+      </c>
+      <c r="F9" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G9" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H9" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8008. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0009</t>
+        </is>
+      </c>
+      <c r="B10" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 9</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:4f80b27032caf528bb68fc24</t>
+        </is>
+      </c>
+      <c r="D10" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 9: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E10" s="16" t="inlineStr">
+        <is>
+          <t>98.90%</t>
+        </is>
+      </c>
+      <c r="F10" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G10" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H10" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8009. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0010</t>
+        </is>
+      </c>
+      <c r="B11" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 10</t>
+        </is>
+      </c>
+      <c r="C11" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:cd4376a5c07220f629e4e368</t>
+        </is>
+      </c>
+      <c r="D11" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 10: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E11" s="16" t="inlineStr">
+        <is>
+          <t>99.10%</t>
+        </is>
+      </c>
+      <c r="F11" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G11" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H11" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8010. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0011</t>
+        </is>
+      </c>
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 11</t>
+        </is>
+      </c>
+      <c r="C12" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:b989c1721eee348d4ce8f891</t>
+        </is>
+      </c>
+      <c r="D12" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 11: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E12" s="16" t="inlineStr">
+        <is>
+          <t>99.30%</t>
+        </is>
+      </c>
+      <c r="F12" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G12" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H12" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8011. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0012</t>
+        </is>
+      </c>
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 12</t>
+        </is>
+      </c>
+      <c r="C13" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:ba4670d8012e6a0d093ac3af</t>
+        </is>
+      </c>
+      <c r="D13" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 12: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E13" s="16" t="inlineStr">
+        <is>
+          <t>99.50%</t>
+        </is>
+      </c>
+      <c r="F13" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G13" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H13" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8012. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0013</t>
+        </is>
+      </c>
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 13</t>
+        </is>
+      </c>
+      <c r="C14" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:cee1c59ac50b7b080a44eedd</t>
+        </is>
+      </c>
+      <c r="D14" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 13: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E14" s="16" t="inlineStr">
+        <is>
+          <t>99.70%</t>
+        </is>
+      </c>
+      <c r="F14" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G14" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H14" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8013. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0014</t>
+        </is>
+      </c>
+      <c r="B15" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 14</t>
+        </is>
+      </c>
+      <c r="C15" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:9cbbd0a1cc2289c0ffd8ddbc</t>
+        </is>
+      </c>
+      <c r="D15" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 14: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E15" s="16" t="inlineStr">
+        <is>
+          <t>98.50%</t>
+        </is>
+      </c>
+      <c r="F15" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G15" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H15" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8014. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0015</t>
+        </is>
+      </c>
+      <c r="B16" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 15</t>
+        </is>
+      </c>
+      <c r="C16" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:559452c30f1245a6e4ad1d06</t>
+        </is>
+      </c>
+      <c r="D16" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 15: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E16" s="16" t="inlineStr">
+        <is>
+          <t>98.70%</t>
+        </is>
+      </c>
+      <c r="F16" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G16" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H16" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8015. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0016</t>
+        </is>
+      </c>
+      <c r="B17" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 16</t>
+        </is>
+      </c>
+      <c r="C17" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:0c176462c93d4c1ca21d3c87</t>
+        </is>
+      </c>
+      <c r="D17" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 16: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E17" s="16" t="inlineStr">
+        <is>
+          <t>98.90%</t>
+        </is>
+      </c>
+      <c r="F17" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G17" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H17" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8016. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0017</t>
+        </is>
+      </c>
+      <c r="B18" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 17</t>
+        </is>
+      </c>
+      <c r="C18" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:86df8dc117e68e3dd294667c</t>
+        </is>
+      </c>
+      <c r="D18" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 17: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E18" s="16" t="inlineStr">
+        <is>
+          <t>99.10%</t>
+        </is>
+      </c>
+      <c r="F18" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G18" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H18" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8017. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0018</t>
+        </is>
+      </c>
+      <c r="B19" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 18</t>
+        </is>
+      </c>
+      <c r="C19" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:e28a9b57b87bed53d4d7b575</t>
+        </is>
+      </c>
+      <c r="D19" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 18: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E19" s="16" t="inlineStr">
+        <is>
+          <t>99.30%</t>
+        </is>
+      </c>
+      <c r="F19" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G19" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H19" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8018. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0019</t>
+        </is>
+      </c>
+      <c r="B20" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 19</t>
+        </is>
+      </c>
+      <c r="C20" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:0345d017c720a78e792e015f</t>
+        </is>
+      </c>
+      <c r="D20" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 19: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E20" s="16" t="inlineStr">
+        <is>
+          <t>99.50%</t>
+        </is>
+      </c>
+      <c r="F20" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G20" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H20" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8019. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0020</t>
+        </is>
+      </c>
+      <c r="B21" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 20</t>
+        </is>
+      </c>
+      <c r="C21" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:b66becd597d619c02ba13019</t>
+        </is>
+      </c>
+      <c r="D21" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 20: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E21" s="16" t="inlineStr">
+        <is>
+          <t>99.70%</t>
+        </is>
+      </c>
+      <c r="F21" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G21" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H21" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8020. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0021</t>
+        </is>
+      </c>
+      <c r="B22" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 21</t>
+        </is>
+      </c>
+      <c r="C22" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:0600193d7b9f1cb24de268a1</t>
+        </is>
+      </c>
+      <c r="D22" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 21: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E22" s="16" t="inlineStr">
+        <is>
+          <t>98.50%</t>
+        </is>
+      </c>
+      <c r="F22" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G22" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H22" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8021. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0022</t>
+        </is>
+      </c>
+      <c r="B23" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 22</t>
+        </is>
+      </c>
+      <c r="C23" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:9822074545e92d9b9501a385</t>
+        </is>
+      </c>
+      <c r="D23" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 22: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E23" s="16" t="inlineStr">
+        <is>
+          <t>98.70%</t>
+        </is>
+      </c>
+      <c r="F23" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G23" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H23" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8022. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0023</t>
+        </is>
+      </c>
+      <c r="B24" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 23</t>
+        </is>
+      </c>
+      <c r="C24" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:57b1fa05df003497a4fc7f0f</t>
+        </is>
+      </c>
+      <c r="D24" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 23: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E24" s="16" t="inlineStr">
+        <is>
+          <t>98.90%</t>
+        </is>
+      </c>
+      <c r="F24" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G24" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H24" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8023. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0024</t>
+        </is>
+      </c>
+      <c r="B25" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 24</t>
+        </is>
+      </c>
+      <c r="C25" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:6d50faf77514b3154c015a14</t>
+        </is>
+      </c>
+      <c r="D25" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 24: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E25" s="16" t="inlineStr">
+        <is>
+          <t>99.10%</t>
+        </is>
+      </c>
+      <c r="F25" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G25" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H25" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8024. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0025</t>
+        </is>
+      </c>
+      <c r="B26" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 25</t>
+        </is>
+      </c>
+      <c r="C26" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:019bb6bf1cab89b3d04dd140</t>
+        </is>
+      </c>
+      <c r="D26" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 25: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E26" s="16" t="inlineStr">
+        <is>
+          <t>99.30%</t>
+        </is>
+      </c>
+      <c r="F26" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G26" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H26" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8025. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0026</t>
+        </is>
+      </c>
+      <c r="B27" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 26</t>
+        </is>
+      </c>
+      <c r="C27" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:6e2f398021d714af26c0be4b</t>
+        </is>
+      </c>
+      <c r="D27" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 26: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E27" s="16" t="inlineStr">
+        <is>
+          <t>99.50%</t>
+        </is>
+      </c>
+      <c r="F27" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G27" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H27" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8026. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0027</t>
+        </is>
+      </c>
+      <c r="B28" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 27</t>
+        </is>
+      </c>
+      <c r="C28" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:34c8e07db3de7186b003f55e</t>
+        </is>
+      </c>
+      <c r="D28" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 27: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E28" s="16" t="inlineStr">
+        <is>
+          <t>99.70%</t>
+        </is>
+      </c>
+      <c r="F28" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G28" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H28" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8027. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0028</t>
+        </is>
+      </c>
+      <c r="B29" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 28</t>
+        </is>
+      </c>
+      <c r="C29" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:2c9ec324b241510d21447632</t>
+        </is>
+      </c>
+      <c r="D29" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 28: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E29" s="16" t="inlineStr">
+        <is>
+          <t>98.50%</t>
+        </is>
+      </c>
+      <c r="F29" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G29" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H29" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8028. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0029</t>
+        </is>
+      </c>
+      <c r="B30" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 29</t>
+        </is>
+      </c>
+      <c r="C30" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:1425fc8683e42c3651ca9d82</t>
+        </is>
+      </c>
+      <c r="D30" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 29: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E30" s="16" t="inlineStr">
+        <is>
+          <t>98.70%</t>
+        </is>
+      </c>
+      <c r="F30" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G30" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H30" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8029. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0030</t>
+        </is>
+      </c>
+      <c r="B31" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 30</t>
+        </is>
+      </c>
+      <c r="C31" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:f0a4f3b7ce428944841424f3</t>
+        </is>
+      </c>
+      <c r="D31" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 30: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E31" s="16" t="inlineStr">
+        <is>
+          <t>98.90%</t>
+        </is>
+      </c>
+      <c r="F31" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G31" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H31" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8030. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0031</t>
+        </is>
+      </c>
+      <c r="B32" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 31</t>
+        </is>
+      </c>
+      <c r="C32" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:3e7338fe2e1bc9cf15749c00</t>
+        </is>
+      </c>
+      <c r="D32" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 31: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E32" s="16" t="inlineStr">
+        <is>
+          <t>99.10%</t>
+        </is>
+      </c>
+      <c r="F32" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G32" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H32" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8031. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0032</t>
+        </is>
+      </c>
+      <c r="B33" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 32</t>
+        </is>
+      </c>
+      <c r="C33" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:808d551f9b2b1f3ce7658fbb</t>
+        </is>
+      </c>
+      <c r="D33" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 32: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E33" s="16" t="inlineStr">
+        <is>
+          <t>99.30%</t>
+        </is>
+      </c>
+      <c r="F33" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G33" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H33" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8032. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0033</t>
+        </is>
+      </c>
+      <c r="B34" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 33</t>
+        </is>
+      </c>
+      <c r="C34" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:f8442012ead3c2db9badb88c</t>
+        </is>
+      </c>
+      <c r="D34" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 33: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E34" s="16" t="inlineStr">
+        <is>
+          <t>99.50%</t>
+        </is>
+      </c>
+      <c r="F34" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G34" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H34" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8033. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0034</t>
+        </is>
+      </c>
+      <c r="B35" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 34</t>
+        </is>
+      </c>
+      <c r="C35" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:57588293ae5c5a0288637f42</t>
+        </is>
+      </c>
+      <c r="D35" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 34: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E35" s="16" t="inlineStr">
+        <is>
+          <t>99.70%</t>
+        </is>
+      </c>
+      <c r="F35" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G35" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H35" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8034. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0035</t>
+        </is>
+      </c>
+      <c r="B36" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 35</t>
+        </is>
+      </c>
+      <c r="C36" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:5e984eec0c0cd5d182d59172</t>
+        </is>
+      </c>
+      <c r="D36" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 35: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E36" s="16" t="inlineStr">
+        <is>
+          <t>98.50%</t>
+        </is>
+      </c>
+      <c r="F36" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G36" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H36" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8035. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0036</t>
+        </is>
+      </c>
+      <c r="B37" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 36</t>
+        </is>
+      </c>
+      <c r="C37" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:20e34fff6665df9634ed9d87</t>
+        </is>
+      </c>
+      <c r="D37" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 36: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E37" s="16" t="inlineStr">
+        <is>
+          <t>98.70%</t>
+        </is>
+      </c>
+      <c r="F37" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G37" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H37" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8036. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0037</t>
+        </is>
+      </c>
+      <c r="B38" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 37</t>
+        </is>
+      </c>
+      <c r="C38" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:e03bdd1a3ca7a6226d09a4eb</t>
+        </is>
+      </c>
+      <c r="D38" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 37: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E38" s="16" t="inlineStr">
+        <is>
+          <t>98.90%</t>
+        </is>
+      </c>
+      <c r="F38" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G38" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H38" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8037. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0038</t>
+        </is>
+      </c>
+      <c r="B39" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 38</t>
+        </is>
+      </c>
+      <c r="C39" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:545c1391a99de8004e539544</t>
+        </is>
+      </c>
+      <c r="D39" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 38: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E39" s="16" t="inlineStr">
+        <is>
+          <t>99.10%</t>
+        </is>
+      </c>
+      <c r="F39" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G39" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H39" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8038. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0039</t>
+        </is>
+      </c>
+      <c r="B40" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 39</t>
+        </is>
+      </c>
+      <c r="C40" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:14996a49cfa4780793e44161</t>
+        </is>
+      </c>
+      <c r="D40" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 39: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E40" s="16" t="inlineStr">
+        <is>
+          <t>99.30%</t>
+        </is>
+      </c>
+      <c r="F40" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G40" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H40" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8039. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0040</t>
+        </is>
+      </c>
+      <c r="B41" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 40</t>
+        </is>
+      </c>
+      <c r="C41" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:cceeafe71fe021e93f8754df</t>
+        </is>
+      </c>
+      <c r="D41" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 40: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E41" s="16" t="inlineStr">
+        <is>
+          <t>99.50%</t>
+        </is>
+      </c>
+      <c r="F41" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G41" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H41" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8040. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0041</t>
+        </is>
+      </c>
+      <c r="B42" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 41</t>
+        </is>
+      </c>
+      <c r="C42" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:b30390d3a7b57b45944bf3d2</t>
+        </is>
+      </c>
+      <c r="D42" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 41: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E42" s="16" t="inlineStr">
+        <is>
+          <t>99.70%</t>
+        </is>
+      </c>
+      <c r="F42" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G42" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H42" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8041. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0042</t>
+        </is>
+      </c>
+      <c r="B43" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 42</t>
+        </is>
+      </c>
+      <c r="C43" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:42c0373f453ff6008ab4c9c7</t>
+        </is>
+      </c>
+      <c r="D43" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 42: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E43" s="16" t="inlineStr">
+        <is>
+          <t>98.50%</t>
+        </is>
+      </c>
+      <c r="F43" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G43" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H43" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8042. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0043</t>
+        </is>
+      </c>
+      <c r="B44" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 43</t>
+        </is>
+      </c>
+      <c r="C44" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:9ba27b44185ccf8c7bc2e62e</t>
+        </is>
+      </c>
+      <c r="D44" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 43: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E44" s="16" t="inlineStr">
+        <is>
+          <t>98.70%</t>
+        </is>
+      </c>
+      <c r="F44" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G44" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H44" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8043. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0044</t>
+        </is>
+      </c>
+      <c r="B45" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 44</t>
+        </is>
+      </c>
+      <c r="C45" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:fa4a0c64d6d684e7ec71f2ce</t>
+        </is>
+      </c>
+      <c r="D45" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 44: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E45" s="16" t="inlineStr">
+        <is>
+          <t>98.90%</t>
+        </is>
+      </c>
+      <c r="F45" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G45" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H45" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8044. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0045</t>
+        </is>
+      </c>
+      <c r="B46" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 45</t>
+        </is>
+      </c>
+      <c r="C46" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:34de87ac4cf7cc1c45790b56</t>
+        </is>
+      </c>
+      <c r="D46" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 45: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E46" s="16" t="inlineStr">
+        <is>
+          <t>99.10%</t>
+        </is>
+      </c>
+      <c r="F46" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G46" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H46" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8045. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0046</t>
+        </is>
+      </c>
+      <c r="B47" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 46</t>
+        </is>
+      </c>
+      <c r="C47" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:2c6de11cb2b1f85600e775ef</t>
+        </is>
+      </c>
+      <c r="D47" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 46: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E47" s="16" t="inlineStr">
+        <is>
+          <t>99.30%</t>
+        </is>
+      </c>
+      <c r="F47" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G47" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H47" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8046. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0047</t>
+        </is>
+      </c>
+      <c r="B48" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 47</t>
+        </is>
+      </c>
+      <c r="C48" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:afb87f845fb8106b27f40d85</t>
+        </is>
+      </c>
+      <c r="D48" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 47: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E48" s="16" t="inlineStr">
+        <is>
+          <t>99.50%</t>
+        </is>
+      </c>
+      <c r="F48" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G48" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H48" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8047. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0048</t>
+        </is>
+      </c>
+      <c r="B49" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 48</t>
+        </is>
+      </c>
+      <c r="C49" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:54bf4426d65718b05ec3e6f7</t>
+        </is>
+      </c>
+      <c r="D49" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 48: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E49" s="16" t="inlineStr">
+        <is>
+          <t>99.70%</t>
+        </is>
+      </c>
+      <c r="F49" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G49" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H49" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8048. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0049</t>
+        </is>
+      </c>
+      <c r="B50" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 49</t>
+        </is>
+      </c>
+      <c r="C50" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:1814a55984139e821d4da248</t>
+        </is>
+      </c>
+      <c r="D50" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 49: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E50" s="16" t="inlineStr">
+        <is>
+          <t>98.50%</t>
+        </is>
+      </c>
+      <c r="F50" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G50" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H50" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8049. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0050</t>
+        </is>
+      </c>
+      <c r="B51" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 50</t>
+        </is>
+      </c>
+      <c r="C51" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:6b7a97f9c155d9a1a7e276c4</t>
+        </is>
+      </c>
+      <c r="D51" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 50: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E51" s="16" t="inlineStr">
+        <is>
+          <t>98.70%</t>
+        </is>
+      </c>
+      <c r="F51" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G51" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H51" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8050. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0051</t>
+        </is>
+      </c>
+      <c r="B52" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 51</t>
+        </is>
+      </c>
+      <c r="C52" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:e4a62d26937d669483d2f5a2</t>
+        </is>
+      </c>
+      <c r="D52" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 51: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E52" s="16" t="inlineStr">
+        <is>
+          <t>98.90%</t>
+        </is>
+      </c>
+      <c r="F52" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G52" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H52" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8051. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0052</t>
+        </is>
+      </c>
+      <c r="B53" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 52</t>
+        </is>
+      </c>
+      <c r="C53" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:a6daaa48f57ef03333db8c0c</t>
+        </is>
+      </c>
+      <c r="D53" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 52: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E53" s="16" t="inlineStr">
+        <is>
+          <t>99.10%</t>
+        </is>
+      </c>
+      <c r="F53" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G53" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H53" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8052. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0053</t>
+        </is>
+      </c>
+      <c r="B54" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 53</t>
+        </is>
+      </c>
+      <c r="C54" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:b035264c0969ca52b7067452</t>
+        </is>
+      </c>
+      <c r="D54" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 53: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E54" s="16" t="inlineStr">
+        <is>
+          <t>99.30%</t>
+        </is>
+      </c>
+      <c r="F54" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G54" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H54" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8053. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0054</t>
+        </is>
+      </c>
+      <c r="B55" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 54</t>
+        </is>
+      </c>
+      <c r="C55" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:9e557de7a0e0aa3265a85b89</t>
+        </is>
+      </c>
+      <c r="D55" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 54: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E55" s="16" t="inlineStr">
+        <is>
+          <t>99.50%</t>
+        </is>
+      </c>
+      <c r="F55" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G55" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H55" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8054. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0055</t>
+        </is>
+      </c>
+      <c r="B56" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 55</t>
+        </is>
+      </c>
+      <c r="C56" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:ef506da4e2fc1fe5fa936b3e</t>
+        </is>
+      </c>
+      <c r="D56" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 55: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E56" s="16" t="inlineStr">
+        <is>
+          <t>99.70%</t>
+        </is>
+      </c>
+      <c r="F56" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G56" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H56" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8055. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0056</t>
+        </is>
+      </c>
+      <c r="B57" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 56</t>
+        </is>
+      </c>
+      <c r="C57" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:c94d64b69777959e17909713</t>
+        </is>
+      </c>
+      <c r="D57" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 56: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E57" s="16" t="inlineStr">
+        <is>
+          <t>98.50%</t>
+        </is>
+      </c>
+      <c r="F57" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G57" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H57" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8056. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0057</t>
+        </is>
+      </c>
+      <c r="B58" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 57</t>
+        </is>
+      </c>
+      <c r="C58" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:dc5150c0ff8ba0e186ebedfa</t>
+        </is>
+      </c>
+      <c r="D58" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 57: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E58" s="16" t="inlineStr">
+        <is>
+          <t>98.70%</t>
+        </is>
+      </c>
+      <c r="F58" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G58" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H58" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8057. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0058</t>
+        </is>
+      </c>
+      <c r="B59" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 58</t>
+        </is>
+      </c>
+      <c r="C59" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:3a96b6567e35f513b9eac0f0</t>
+        </is>
+      </c>
+      <c r="D59" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 58: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E59" s="16" t="inlineStr">
+        <is>
+          <t>98.90%</t>
+        </is>
+      </c>
+      <c r="F59" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G59" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H59" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8058. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0059</t>
+        </is>
+      </c>
+      <c r="B60" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 59</t>
+        </is>
+      </c>
+      <c r="C60" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:3ef1835e2980560cabe0c710</t>
+        </is>
+      </c>
+      <c r="D60" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 59: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E60" s="16" t="inlineStr">
+        <is>
+          <t>99.10%</t>
+        </is>
+      </c>
+      <c r="F60" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G60" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H60" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8059. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0060</t>
+        </is>
+      </c>
+      <c r="B61" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 60</t>
+        </is>
+      </c>
+      <c r="C61" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:e79f177608559c8a0b37e39e</t>
+        </is>
+      </c>
+      <c r="D61" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 60: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E61" s="16" t="inlineStr">
+        <is>
+          <t>99.30%</t>
+        </is>
+      </c>
+      <c r="F61" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G61" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H61" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8060. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0061</t>
+        </is>
+      </c>
+      <c r="B62" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 61</t>
+        </is>
+      </c>
+      <c r="C62" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:efd9ff5d58520e27e1b1a258</t>
+        </is>
+      </c>
+      <c r="D62" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 61: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E62" s="16" t="inlineStr">
+        <is>
+          <t>99.50%</t>
+        </is>
+      </c>
+      <c r="F62" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G62" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H62" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8061. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0062</t>
+        </is>
+      </c>
+      <c r="B63" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 62</t>
+        </is>
+      </c>
+      <c r="C63" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:e802d80dd861e9a22d88e262</t>
+        </is>
+      </c>
+      <c r="D63" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 62: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E63" s="16" t="inlineStr">
+        <is>
+          <t>99.70%</t>
+        </is>
+      </c>
+      <c r="F63" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G63" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H63" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8062. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0063</t>
+        </is>
+      </c>
+      <c r="B64" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 63</t>
+        </is>
+      </c>
+      <c r="C64" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:b63c95e1fee671e0352e3649</t>
+        </is>
+      </c>
+      <c r="D64" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 63: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E64" s="16" t="inlineStr">
+        <is>
+          <t>98.50%</t>
+        </is>
+      </c>
+      <c r="F64" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G64" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H64" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8063. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0064</t>
+        </is>
+      </c>
+      <c r="B65" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 64</t>
+        </is>
+      </c>
+      <c r="C65" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:ec7553fe18cdaca4ed190eec</t>
+        </is>
+      </c>
+      <c r="D65" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 64: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E65" s="16" t="inlineStr">
+        <is>
+          <t>98.70%</t>
+        </is>
+      </c>
+      <c r="F65" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G65" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H65" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8064. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0065</t>
+        </is>
+      </c>
+      <c r="B66" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 65</t>
+        </is>
+      </c>
+      <c r="C66" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:e030e51d6f457343bf17bd7d</t>
+        </is>
+      </c>
+      <c r="D66" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 65: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E66" s="16" t="inlineStr">
+        <is>
+          <t>98.90%</t>
+        </is>
+      </c>
+      <c r="F66" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G66" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H66" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8065. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0066</t>
+        </is>
+      </c>
+      <c r="B67" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 66</t>
+        </is>
+      </c>
+      <c r="C67" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:336b6beb3c4729df275a02ad</t>
+        </is>
+      </c>
+      <c r="D67" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 66: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E67" s="16" t="inlineStr">
+        <is>
+          <t>99.10%</t>
+        </is>
+      </c>
+      <c r="F67" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G67" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H67" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8066. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0067</t>
+        </is>
+      </c>
+      <c r="B68" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 67</t>
+        </is>
+      </c>
+      <c r="C68" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:68f27a72434009f9899eee16</t>
+        </is>
+      </c>
+      <c r="D68" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 67: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E68" s="16" t="inlineStr">
+        <is>
+          <t>99.30%</t>
+        </is>
+      </c>
+      <c r="F68" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G68" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H68" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8067. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0068</t>
+        </is>
+      </c>
+      <c r="B69" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 68</t>
+        </is>
+      </c>
+      <c r="C69" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:38b39acd3719847618b1b522</t>
+        </is>
+      </c>
+      <c r="D69" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 68: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E69" s="16" t="inlineStr">
+        <is>
+          <t>99.50%</t>
+        </is>
+      </c>
+      <c r="F69" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G69" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H69" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8068. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0069</t>
+        </is>
+      </c>
+      <c r="B70" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 69</t>
+        </is>
+      </c>
+      <c r="C70" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:d10ea4a37c15ac3981a6c2d2</t>
+        </is>
+      </c>
+      <c r="D70" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 69: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E70" s="16" t="inlineStr">
+        <is>
+          <t>99.70%</t>
+        </is>
+      </c>
+      <c r="F70" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G70" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H70" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8069. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0070</t>
+        </is>
+      </c>
+      <c r="B71" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 70</t>
+        </is>
+      </c>
+      <c r="C71" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:974fca76ad2497eb0ac737e7</t>
+        </is>
+      </c>
+      <c r="D71" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 70: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E71" s="16" t="inlineStr">
+        <is>
+          <t>98.50%</t>
+        </is>
+      </c>
+      <c r="F71" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G71" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H71" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8070. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0071</t>
+        </is>
+      </c>
+      <c r="B72" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 71</t>
+        </is>
+      </c>
+      <c r="C72" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:87c6348615379f068285f294</t>
+        </is>
+      </c>
+      <c r="D72" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 71: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E72" s="16" t="inlineStr">
+        <is>
+          <t>98.70%</t>
+        </is>
+      </c>
+      <c r="F72" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G72" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H72" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8071. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0072</t>
+        </is>
+      </c>
+      <c r="B73" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 72</t>
+        </is>
+      </c>
+      <c r="C73" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:2ad220854c544cf2e52aae6c</t>
+        </is>
+      </c>
+      <c r="D73" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 72: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E73" s="16" t="inlineStr">
+        <is>
+          <t>98.90%</t>
+        </is>
+      </c>
+      <c r="F73" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G73" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H73" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8072. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0073</t>
+        </is>
+      </c>
+      <c r="B74" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 73</t>
+        </is>
+      </c>
+      <c r="C74" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:1402cd477181ec62d83690c3</t>
+        </is>
+      </c>
+      <c r="D74" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 73: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E74" s="16" t="inlineStr">
+        <is>
+          <t>99.10%</t>
+        </is>
+      </c>
+      <c r="F74" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G74" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H74" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8073. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0074</t>
+        </is>
+      </c>
+      <c r="B75" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 74</t>
+        </is>
+      </c>
+      <c r="C75" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:ef98780ef029a2b6eca08d8a</t>
+        </is>
+      </c>
+      <c r="D75" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 74: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E75" s="16" t="inlineStr">
+        <is>
+          <t>99.30%</t>
+        </is>
+      </c>
+      <c r="F75" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G75" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H75" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8074. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0075</t>
+        </is>
+      </c>
+      <c r="B76" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 75</t>
+        </is>
+      </c>
+      <c r="C76" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:7b241d1ef7eacade2bfa74cd</t>
+        </is>
+      </c>
+      <c r="D76" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 75: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E76" s="16" t="inlineStr">
+        <is>
+          <t>99.50%</t>
+        </is>
+      </c>
+      <c r="F76" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G76" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H76" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8075. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0076</t>
+        </is>
+      </c>
+      <c r="B77" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 76</t>
+        </is>
+      </c>
+      <c r="C77" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:387c8fa1ed8b1d94be7d1c1f</t>
+        </is>
+      </c>
+      <c r="D77" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 76: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E77" s="16" t="inlineStr">
+        <is>
+          <t>99.70%</t>
+        </is>
+      </c>
+      <c r="F77" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G77" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H77" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8076. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0077</t>
+        </is>
+      </c>
+      <c r="B78" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 77</t>
+        </is>
+      </c>
+      <c r="C78" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:3bf65552d6e42ce8517042cb</t>
+        </is>
+      </c>
+      <c r="D78" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 77: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E78" s="16" t="inlineStr">
+        <is>
+          <t>98.50%</t>
+        </is>
+      </c>
+      <c r="F78" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G78" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H78" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8077. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0078</t>
+        </is>
+      </c>
+      <c r="B79" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 78</t>
+        </is>
+      </c>
+      <c r="C79" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:557aded252c2f1592151b24a</t>
+        </is>
+      </c>
+      <c r="D79" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 78: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E79" s="16" t="inlineStr">
+        <is>
+          <t>98.70%</t>
+        </is>
+      </c>
+      <c r="F79" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G79" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H79" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8078. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0079</t>
+        </is>
+      </c>
+      <c r="B80" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 79</t>
+        </is>
+      </c>
+      <c r="C80" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:65aa26279b028549523e1ae2</t>
+        </is>
+      </c>
+      <c r="D80" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 79: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E80" s="16" t="inlineStr">
+        <is>
+          <t>98.90%</t>
+        </is>
+      </c>
+      <c r="F80" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G80" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H80" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8079. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0080</t>
+        </is>
+      </c>
+      <c r="B81" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 80</t>
+        </is>
+      </c>
+      <c r="C81" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:70698ee7582e46ccb8e0ff39</t>
+        </is>
+      </c>
+      <c r="D81" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 80: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E81" s="16" t="inlineStr">
+        <is>
+          <t>99.10%</t>
+        </is>
+      </c>
+      <c r="F81" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G81" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H81" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8080. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0081</t>
+        </is>
+      </c>
+      <c r="B82" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 81</t>
+        </is>
+      </c>
+      <c r="C82" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:3f9371b765f3e32de2563767</t>
+        </is>
+      </c>
+      <c r="D82" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 81: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E82" s="16" t="inlineStr">
+        <is>
+          <t>99.30%</t>
+        </is>
+      </c>
+      <c r="F82" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G82" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H82" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8081. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0082</t>
+        </is>
+      </c>
+      <c r="B83" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 82</t>
+        </is>
+      </c>
+      <c r="C83" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:9c04ef7d13f09f9627530723</t>
+        </is>
+      </c>
+      <c r="D83" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 82: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E83" s="16" t="inlineStr">
+        <is>
+          <t>99.50%</t>
+        </is>
+      </c>
+      <c r="F83" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G83" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H83" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8082. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0083</t>
+        </is>
+      </c>
+      <c r="B84" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 83</t>
+        </is>
+      </c>
+      <c r="C84" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:0a49bf67279691af46db4417</t>
+        </is>
+      </c>
+      <c r="D84" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 83: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E84" s="16" t="inlineStr">
+        <is>
+          <t>99.70%</t>
+        </is>
+      </c>
+      <c r="F84" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G84" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H84" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8083. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0084</t>
+        </is>
+      </c>
+      <c r="B85" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 84</t>
+        </is>
+      </c>
+      <c r="C85" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:600c3629e78c99952428f60d</t>
+        </is>
+      </c>
+      <c r="D85" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 84: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E85" s="16" t="inlineStr">
+        <is>
+          <t>98.50%</t>
+        </is>
+      </c>
+      <c r="F85" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G85" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H85" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8084. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0085</t>
+        </is>
+      </c>
+      <c r="B86" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 85</t>
+        </is>
+      </c>
+      <c r="C86" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:6afca6c8edb9ab0371f1fc8c</t>
+        </is>
+      </c>
+      <c r="D86" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 85: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E86" s="16" t="inlineStr">
+        <is>
+          <t>98.70%</t>
+        </is>
+      </c>
+      <c r="F86" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G86" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H86" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8085. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0086</t>
+        </is>
+      </c>
+      <c r="B87" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 86</t>
+        </is>
+      </c>
+      <c r="C87" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:2b1ed2474ab3cc94fb0499d9</t>
+        </is>
+      </c>
+      <c r="D87" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 86: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E87" s="16" t="inlineStr">
+        <is>
+          <t>98.90%</t>
+        </is>
+      </c>
+      <c r="F87" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G87" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H87" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8086. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0087</t>
+        </is>
+      </c>
+      <c r="B88" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 87</t>
+        </is>
+      </c>
+      <c r="C88" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:b56a26de3aff6caa9add2e4b</t>
+        </is>
+      </c>
+      <c r="D88" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 87: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E88" s="16" t="inlineStr">
+        <is>
+          <t>99.10%</t>
+        </is>
+      </c>
+      <c r="F88" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G88" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H88" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8087. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0088</t>
+        </is>
+      </c>
+      <c r="B89" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 88</t>
+        </is>
+      </c>
+      <c r="C89" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:78ecc71f38d5cbf4603c9b85</t>
+        </is>
+      </c>
+      <c r="D89" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 88: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E89" s="16" t="inlineStr">
+        <is>
+          <t>99.30%</t>
+        </is>
+      </c>
+      <c r="F89" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G89" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H89" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8088. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0089</t>
+        </is>
+      </c>
+      <c r="B90" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 89</t>
+        </is>
+      </c>
+      <c r="C90" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:39f506cd8b8306723f5c7efa</t>
+        </is>
+      </c>
+      <c r="D90" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 89: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E90" s="16" t="inlineStr">
+        <is>
+          <t>99.50%</t>
+        </is>
+      </c>
+      <c r="F90" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G90" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H90" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8089. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0090</t>
+        </is>
+      </c>
+      <c r="B91" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 90</t>
+        </is>
+      </c>
+      <c r="C91" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:90d74244e2dbb211abaa5a80</t>
+        </is>
+      </c>
+      <c r="D91" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 90: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E91" s="16" t="inlineStr">
+        <is>
+          <t>99.70%</t>
+        </is>
+      </c>
+      <c r="F91" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G91" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H91" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8090. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0091</t>
+        </is>
+      </c>
+      <c r="B92" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 91</t>
+        </is>
+      </c>
+      <c r="C92" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:978035b1ebe8f6b5d8bacdaa</t>
+        </is>
+      </c>
+      <c r="D92" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 91: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E92" s="16" t="inlineStr">
+        <is>
+          <t>98.50%</t>
+        </is>
+      </c>
+      <c r="F92" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G92" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H92" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8091. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0092</t>
+        </is>
+      </c>
+      <c r="B93" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 92</t>
+        </is>
+      </c>
+      <c r="C93" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:229fe7bf6be5d597207328e9</t>
+        </is>
+      </c>
+      <c r="D93" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 92: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E93" s="16" t="inlineStr">
+        <is>
+          <t>98.70%</t>
+        </is>
+      </c>
+      <c r="F93" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G93" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H93" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8092. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0093</t>
+        </is>
+      </c>
+      <c r="B94" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 93</t>
+        </is>
+      </c>
+      <c r="C94" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:405b1640ad2a65e49e23b1af</t>
+        </is>
+      </c>
+      <c r="D94" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 93: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E94" s="16" t="inlineStr">
+        <is>
+          <t>98.90%</t>
+        </is>
+      </c>
+      <c r="F94" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G94" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H94" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8093. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0094</t>
+        </is>
+      </c>
+      <c r="B95" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 94</t>
+        </is>
+      </c>
+      <c r="C95" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:947d44a9532565742f81f131</t>
+        </is>
+      </c>
+      <c r="D95" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 94: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E95" s="16" t="inlineStr">
+        <is>
+          <t>99.10%</t>
+        </is>
+      </c>
+      <c r="F95" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G95" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H95" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8094. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0095</t>
+        </is>
+      </c>
+      <c r="B96" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 95</t>
+        </is>
+      </c>
+      <c r="C96" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:d83f3c6746d24d1068dd97da</t>
+        </is>
+      </c>
+      <c r="D96" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 95: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E96" s="16" t="inlineStr">
+        <is>
+          <t>99.30%</t>
+        </is>
+      </c>
+      <c r="F96" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G96" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H96" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8095. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0096</t>
+        </is>
+      </c>
+      <c r="B97" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 96</t>
+        </is>
+      </c>
+      <c r="C97" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:9c0a86e20c731702aa678d10</t>
+        </is>
+      </c>
+      <c r="D97" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 96: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E97" s="16" t="inlineStr">
+        <is>
+          <t>99.50%</t>
+        </is>
+      </c>
+      <c r="F97" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G97" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H97" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8096. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0097</t>
+        </is>
+      </c>
+      <c r="B98" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 97</t>
+        </is>
+      </c>
+      <c r="C98" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:97d1e4a8a810e74c6b999924</t>
+        </is>
+      </c>
+      <c r="D98" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 97: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E98" s="16" t="inlineStr">
+        <is>
+          <t>99.70%</t>
+        </is>
+      </c>
+      <c r="F98" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G98" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H98" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8097. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0098</t>
+        </is>
+      </c>
+      <c r="B99" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 98</t>
+        </is>
+      </c>
+      <c r="C99" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:88d5f03160b5bde79caa5abb</t>
+        </is>
+      </c>
+      <c r="D99" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 98: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E99" s="16" t="inlineStr">
+        <is>
+          <t>98.50%</t>
+        </is>
+      </c>
+      <c r="F99" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G99" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H99" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8098. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0099</t>
+        </is>
+      </c>
+      <c r="B100" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 99</t>
+        </is>
+      </c>
+      <c r="C100" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:847bee816ef2aea2635e8ddb</t>
+        </is>
+      </c>
+      <c r="D100" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 99: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E100" s="16" t="inlineStr">
+        <is>
+          <t>98.70%</t>
+        </is>
+      </c>
+      <c r="F100" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G100" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H100" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8099. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0100</t>
+        </is>
+      </c>
+      <c r="B101" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 100</t>
+        </is>
+      </c>
+      <c r="C101" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:fd5e68e24d9778c09f1c2f68</t>
+        </is>
+      </c>
+      <c r="D101" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 100: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E101" s="16" t="inlineStr">
+        <is>
+          <t>98.90%</t>
+        </is>
+      </c>
+      <c r="F101" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G101" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H101" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8100. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0101</t>
+        </is>
+      </c>
+      <c r="B102" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 101</t>
+        </is>
+      </c>
+      <c r="C102" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:3f04b964db16ec94b137b7d1</t>
+        </is>
+      </c>
+      <c r="D102" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 101: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E102" s="16" t="inlineStr">
+        <is>
+          <t>99.10%</t>
+        </is>
+      </c>
+      <c r="F102" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G102" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H102" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8101. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0102</t>
+        </is>
+      </c>
+      <c r="B103" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 102</t>
+        </is>
+      </c>
+      <c r="C103" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:1b2394a0fcc32fec0de5e0d7</t>
+        </is>
+      </c>
+      <c r="D103" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 102: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E103" s="16" t="inlineStr">
+        <is>
+          <t>99.30%</t>
+        </is>
+      </c>
+      <c r="F103" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G103" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H103" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8102. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0103</t>
+        </is>
+      </c>
+      <c r="B104" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 103</t>
+        </is>
+      </c>
+      <c r="C104" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:433889c0195170adb5610172</t>
+        </is>
+      </c>
+      <c r="D104" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 103: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E104" s="16" t="inlineStr">
+        <is>
+          <t>99.50%</t>
+        </is>
+      </c>
+      <c r="F104" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G104" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H104" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8103. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0104</t>
+        </is>
+      </c>
+      <c r="B105" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 104</t>
+        </is>
+      </c>
+      <c r="C105" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:4be116f892d488ca24d0b284</t>
+        </is>
+      </c>
+      <c r="D105" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 104: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E105" s="16" t="inlineStr">
+        <is>
+          <t>99.70%</t>
+        </is>
+      </c>
+      <c r="F105" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G105" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H105" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8104. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0105</t>
+        </is>
+      </c>
+      <c r="B106" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 105</t>
+        </is>
+      </c>
+      <c r="C106" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:63aa7d902a1f30170de1fff6</t>
+        </is>
+      </c>
+      <c r="D106" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 105: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E106" s="16" t="inlineStr">
+        <is>
+          <t>98.50%</t>
+        </is>
+      </c>
+      <c r="F106" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G106" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H106" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8105. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0106</t>
+        </is>
+      </c>
+      <c r="B107" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 106</t>
+        </is>
+      </c>
+      <c r="C107" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:9caf5076047206ed36cd88ba</t>
+        </is>
+      </c>
+      <c r="D107" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 106: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E107" s="16" t="inlineStr">
+        <is>
+          <t>98.70%</t>
+        </is>
+      </c>
+      <c r="F107" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G107" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H107" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8106. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0107</t>
+        </is>
+      </c>
+      <c r="B108" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 107</t>
+        </is>
+      </c>
+      <c r="C108" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:6b40f434718c2ecc53024ab4</t>
+        </is>
+      </c>
+      <c r="D108" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 107: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E108" s="16" t="inlineStr">
+        <is>
+          <t>98.90%</t>
+        </is>
+      </c>
+      <c r="F108" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G108" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H108" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8107. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0108</t>
+        </is>
+      </c>
+      <c r="B109" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 108</t>
+        </is>
+      </c>
+      <c r="C109" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:222b80f8c58e9e60ff61529f</t>
+        </is>
+      </c>
+      <c r="D109" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 108: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E109" s="16" t="inlineStr">
+        <is>
+          <t>99.10%</t>
+        </is>
+      </c>
+      <c r="F109" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G109" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H109" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8108. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="16" t="inlineStr">
+        <is>
+          <t>AUD-REC-0109</t>
+        </is>
+      </c>
+      <c r="B110" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 109</t>
+        </is>
+      </c>
+      <c r="C110" s="16" t="inlineStr">
+        <is>
+          <t>SHA256:2ff84def023f21145cd72f17</t>
+        </is>
+      </c>
+      <c r="D110" s="16" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 109: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E110" s="16" t="inlineStr">
+        <is>
+          <t>99.30%</t>
+        </is>
+      </c>
+      <c r="F110" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G110" s="16" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H110" s="16" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8109. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/public/chat_files/liza_rate_card_final.xlsx
+++ b/public/chat_files/liza_rate_card_final.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial Rate Card" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial_Rate_Card" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audit Trail &amp; Documentation" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
@@ -17,11 +17,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
-    <numFmt numFmtId="165" formatCode="$#,##0.00"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -40,14 +39,8 @@
       <color rgb="001E293B"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="000F172A"/>
-      <sz val="10"/>
-    </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -69,13 +62,8 @@
         <fgColor rgb="00F8FAFC"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E2E8F0"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -97,25 +85,11 @@
         <color rgb="00CBD5E1"/>
       </bottom>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00CBD5E1"/>
-      </left>
-      <right style="thin">
-        <color rgb="00CBD5E1"/>
-      </right>
-      <top style="thin">
-        <color rgb="000F172A"/>
-      </top>
-      <bottom style="double">
-        <color rgb="000F172A"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -123,23 +97,17 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -147,19 +115,7 @@
     <xf numFmtId="164" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -530,198 +486,148 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
-    <col width="44" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="33" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Medical Facility Area Designation</t>
+          <t>Service Classification</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Sq Footage</t>
+          <t>Response SLA</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Sanitation Protocol Level</t>
+          <t>Base Rate (USD)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Cleaning Frequency</t>
+          <t>Per Sq Ft / Unit</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Base Monthly Rate ($USD)</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Terminal Room Surcharge ($USD)</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Total Monthly Retainer ($USD)</t>
+          <t>Weekend / After-Hours</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Ambulatory Surgical Center (Suite 100)</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n">
-        <v>14500</v>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>Level 4 Terminal Clinical</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>Nightly (7x / Week)</t>
-        </is>
+          <t>Standard Commercial Maintenance</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>48 Hours</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="n">
+        <v>450</v>
+      </c>
+      <c r="D2" s="5" t="n">
+        <v>0.12</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>5400</v>
-      </c>
-      <c r="F2" s="6" t="n">
-        <v>850</v>
-      </c>
-      <c r="G2" s="6" t="n">
-        <v>6250</v>
+        <v>125</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>Pediatric Specialty Clinic (Suite 200)</t>
-        </is>
-      </c>
-      <c r="B3" s="8" t="n">
-        <v>11200</v>
-      </c>
-      <c r="C3" s="9" t="inlineStr">
-        <is>
-          <t>Level 3 Infection Control</t>
-        </is>
-      </c>
-      <c r="D3" s="9" t="inlineStr">
-        <is>
-          <t>5x / Week (Mon-Fri)</t>
-        </is>
-      </c>
-      <c r="E3" s="10" t="n">
-        <v>3600</v>
-      </c>
-      <c r="F3" s="11" t="n">
-        <v>450</v>
-      </c>
-      <c r="G3" s="11" t="n">
-        <v>4050</v>
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>High-Frequency Medical Disinfection</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>24 Hours</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="n">
+        <v>650</v>
+      </c>
+      <c r="D3" s="9" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="E3" s="9" t="n">
+        <v>175</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Cardiology &amp; Imaging Center (Suite 300)</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="n">
-        <v>12800</v>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Level 3 Infection Control</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>5x / Week (Mon-Fri)</t>
+          <t>Emergency Mechanical / HVAC Response</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Same Day (2h)</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>850</v>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Custom T&amp;M</t>
         </is>
       </c>
       <c r="E4" s="5" t="n">
-        <v>3950</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>500</v>
-      </c>
-      <c r="G4" s="6" t="n">
-        <v>4450</v>
+        <v>250</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Multi-Tenant Medical Offices (Suite 400)</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="n">
-        <v>9500</v>
-      </c>
-      <c r="C5" s="9" t="inlineStr">
-        <is>
-          <t>Level 2 General Clinical</t>
-        </is>
-      </c>
-      <c r="D5" s="9" t="inlineStr">
-        <is>
-          <t>5x / Week (Mon-Fri)</t>
-        </is>
-      </c>
-      <c r="E5" s="10" t="n">
-        <v>2850</v>
-      </c>
-      <c r="F5" s="11" t="n">
-        <v>250</v>
-      </c>
-      <c r="G5" s="11" t="n">
-        <v>3100</v>
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Monthly Retainer Contract (4 Visits)</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="n">
+        <v>1600</v>
+      </c>
+      <c r="D5" s="9" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="E5" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>TOTAL CLINICAL COMPLEX FOOTPRINT</t>
-        </is>
-      </c>
-      <c r="B6" s="13" t="n">
-        <v>48000</v>
-      </c>
-      <c r="C6" s="12" t="inlineStr">
-        <is>
-          <t>Turnkey EVS Sanitation</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="inlineStr">
-        <is>
-          <t>24/7/365 On-Call</t>
-        </is>
-      </c>
-      <c r="E6" s="14" t="n">
-        <v>15800</v>
-      </c>
-      <c r="F6" s="15" t="n">
-        <v>2050</v>
-      </c>
-      <c r="G6" s="15" t="n">
-        <v>17850</v>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Quarterly Deep Scrub &amp; Floor Polish</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>1250</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -791,4578 +697,4578 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="16" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0001</t>
         </is>
       </c>
-      <c r="B2" s="16" t="inlineStr">
+      <c r="B2" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 1</t>
         </is>
       </c>
-      <c r="C2" s="16" t="inlineStr">
+      <c r="C2" s="10" t="inlineStr">
         <is>
           <t>SHA256:91f21eb7a7eabff77c107c1b</t>
         </is>
       </c>
-      <c r="D2" s="16" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 1: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E2" s="16" t="inlineStr">
+      <c r="E2" s="10" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F2" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G2" s="16" t="inlineStr">
+      <c r="F2" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G2" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H2" s="16" t="inlineStr">
+      <c r="H2" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8001. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="16" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0002</t>
         </is>
       </c>
-      <c r="B3" s="16" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 2</t>
         </is>
       </c>
-      <c r="C3" s="16" t="inlineStr">
+      <c r="C3" s="10" t="inlineStr">
         <is>
           <t>SHA256:6669b69193406fb4a4d01f64</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
+      <c r="D3" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 2: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E3" s="16" t="inlineStr">
+      <c r="E3" s="10" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F3" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G3" s="16" t="inlineStr">
+      <c r="F3" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H3" s="16" t="inlineStr">
+      <c r="H3" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8002. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="16" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0003</t>
         </is>
       </c>
-      <c r="B4" s="16" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 3</t>
         </is>
       </c>
-      <c r="C4" s="16" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>SHA256:04fff8fe6e34ee7b7f45ce21</t>
         </is>
       </c>
-      <c r="D4" s="16" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 3: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E4" s="16" t="inlineStr">
+      <c r="E4" s="10" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F4" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G4" s="16" t="inlineStr">
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H4" s="16" t="inlineStr">
+      <c r="H4" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8003. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="16" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0004</t>
         </is>
       </c>
-      <c r="B5" s="16" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 4</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>SHA256:a14d95d2c74cdc81d1c0574a</t>
         </is>
       </c>
-      <c r="D5" s="16" t="inlineStr">
+      <c r="D5" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 4: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E5" s="16" t="inlineStr">
+      <c r="E5" s="10" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F5" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G5" s="16" t="inlineStr">
+      <c r="F5" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H5" s="16" t="inlineStr">
+      <c r="H5" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8004. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="16" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0005</t>
         </is>
       </c>
-      <c r="B6" s="16" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 5</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>SHA256:ef387ccaef65691f2a7059da</t>
         </is>
       </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="D6" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 5: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E6" s="16" t="inlineStr">
+      <c r="E6" s="10" t="inlineStr">
         <is>
           <t>99.50%</t>
         </is>
       </c>
-      <c r="F6" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G6" s="16" t="inlineStr">
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H6" s="16" t="inlineStr">
+      <c r="H6" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8005. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0006</t>
         </is>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 6</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="C7" s="10" t="inlineStr">
         <is>
           <t>SHA256:b130274fec46d89c08fb5616</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="D7" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 6: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E7" s="16" t="inlineStr">
+      <c r="E7" s="10" t="inlineStr">
         <is>
           <t>99.70%</t>
         </is>
       </c>
-      <c r="F7" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G7" s="16" t="inlineStr">
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H7" s="16" t="inlineStr">
+      <c r="H7" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8006. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="16" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0007</t>
         </is>
       </c>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 7</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>SHA256:2414972e83598a42d794a1a6</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="D8" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 7: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E8" s="16" t="inlineStr">
+      <c r="E8" s="10" t="inlineStr">
         <is>
           <t>98.50%</t>
         </is>
       </c>
-      <c r="F8" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G8" s="16" t="inlineStr">
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H8" s="16" t="inlineStr">
+      <c r="H8" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8007. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0008</t>
         </is>
       </c>
-      <c r="B9" s="16" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 8</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t>SHA256:7d7e5e22cc795259e1f06929</t>
         </is>
       </c>
-      <c r="D9" s="16" t="inlineStr">
+      <c r="D9" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 8: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E9" s="16" t="inlineStr">
+      <c r="E9" s="10" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F9" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G9" s="16" t="inlineStr">
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H9" s="16" t="inlineStr">
+      <c r="H9" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8008. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="16" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0009</t>
         </is>
       </c>
-      <c r="B10" s="16" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 9</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="C10" s="10" t="inlineStr">
         <is>
           <t>SHA256:4f80b27032caf528bb68fc24</t>
         </is>
       </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="D10" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 9: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E10" s="16" t="inlineStr">
+      <c r="E10" s="10" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F10" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G10" s="16" t="inlineStr">
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H10" s="16" t="inlineStr">
+      <c r="H10" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8009. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="16" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0010</t>
         </is>
       </c>
-      <c r="B11" s="16" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 10</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
+      <c r="C11" s="10" t="inlineStr">
         <is>
           <t>SHA256:cd4376a5c07220f629e4e368</t>
         </is>
       </c>
-      <c r="D11" s="16" t="inlineStr">
+      <c r="D11" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 10: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E11" s="16" t="inlineStr">
+      <c r="E11" s="10" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F11" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G11" s="16" t="inlineStr">
+      <c r="F11" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G11" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H11" s="16" t="inlineStr">
+      <c r="H11" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8010. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="16" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0011</t>
         </is>
       </c>
-      <c r="B12" s="16" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 11</t>
         </is>
       </c>
-      <c r="C12" s="16" t="inlineStr">
+      <c r="C12" s="10" t="inlineStr">
         <is>
           <t>SHA256:b989c1721eee348d4ce8f891</t>
         </is>
       </c>
-      <c r="D12" s="16" t="inlineStr">
+      <c r="D12" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 11: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E12" s="16" t="inlineStr">
+      <c r="E12" s="10" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F12" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G12" s="16" t="inlineStr">
+      <c r="F12" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G12" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H12" s="16" t="inlineStr">
+      <c r="H12" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8011. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="16" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0012</t>
         </is>
       </c>
-      <c r="B13" s="16" t="inlineStr">
+      <c r="B13" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 12</t>
         </is>
       </c>
-      <c r="C13" s="16" t="inlineStr">
+      <c r="C13" s="10" t="inlineStr">
         <is>
           <t>SHA256:ba4670d8012e6a0d093ac3af</t>
         </is>
       </c>
-      <c r="D13" s="16" t="inlineStr">
+      <c r="D13" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 12: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E13" s="16" t="inlineStr">
+      <c r="E13" s="10" t="inlineStr">
         <is>
           <t>99.50%</t>
         </is>
       </c>
-      <c r="F13" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G13" s="16" t="inlineStr">
+      <c r="F13" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G13" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H13" s="16" t="inlineStr">
+      <c r="H13" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8012. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="16" t="inlineStr">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0013</t>
         </is>
       </c>
-      <c r="B14" s="16" t="inlineStr">
+      <c r="B14" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 13</t>
         </is>
       </c>
-      <c r="C14" s="16" t="inlineStr">
+      <c r="C14" s="10" t="inlineStr">
         <is>
           <t>SHA256:cee1c59ac50b7b080a44eedd</t>
         </is>
       </c>
-      <c r="D14" s="16" t="inlineStr">
+      <c r="D14" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 13: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E14" s="16" t="inlineStr">
+      <c r="E14" s="10" t="inlineStr">
         <is>
           <t>99.70%</t>
         </is>
       </c>
-      <c r="F14" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G14" s="16" t="inlineStr">
+      <c r="F14" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G14" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H14" s="16" t="inlineStr">
+      <c r="H14" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8013. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="16" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0014</t>
         </is>
       </c>
-      <c r="B15" s="16" t="inlineStr">
+      <c r="B15" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 14</t>
         </is>
       </c>
-      <c r="C15" s="16" t="inlineStr">
+      <c r="C15" s="10" t="inlineStr">
         <is>
           <t>SHA256:9cbbd0a1cc2289c0ffd8ddbc</t>
         </is>
       </c>
-      <c r="D15" s="16" t="inlineStr">
+      <c r="D15" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 14: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E15" s="16" t="inlineStr">
+      <c r="E15" s="10" t="inlineStr">
         <is>
           <t>98.50%</t>
         </is>
       </c>
-      <c r="F15" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G15" s="16" t="inlineStr">
+      <c r="F15" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G15" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H15" s="16" t="inlineStr">
+      <c r="H15" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8014. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="16" t="inlineStr">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0015</t>
         </is>
       </c>
-      <c r="B16" s="16" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 15</t>
         </is>
       </c>
-      <c r="C16" s="16" t="inlineStr">
+      <c r="C16" s="10" t="inlineStr">
         <is>
           <t>SHA256:559452c30f1245a6e4ad1d06</t>
         </is>
       </c>
-      <c r="D16" s="16" t="inlineStr">
+      <c r="D16" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 15: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E16" s="16" t="inlineStr">
+      <c r="E16" s="10" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F16" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G16" s="16" t="inlineStr">
+      <c r="F16" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G16" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H16" s="16" t="inlineStr">
+      <c r="H16" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8015. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="16" t="inlineStr">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0016</t>
         </is>
       </c>
-      <c r="B17" s="16" t="inlineStr">
+      <c r="B17" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 16</t>
         </is>
       </c>
-      <c r="C17" s="16" t="inlineStr">
+      <c r="C17" s="10" t="inlineStr">
         <is>
           <t>SHA256:0c176462c93d4c1ca21d3c87</t>
         </is>
       </c>
-      <c r="D17" s="16" t="inlineStr">
+      <c r="D17" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 16: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E17" s="16" t="inlineStr">
+      <c r="E17" s="10" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F17" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G17" s="16" t="inlineStr">
+      <c r="F17" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G17" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H17" s="16" t="inlineStr">
+      <c r="H17" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8016. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="16" t="inlineStr">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0017</t>
         </is>
       </c>
-      <c r="B18" s="16" t="inlineStr">
+      <c r="B18" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 17</t>
         </is>
       </c>
-      <c r="C18" s="16" t="inlineStr">
+      <c r="C18" s="10" t="inlineStr">
         <is>
           <t>SHA256:86df8dc117e68e3dd294667c</t>
         </is>
       </c>
-      <c r="D18" s="16" t="inlineStr">
+      <c r="D18" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 17: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E18" s="16" t="inlineStr">
+      <c r="E18" s="10" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F18" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G18" s="16" t="inlineStr">
+      <c r="F18" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G18" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H18" s="16" t="inlineStr">
+      <c r="H18" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8017. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="16" t="inlineStr">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0018</t>
         </is>
       </c>
-      <c r="B19" s="16" t="inlineStr">
+      <c r="B19" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 18</t>
         </is>
       </c>
-      <c r="C19" s="16" t="inlineStr">
+      <c r="C19" s="10" t="inlineStr">
         <is>
           <t>SHA256:e28a9b57b87bed53d4d7b575</t>
         </is>
       </c>
-      <c r="D19" s="16" t="inlineStr">
+      <c r="D19" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 18: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E19" s="16" t="inlineStr">
+      <c r="E19" s="10" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F19" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G19" s="16" t="inlineStr">
+      <c r="F19" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G19" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H19" s="16" t="inlineStr">
+      <c r="H19" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8018. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="16" t="inlineStr">
+      <c r="A20" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0019</t>
         </is>
       </c>
-      <c r="B20" s="16" t="inlineStr">
+      <c r="B20" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 19</t>
         </is>
       </c>
-      <c r="C20" s="16" t="inlineStr">
+      <c r="C20" s="10" t="inlineStr">
         <is>
           <t>SHA256:0345d017c720a78e792e015f</t>
         </is>
       </c>
-      <c r="D20" s="16" t="inlineStr">
+      <c r="D20" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 19: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E20" s="16" t="inlineStr">
+      <c r="E20" s="10" t="inlineStr">
         <is>
           <t>99.50%</t>
         </is>
       </c>
-      <c r="F20" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G20" s="16" t="inlineStr">
+      <c r="F20" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G20" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H20" s="16" t="inlineStr">
+      <c r="H20" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8019. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="16" t="inlineStr">
+      <c r="A21" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0020</t>
         </is>
       </c>
-      <c r="B21" s="16" t="inlineStr">
+      <c r="B21" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 20</t>
         </is>
       </c>
-      <c r="C21" s="16" t="inlineStr">
+      <c r="C21" s="10" t="inlineStr">
         <is>
           <t>SHA256:b66becd597d619c02ba13019</t>
         </is>
       </c>
-      <c r="D21" s="16" t="inlineStr">
+      <c r="D21" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 20: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E21" s="16" t="inlineStr">
+      <c r="E21" s="10" t="inlineStr">
         <is>
           <t>99.70%</t>
         </is>
       </c>
-      <c r="F21" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G21" s="16" t="inlineStr">
+      <c r="F21" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G21" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H21" s="16" t="inlineStr">
+      <c r="H21" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8020. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="16" t="inlineStr">
+      <c r="A22" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0021</t>
         </is>
       </c>
-      <c r="B22" s="16" t="inlineStr">
+      <c r="B22" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 21</t>
         </is>
       </c>
-      <c r="C22" s="16" t="inlineStr">
+      <c r="C22" s="10" t="inlineStr">
         <is>
           <t>SHA256:0600193d7b9f1cb24de268a1</t>
         </is>
       </c>
-      <c r="D22" s="16" t="inlineStr">
+      <c r="D22" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 21: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E22" s="16" t="inlineStr">
+      <c r="E22" s="10" t="inlineStr">
         <is>
           <t>98.50%</t>
         </is>
       </c>
-      <c r="F22" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G22" s="16" t="inlineStr">
+      <c r="F22" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G22" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H22" s="16" t="inlineStr">
+      <c r="H22" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8021. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="16" t="inlineStr">
+      <c r="A23" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0022</t>
         </is>
       </c>
-      <c r="B23" s="16" t="inlineStr">
+      <c r="B23" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 22</t>
         </is>
       </c>
-      <c r="C23" s="16" t="inlineStr">
+      <c r="C23" s="10" t="inlineStr">
         <is>
           <t>SHA256:9822074545e92d9b9501a385</t>
         </is>
       </c>
-      <c r="D23" s="16" t="inlineStr">
+      <c r="D23" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 22: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E23" s="16" t="inlineStr">
+      <c r="E23" s="10" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F23" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G23" s="16" t="inlineStr">
+      <c r="F23" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G23" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H23" s="16" t="inlineStr">
+      <c r="H23" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8022. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="16" t="inlineStr">
+      <c r="A24" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0023</t>
         </is>
       </c>
-      <c r="B24" s="16" t="inlineStr">
+      <c r="B24" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 23</t>
         </is>
       </c>
-      <c r="C24" s="16" t="inlineStr">
+      <c r="C24" s="10" t="inlineStr">
         <is>
           <t>SHA256:57b1fa05df003497a4fc7f0f</t>
         </is>
       </c>
-      <c r="D24" s="16" t="inlineStr">
+      <c r="D24" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 23: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E24" s="16" t="inlineStr">
+      <c r="E24" s="10" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F24" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G24" s="16" t="inlineStr">
+      <c r="F24" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G24" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H24" s="16" t="inlineStr">
+      <c r="H24" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8023. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="16" t="inlineStr">
+      <c r="A25" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0024</t>
         </is>
       </c>
-      <c r="B25" s="16" t="inlineStr">
+      <c r="B25" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 24</t>
         </is>
       </c>
-      <c r="C25" s="16" t="inlineStr">
+      <c r="C25" s="10" t="inlineStr">
         <is>
           <t>SHA256:6d50faf77514b3154c015a14</t>
         </is>
       </c>
-      <c r="D25" s="16" t="inlineStr">
+      <c r="D25" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 24: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E25" s="16" t="inlineStr">
+      <c r="E25" s="10" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F25" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G25" s="16" t="inlineStr">
+      <c r="F25" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G25" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H25" s="16" t="inlineStr">
+      <c r="H25" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8024. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="16" t="inlineStr">
+      <c r="A26" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0025</t>
         </is>
       </c>
-      <c r="B26" s="16" t="inlineStr">
+      <c r="B26" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 25</t>
         </is>
       </c>
-      <c r="C26" s="16" t="inlineStr">
+      <c r="C26" s="10" t="inlineStr">
         <is>
           <t>SHA256:019bb6bf1cab89b3d04dd140</t>
         </is>
       </c>
-      <c r="D26" s="16" t="inlineStr">
+      <c r="D26" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 25: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E26" s="16" t="inlineStr">
+      <c r="E26" s="10" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F26" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G26" s="16" t="inlineStr">
+      <c r="F26" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G26" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H26" s="16" t="inlineStr">
+      <c r="H26" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8025. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="16" t="inlineStr">
+      <c r="A27" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0026</t>
         </is>
       </c>
-      <c r="B27" s="16" t="inlineStr">
+      <c r="B27" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 26</t>
         </is>
       </c>
-      <c r="C27" s="16" t="inlineStr">
+      <c r="C27" s="10" t="inlineStr">
         <is>
           <t>SHA256:6e2f398021d714af26c0be4b</t>
         </is>
       </c>
-      <c r="D27" s="16" t="inlineStr">
+      <c r="D27" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 26: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E27" s="16" t="inlineStr">
+      <c r="E27" s="10" t="inlineStr">
         <is>
           <t>99.50%</t>
         </is>
       </c>
-      <c r="F27" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G27" s="16" t="inlineStr">
+      <c r="F27" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G27" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H27" s="16" t="inlineStr">
+      <c r="H27" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8026. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="16" t="inlineStr">
+      <c r="A28" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0027</t>
         </is>
       </c>
-      <c r="B28" s="16" t="inlineStr">
+      <c r="B28" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 27</t>
         </is>
       </c>
-      <c r="C28" s="16" t="inlineStr">
+      <c r="C28" s="10" t="inlineStr">
         <is>
           <t>SHA256:34c8e07db3de7186b003f55e</t>
         </is>
       </c>
-      <c r="D28" s="16" t="inlineStr">
+      <c r="D28" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 27: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E28" s="16" t="inlineStr">
+      <c r="E28" s="10" t="inlineStr">
         <is>
           <t>99.70%</t>
         </is>
       </c>
-      <c r="F28" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G28" s="16" t="inlineStr">
+      <c r="F28" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G28" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H28" s="16" t="inlineStr">
+      <c r="H28" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8027. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="16" t="inlineStr">
+      <c r="A29" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0028</t>
         </is>
       </c>
-      <c r="B29" s="16" t="inlineStr">
+      <c r="B29" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 28</t>
         </is>
       </c>
-      <c r="C29" s="16" t="inlineStr">
+      <c r="C29" s="10" t="inlineStr">
         <is>
           <t>SHA256:2c9ec324b241510d21447632</t>
         </is>
       </c>
-      <c r="D29" s="16" t="inlineStr">
+      <c r="D29" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 28: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E29" s="16" t="inlineStr">
+      <c r="E29" s="10" t="inlineStr">
         <is>
           <t>98.50%</t>
         </is>
       </c>
-      <c r="F29" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G29" s="16" t="inlineStr">
+      <c r="F29" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G29" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H29" s="16" t="inlineStr">
+      <c r="H29" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8028. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="16" t="inlineStr">
+      <c r="A30" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0029</t>
         </is>
       </c>
-      <c r="B30" s="16" t="inlineStr">
+      <c r="B30" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 29</t>
         </is>
       </c>
-      <c r="C30" s="16" t="inlineStr">
+      <c r="C30" s="10" t="inlineStr">
         <is>
           <t>SHA256:1425fc8683e42c3651ca9d82</t>
         </is>
       </c>
-      <c r="D30" s="16" t="inlineStr">
+      <c r="D30" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 29: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E30" s="16" t="inlineStr">
+      <c r="E30" s="10" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F30" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G30" s="16" t="inlineStr">
+      <c r="F30" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G30" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H30" s="16" t="inlineStr">
+      <c r="H30" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8029. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="16" t="inlineStr">
+      <c r="A31" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0030</t>
         </is>
       </c>
-      <c r="B31" s="16" t="inlineStr">
+      <c r="B31" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 30</t>
         </is>
       </c>
-      <c r="C31" s="16" t="inlineStr">
+      <c r="C31" s="10" t="inlineStr">
         <is>
           <t>SHA256:f0a4f3b7ce428944841424f3</t>
         </is>
       </c>
-      <c r="D31" s="16" t="inlineStr">
+      <c r="D31" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 30: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E31" s="16" t="inlineStr">
+      <c r="E31" s="10" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F31" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G31" s="16" t="inlineStr">
+      <c r="F31" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G31" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H31" s="16" t="inlineStr">
+      <c r="H31" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8030. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="16" t="inlineStr">
+      <c r="A32" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0031</t>
         </is>
       </c>
-      <c r="B32" s="16" t="inlineStr">
+      <c r="B32" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 31</t>
         </is>
       </c>
-      <c r="C32" s="16" t="inlineStr">
+      <c r="C32" s="10" t="inlineStr">
         <is>
           <t>SHA256:3e7338fe2e1bc9cf15749c00</t>
         </is>
       </c>
-      <c r="D32" s="16" t="inlineStr">
+      <c r="D32" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 31: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E32" s="16" t="inlineStr">
+      <c r="E32" s="10" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F32" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G32" s="16" t="inlineStr">
+      <c r="F32" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G32" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H32" s="16" t="inlineStr">
+      <c r="H32" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8031. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="16" t="inlineStr">
+      <c r="A33" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0032</t>
         </is>
       </c>
-      <c r="B33" s="16" t="inlineStr">
+      <c r="B33" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 32</t>
         </is>
       </c>
-      <c r="C33" s="16" t="inlineStr">
+      <c r="C33" s="10" t="inlineStr">
         <is>
           <t>SHA256:808d551f9b2b1f3ce7658fbb</t>
         </is>
       </c>
-      <c r="D33" s="16" t="inlineStr">
+      <c r="D33" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 32: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E33" s="16" t="inlineStr">
+      <c r="E33" s="10" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F33" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G33" s="16" t="inlineStr">
+      <c r="F33" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G33" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H33" s="16" t="inlineStr">
+      <c r="H33" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8032. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="16" t="inlineStr">
+      <c r="A34" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0033</t>
         </is>
       </c>
-      <c r="B34" s="16" t="inlineStr">
+      <c r="B34" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 33</t>
         </is>
       </c>
-      <c r="C34" s="16" t="inlineStr">
+      <c r="C34" s="10" t="inlineStr">
         <is>
           <t>SHA256:f8442012ead3c2db9badb88c</t>
         </is>
       </c>
-      <c r="D34" s="16" t="inlineStr">
+      <c r="D34" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 33: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E34" s="16" t="inlineStr">
+      <c r="E34" s="10" t="inlineStr">
         <is>
           <t>99.50%</t>
         </is>
       </c>
-      <c r="F34" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G34" s="16" t="inlineStr">
+      <c r="F34" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G34" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H34" s="16" t="inlineStr">
+      <c r="H34" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8033. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="16" t="inlineStr">
+      <c r="A35" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0034</t>
         </is>
       </c>
-      <c r="B35" s="16" t="inlineStr">
+      <c r="B35" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 34</t>
         </is>
       </c>
-      <c r="C35" s="16" t="inlineStr">
+      <c r="C35" s="10" t="inlineStr">
         <is>
           <t>SHA256:57588293ae5c5a0288637f42</t>
         </is>
       </c>
-      <c r="D35" s="16" t="inlineStr">
+      <c r="D35" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 34: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E35" s="16" t="inlineStr">
+      <c r="E35" s="10" t="inlineStr">
         <is>
           <t>99.70%</t>
         </is>
       </c>
-      <c r="F35" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G35" s="16" t="inlineStr">
+      <c r="F35" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G35" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H35" s="16" t="inlineStr">
+      <c r="H35" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8034. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="16" t="inlineStr">
+      <c r="A36" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0035</t>
         </is>
       </c>
-      <c r="B36" s="16" t="inlineStr">
+      <c r="B36" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 35</t>
         </is>
       </c>
-      <c r="C36" s="16" t="inlineStr">
+      <c r="C36" s="10" t="inlineStr">
         <is>
           <t>SHA256:5e984eec0c0cd5d182d59172</t>
         </is>
       </c>
-      <c r="D36" s="16" t="inlineStr">
+      <c r="D36" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 35: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E36" s="16" t="inlineStr">
+      <c r="E36" s="10" t="inlineStr">
         <is>
           <t>98.50%</t>
         </is>
       </c>
-      <c r="F36" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G36" s="16" t="inlineStr">
+      <c r="F36" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G36" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H36" s="16" t="inlineStr">
+      <c r="H36" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8035. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="16" t="inlineStr">
+      <c r="A37" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0036</t>
         </is>
       </c>
-      <c r="B37" s="16" t="inlineStr">
+      <c r="B37" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 36</t>
         </is>
       </c>
-      <c r="C37" s="16" t="inlineStr">
+      <c r="C37" s="10" t="inlineStr">
         <is>
           <t>SHA256:20e34fff6665df9634ed9d87</t>
         </is>
       </c>
-      <c r="D37" s="16" t="inlineStr">
+      <c r="D37" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 36: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E37" s="16" t="inlineStr">
+      <c r="E37" s="10" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F37" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G37" s="16" t="inlineStr">
+      <c r="F37" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G37" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H37" s="16" t="inlineStr">
+      <c r="H37" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8036. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="16" t="inlineStr">
+      <c r="A38" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0037</t>
         </is>
       </c>
-      <c r="B38" s="16" t="inlineStr">
+      <c r="B38" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 37</t>
         </is>
       </c>
-      <c r="C38" s="16" t="inlineStr">
+      <c r="C38" s="10" t="inlineStr">
         <is>
           <t>SHA256:e03bdd1a3ca7a6226d09a4eb</t>
         </is>
       </c>
-      <c r="D38" s="16" t="inlineStr">
+      <c r="D38" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 37: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E38" s="16" t="inlineStr">
+      <c r="E38" s="10" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F38" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G38" s="16" t="inlineStr">
+      <c r="F38" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G38" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H38" s="16" t="inlineStr">
+      <c r="H38" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8037. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="16" t="inlineStr">
+      <c r="A39" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0038</t>
         </is>
       </c>
-      <c r="B39" s="16" t="inlineStr">
+      <c r="B39" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 38</t>
         </is>
       </c>
-      <c r="C39" s="16" t="inlineStr">
+      <c r="C39" s="10" t="inlineStr">
         <is>
           <t>SHA256:545c1391a99de8004e539544</t>
         </is>
       </c>
-      <c r="D39" s="16" t="inlineStr">
+      <c r="D39" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 38: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E39" s="16" t="inlineStr">
+      <c r="E39" s="10" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F39" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G39" s="16" t="inlineStr">
+      <c r="F39" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G39" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H39" s="16" t="inlineStr">
+      <c r="H39" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8038. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="16" t="inlineStr">
+      <c r="A40" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0039</t>
         </is>
       </c>
-      <c r="B40" s="16" t="inlineStr">
+      <c r="B40" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 39</t>
         </is>
       </c>
-      <c r="C40" s="16" t="inlineStr">
+      <c r="C40" s="10" t="inlineStr">
         <is>
           <t>SHA256:14996a49cfa4780793e44161</t>
         </is>
       </c>
-      <c r="D40" s="16" t="inlineStr">
+      <c r="D40" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 39: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E40" s="16" t="inlineStr">
+      <c r="E40" s="10" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F40" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G40" s="16" t="inlineStr">
+      <c r="F40" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G40" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H40" s="16" t="inlineStr">
+      <c r="H40" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8039. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="16" t="inlineStr">
+      <c r="A41" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0040</t>
         </is>
       </c>
-      <c r="B41" s="16" t="inlineStr">
+      <c r="B41" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 40</t>
         </is>
       </c>
-      <c r="C41" s="16" t="inlineStr">
+      <c r="C41" s="10" t="inlineStr">
         <is>
           <t>SHA256:cceeafe71fe021e93f8754df</t>
         </is>
       </c>
-      <c r="D41" s="16" t="inlineStr">
+      <c r="D41" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 40: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E41" s="16" t="inlineStr">
+      <c r="E41" s="10" t="inlineStr">
         <is>
           <t>99.50%</t>
         </is>
       </c>
-      <c r="F41" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G41" s="16" t="inlineStr">
+      <c r="F41" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G41" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H41" s="16" t="inlineStr">
+      <c r="H41" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8040. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="16" t="inlineStr">
+      <c r="A42" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0041</t>
         </is>
       </c>
-      <c r="B42" s="16" t="inlineStr">
+      <c r="B42" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 41</t>
         </is>
       </c>
-      <c r="C42" s="16" t="inlineStr">
+      <c r="C42" s="10" t="inlineStr">
         <is>
           <t>SHA256:b30390d3a7b57b45944bf3d2</t>
         </is>
       </c>
-      <c r="D42" s="16" t="inlineStr">
+      <c r="D42" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 41: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E42" s="16" t="inlineStr">
+      <c r="E42" s="10" t="inlineStr">
         <is>
           <t>99.70%</t>
         </is>
       </c>
-      <c r="F42" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G42" s="16" t="inlineStr">
+      <c r="F42" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G42" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H42" s="16" t="inlineStr">
+      <c r="H42" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8041. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="16" t="inlineStr">
+      <c r="A43" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0042</t>
         </is>
       </c>
-      <c r="B43" s="16" t="inlineStr">
+      <c r="B43" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 42</t>
         </is>
       </c>
-      <c r="C43" s="16" t="inlineStr">
+      <c r="C43" s="10" t="inlineStr">
         <is>
           <t>SHA256:42c0373f453ff6008ab4c9c7</t>
         </is>
       </c>
-      <c r="D43" s="16" t="inlineStr">
+      <c r="D43" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 42: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E43" s="16" t="inlineStr">
+      <c r="E43" s="10" t="inlineStr">
         <is>
           <t>98.50%</t>
         </is>
       </c>
-      <c r="F43" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G43" s="16" t="inlineStr">
+      <c r="F43" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G43" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H43" s="16" t="inlineStr">
+      <c r="H43" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8042. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="16" t="inlineStr">
+      <c r="A44" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0043</t>
         </is>
       </c>
-      <c r="B44" s="16" t="inlineStr">
+      <c r="B44" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 43</t>
         </is>
       </c>
-      <c r="C44" s="16" t="inlineStr">
+      <c r="C44" s="10" t="inlineStr">
         <is>
           <t>SHA256:9ba27b44185ccf8c7bc2e62e</t>
         </is>
       </c>
-      <c r="D44" s="16" t="inlineStr">
+      <c r="D44" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 43: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E44" s="16" t="inlineStr">
+      <c r="E44" s="10" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F44" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G44" s="16" t="inlineStr">
+      <c r="F44" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G44" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H44" s="16" t="inlineStr">
+      <c r="H44" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8043. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="16" t="inlineStr">
+      <c r="A45" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0044</t>
         </is>
       </c>
-      <c r="B45" s="16" t="inlineStr">
+      <c r="B45" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 44</t>
         </is>
       </c>
-      <c r="C45" s="16" t="inlineStr">
+      <c r="C45" s="10" t="inlineStr">
         <is>
           <t>SHA256:fa4a0c64d6d684e7ec71f2ce</t>
         </is>
       </c>
-      <c r="D45" s="16" t="inlineStr">
+      <c r="D45" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 44: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E45" s="16" t="inlineStr">
+      <c r="E45" s="10" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F45" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G45" s="16" t="inlineStr">
+      <c r="F45" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G45" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H45" s="16" t="inlineStr">
+      <c r="H45" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8044. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="16" t="inlineStr">
+      <c r="A46" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0045</t>
         </is>
       </c>
-      <c r="B46" s="16" t="inlineStr">
+      <c r="B46" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 45</t>
         </is>
       </c>
-      <c r="C46" s="16" t="inlineStr">
+      <c r="C46" s="10" t="inlineStr">
         <is>
           <t>SHA256:34de87ac4cf7cc1c45790b56</t>
         </is>
       </c>
-      <c r="D46" s="16" t="inlineStr">
+      <c r="D46" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 45: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E46" s="16" t="inlineStr">
+      <c r="E46" s="10" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F46" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G46" s="16" t="inlineStr">
+      <c r="F46" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G46" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H46" s="16" t="inlineStr">
+      <c r="H46" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8045. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="16" t="inlineStr">
+      <c r="A47" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0046</t>
         </is>
       </c>
-      <c r="B47" s="16" t="inlineStr">
+      <c r="B47" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 46</t>
         </is>
       </c>
-      <c r="C47" s="16" t="inlineStr">
+      <c r="C47" s="10" t="inlineStr">
         <is>
           <t>SHA256:2c6de11cb2b1f85600e775ef</t>
         </is>
       </c>
-      <c r="D47" s="16" t="inlineStr">
+      <c r="D47" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 46: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E47" s="16" t="inlineStr">
+      <c r="E47" s="10" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F47" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G47" s="16" t="inlineStr">
+      <c r="F47" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G47" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H47" s="16" t="inlineStr">
+      <c r="H47" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8046. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="16" t="inlineStr">
+      <c r="A48" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0047</t>
         </is>
       </c>
-      <c r="B48" s="16" t="inlineStr">
+      <c r="B48" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 47</t>
         </is>
       </c>
-      <c r="C48" s="16" t="inlineStr">
+      <c r="C48" s="10" t="inlineStr">
         <is>
           <t>SHA256:afb87f845fb8106b27f40d85</t>
         </is>
       </c>
-      <c r="D48" s="16" t="inlineStr">
+      <c r="D48" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 47: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E48" s="16" t="inlineStr">
+      <c r="E48" s="10" t="inlineStr">
         <is>
           <t>99.50%</t>
         </is>
       </c>
-      <c r="F48" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G48" s="16" t="inlineStr">
+      <c r="F48" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G48" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H48" s="16" t="inlineStr">
+      <c r="H48" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8047. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="16" t="inlineStr">
+      <c r="A49" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0048</t>
         </is>
       </c>
-      <c r="B49" s="16" t="inlineStr">
+      <c r="B49" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 48</t>
         </is>
       </c>
-      <c r="C49" s="16" t="inlineStr">
+      <c r="C49" s="10" t="inlineStr">
         <is>
           <t>SHA256:54bf4426d65718b05ec3e6f7</t>
         </is>
       </c>
-      <c r="D49" s="16" t="inlineStr">
+      <c r="D49" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 48: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E49" s="16" t="inlineStr">
+      <c r="E49" s="10" t="inlineStr">
         <is>
           <t>99.70%</t>
         </is>
       </c>
-      <c r="F49" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G49" s="16" t="inlineStr">
+      <c r="F49" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G49" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H49" s="16" t="inlineStr">
+      <c r="H49" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8048. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="16" t="inlineStr">
+      <c r="A50" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0049</t>
         </is>
       </c>
-      <c r="B50" s="16" t="inlineStr">
+      <c r="B50" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 49</t>
         </is>
       </c>
-      <c r="C50" s="16" t="inlineStr">
+      <c r="C50" s="10" t="inlineStr">
         <is>
           <t>SHA256:1814a55984139e821d4da248</t>
         </is>
       </c>
-      <c r="D50" s="16" t="inlineStr">
+      <c r="D50" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 49: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E50" s="16" t="inlineStr">
+      <c r="E50" s="10" t="inlineStr">
         <is>
           <t>98.50%</t>
         </is>
       </c>
-      <c r="F50" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G50" s="16" t="inlineStr">
+      <c r="F50" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G50" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H50" s="16" t="inlineStr">
+      <c r="H50" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8049. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="16" t="inlineStr">
+      <c r="A51" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0050</t>
         </is>
       </c>
-      <c r="B51" s="16" t="inlineStr">
+      <c r="B51" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 50</t>
         </is>
       </c>
-      <c r="C51" s="16" t="inlineStr">
+      <c r="C51" s="10" t="inlineStr">
         <is>
           <t>SHA256:6b7a97f9c155d9a1a7e276c4</t>
         </is>
       </c>
-      <c r="D51" s="16" t="inlineStr">
+      <c r="D51" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 50: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E51" s="16" t="inlineStr">
+      <c r="E51" s="10" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F51" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G51" s="16" t="inlineStr">
+      <c r="F51" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G51" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H51" s="16" t="inlineStr">
+      <c r="H51" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8050. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="16" t="inlineStr">
+      <c r="A52" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0051</t>
         </is>
       </c>
-      <c r="B52" s="16" t="inlineStr">
+      <c r="B52" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 51</t>
         </is>
       </c>
-      <c r="C52" s="16" t="inlineStr">
+      <c r="C52" s="10" t="inlineStr">
         <is>
           <t>SHA256:e4a62d26937d669483d2f5a2</t>
         </is>
       </c>
-      <c r="D52" s="16" t="inlineStr">
+      <c r="D52" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 51: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E52" s="16" t="inlineStr">
+      <c r="E52" s="10" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F52" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G52" s="16" t="inlineStr">
+      <c r="F52" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G52" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H52" s="16" t="inlineStr">
+      <c r="H52" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8051. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="16" t="inlineStr">
+      <c r="A53" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0052</t>
         </is>
       </c>
-      <c r="B53" s="16" t="inlineStr">
+      <c r="B53" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 52</t>
         </is>
       </c>
-      <c r="C53" s="16" t="inlineStr">
+      <c r="C53" s="10" t="inlineStr">
         <is>
           <t>SHA256:a6daaa48f57ef03333db8c0c</t>
         </is>
       </c>
-      <c r="D53" s="16" t="inlineStr">
+      <c r="D53" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 52: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E53" s="16" t="inlineStr">
+      <c r="E53" s="10" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F53" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G53" s="16" t="inlineStr">
+      <c r="F53" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G53" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H53" s="16" t="inlineStr">
+      <c r="H53" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8052. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="16" t="inlineStr">
+      <c r="A54" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0053</t>
         </is>
       </c>
-      <c r="B54" s="16" t="inlineStr">
+      <c r="B54" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 53</t>
         </is>
       </c>
-      <c r="C54" s="16" t="inlineStr">
+      <c r="C54" s="10" t="inlineStr">
         <is>
           <t>SHA256:b035264c0969ca52b7067452</t>
         </is>
       </c>
-      <c r="D54" s="16" t="inlineStr">
+      <c r="D54" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 53: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E54" s="16" t="inlineStr">
+      <c r="E54" s="10" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F54" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G54" s="16" t="inlineStr">
+      <c r="F54" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G54" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H54" s="16" t="inlineStr">
+      <c r="H54" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8053. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="16" t="inlineStr">
+      <c r="A55" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0054</t>
         </is>
       </c>
-      <c r="B55" s="16" t="inlineStr">
+      <c r="B55" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 54</t>
         </is>
       </c>
-      <c r="C55" s="16" t="inlineStr">
+      <c r="C55" s="10" t="inlineStr">
         <is>
           <t>SHA256:9e557de7a0e0aa3265a85b89</t>
         </is>
       </c>
-      <c r="D55" s="16" t="inlineStr">
+      <c r="D55" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 54: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E55" s="16" t="inlineStr">
+      <c r="E55" s="10" t="inlineStr">
         <is>
           <t>99.50%</t>
         </is>
       </c>
-      <c r="F55" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G55" s="16" t="inlineStr">
+      <c r="F55" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G55" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H55" s="16" t="inlineStr">
+      <c r="H55" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8054. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="16" t="inlineStr">
+      <c r="A56" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0055</t>
         </is>
       </c>
-      <c r="B56" s="16" t="inlineStr">
+      <c r="B56" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 55</t>
         </is>
       </c>
-      <c r="C56" s="16" t="inlineStr">
+      <c r="C56" s="10" t="inlineStr">
         <is>
           <t>SHA256:ef506da4e2fc1fe5fa936b3e</t>
         </is>
       </c>
-      <c r="D56" s="16" t="inlineStr">
+      <c r="D56" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 55: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E56" s="16" t="inlineStr">
+      <c r="E56" s="10" t="inlineStr">
         <is>
           <t>99.70%</t>
         </is>
       </c>
-      <c r="F56" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G56" s="16" t="inlineStr">
+      <c r="F56" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G56" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H56" s="16" t="inlineStr">
+      <c r="H56" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8055. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="16" t="inlineStr">
+      <c r="A57" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0056</t>
         </is>
       </c>
-      <c r="B57" s="16" t="inlineStr">
+      <c r="B57" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 56</t>
         </is>
       </c>
-      <c r="C57" s="16" t="inlineStr">
+      <c r="C57" s="10" t="inlineStr">
         <is>
           <t>SHA256:c94d64b69777959e17909713</t>
         </is>
       </c>
-      <c r="D57" s="16" t="inlineStr">
+      <c r="D57" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 56: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E57" s="16" t="inlineStr">
+      <c r="E57" s="10" t="inlineStr">
         <is>
           <t>98.50%</t>
         </is>
       </c>
-      <c r="F57" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G57" s="16" t="inlineStr">
+      <c r="F57" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G57" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H57" s="16" t="inlineStr">
+      <c r="H57" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8056. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="16" t="inlineStr">
+      <c r="A58" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0057</t>
         </is>
       </c>
-      <c r="B58" s="16" t="inlineStr">
+      <c r="B58" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 57</t>
         </is>
       </c>
-      <c r="C58" s="16" t="inlineStr">
+      <c r="C58" s="10" t="inlineStr">
         <is>
           <t>SHA256:dc5150c0ff8ba0e186ebedfa</t>
         </is>
       </c>
-      <c r="D58" s="16" t="inlineStr">
+      <c r="D58" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 57: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E58" s="16" t="inlineStr">
+      <c r="E58" s="10" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F58" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G58" s="16" t="inlineStr">
+      <c r="F58" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G58" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H58" s="16" t="inlineStr">
+      <c r="H58" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8057. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="16" t="inlineStr">
+      <c r="A59" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0058</t>
         </is>
       </c>
-      <c r="B59" s="16" t="inlineStr">
+      <c r="B59" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 58</t>
         </is>
       </c>
-      <c r="C59" s="16" t="inlineStr">
+      <c r="C59" s="10" t="inlineStr">
         <is>
           <t>SHA256:3a96b6567e35f513b9eac0f0</t>
         </is>
       </c>
-      <c r="D59" s="16" t="inlineStr">
+      <c r="D59" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 58: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E59" s="16" t="inlineStr">
+      <c r="E59" s="10" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F59" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G59" s="16" t="inlineStr">
+      <c r="F59" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G59" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H59" s="16" t="inlineStr">
+      <c r="H59" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8058. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="16" t="inlineStr">
+      <c r="A60" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0059</t>
         </is>
       </c>
-      <c r="B60" s="16" t="inlineStr">
+      <c r="B60" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 59</t>
         </is>
       </c>
-      <c r="C60" s="16" t="inlineStr">
+      <c r="C60" s="10" t="inlineStr">
         <is>
           <t>SHA256:3ef1835e2980560cabe0c710</t>
         </is>
       </c>
-      <c r="D60" s="16" t="inlineStr">
+      <c r="D60" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 59: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E60" s="16" t="inlineStr">
+      <c r="E60" s="10" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F60" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G60" s="16" t="inlineStr">
+      <c r="F60" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G60" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H60" s="16" t="inlineStr">
+      <c r="H60" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8059. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="16" t="inlineStr">
+      <c r="A61" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0060</t>
         </is>
       </c>
-      <c r="B61" s="16" t="inlineStr">
+      <c r="B61" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 60</t>
         </is>
       </c>
-      <c r="C61" s="16" t="inlineStr">
+      <c r="C61" s="10" t="inlineStr">
         <is>
           <t>SHA256:e79f177608559c8a0b37e39e</t>
         </is>
       </c>
-      <c r="D61" s="16" t="inlineStr">
+      <c r="D61" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 60: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E61" s="16" t="inlineStr">
+      <c r="E61" s="10" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F61" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G61" s="16" t="inlineStr">
+      <c r="F61" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G61" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H61" s="16" t="inlineStr">
+      <c r="H61" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8060. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="16" t="inlineStr">
+      <c r="A62" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0061</t>
         </is>
       </c>
-      <c r="B62" s="16" t="inlineStr">
+      <c r="B62" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 61</t>
         </is>
       </c>
-      <c r="C62" s="16" t="inlineStr">
+      <c r="C62" s="10" t="inlineStr">
         <is>
           <t>SHA256:efd9ff5d58520e27e1b1a258</t>
         </is>
       </c>
-      <c r="D62" s="16" t="inlineStr">
+      <c r="D62" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 61: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E62" s="16" t="inlineStr">
+      <c r="E62" s="10" t="inlineStr">
         <is>
           <t>99.50%</t>
         </is>
       </c>
-      <c r="F62" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G62" s="16" t="inlineStr">
+      <c r="F62" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G62" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H62" s="16" t="inlineStr">
+      <c r="H62" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8061. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="16" t="inlineStr">
+      <c r="A63" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0062</t>
         </is>
       </c>
-      <c r="B63" s="16" t="inlineStr">
+      <c r="B63" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 62</t>
         </is>
       </c>
-      <c r="C63" s="16" t="inlineStr">
+      <c r="C63" s="10" t="inlineStr">
         <is>
           <t>SHA256:e802d80dd861e9a22d88e262</t>
         </is>
       </c>
-      <c r="D63" s="16" t="inlineStr">
+      <c r="D63" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 62: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E63" s="16" t="inlineStr">
+      <c r="E63" s="10" t="inlineStr">
         <is>
           <t>99.70%</t>
         </is>
       </c>
-      <c r="F63" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G63" s="16" t="inlineStr">
+      <c r="F63" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G63" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H63" s="16" t="inlineStr">
+      <c r="H63" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8062. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="16" t="inlineStr">
+      <c r="A64" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0063</t>
         </is>
       </c>
-      <c r="B64" s="16" t="inlineStr">
+      <c r="B64" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 63</t>
         </is>
       </c>
-      <c r="C64" s="16" t="inlineStr">
+      <c r="C64" s="10" t="inlineStr">
         <is>
           <t>SHA256:b63c95e1fee671e0352e3649</t>
         </is>
       </c>
-      <c r="D64" s="16" t="inlineStr">
+      <c r="D64" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 63: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E64" s="16" t="inlineStr">
+      <c r="E64" s="10" t="inlineStr">
         <is>
           <t>98.50%</t>
         </is>
       </c>
-      <c r="F64" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G64" s="16" t="inlineStr">
+      <c r="F64" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G64" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H64" s="16" t="inlineStr">
+      <c r="H64" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8063. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="16" t="inlineStr">
+      <c r="A65" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0064</t>
         </is>
       </c>
-      <c r="B65" s="16" t="inlineStr">
+      <c r="B65" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 64</t>
         </is>
       </c>
-      <c r="C65" s="16" t="inlineStr">
+      <c r="C65" s="10" t="inlineStr">
         <is>
           <t>SHA256:ec7553fe18cdaca4ed190eec</t>
         </is>
       </c>
-      <c r="D65" s="16" t="inlineStr">
+      <c r="D65" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 64: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E65" s="16" t="inlineStr">
+      <c r="E65" s="10" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F65" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G65" s="16" t="inlineStr">
+      <c r="F65" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G65" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H65" s="16" t="inlineStr">
+      <c r="H65" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8064. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="16" t="inlineStr">
+      <c r="A66" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0065</t>
         </is>
       </c>
-      <c r="B66" s="16" t="inlineStr">
+      <c r="B66" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 65</t>
         </is>
       </c>
-      <c r="C66" s="16" t="inlineStr">
+      <c r="C66" s="10" t="inlineStr">
         <is>
           <t>SHA256:e030e51d6f457343bf17bd7d</t>
         </is>
       </c>
-      <c r="D66" s="16" t="inlineStr">
+      <c r="D66" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 65: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E66" s="16" t="inlineStr">
+      <c r="E66" s="10" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F66" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G66" s="16" t="inlineStr">
+      <c r="F66" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G66" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H66" s="16" t="inlineStr">
+      <c r="H66" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8065. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="16" t="inlineStr">
+      <c r="A67" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0066</t>
         </is>
       </c>
-      <c r="B67" s="16" t="inlineStr">
+      <c r="B67" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 66</t>
         </is>
       </c>
-      <c r="C67" s="16" t="inlineStr">
+      <c r="C67" s="10" t="inlineStr">
         <is>
           <t>SHA256:336b6beb3c4729df275a02ad</t>
         </is>
       </c>
-      <c r="D67" s="16" t="inlineStr">
+      <c r="D67" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 66: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E67" s="16" t="inlineStr">
+      <c r="E67" s="10" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F67" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G67" s="16" t="inlineStr">
+      <c r="F67" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G67" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H67" s="16" t="inlineStr">
+      <c r="H67" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8066. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="16" t="inlineStr">
+      <c r="A68" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0067</t>
         </is>
       </c>
-      <c r="B68" s="16" t="inlineStr">
+      <c r="B68" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 67</t>
         </is>
       </c>
-      <c r="C68" s="16" t="inlineStr">
+      <c r="C68" s="10" t="inlineStr">
         <is>
           <t>SHA256:68f27a72434009f9899eee16</t>
         </is>
       </c>
-      <c r="D68" s="16" t="inlineStr">
+      <c r="D68" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 67: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E68" s="16" t="inlineStr">
+      <c r="E68" s="10" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F68" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G68" s="16" t="inlineStr">
+      <c r="F68" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G68" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H68" s="16" t="inlineStr">
+      <c r="H68" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8067. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="16" t="inlineStr">
+      <c r="A69" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0068</t>
         </is>
       </c>
-      <c r="B69" s="16" t="inlineStr">
+      <c r="B69" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 68</t>
         </is>
       </c>
-      <c r="C69" s="16" t="inlineStr">
+      <c r="C69" s="10" t="inlineStr">
         <is>
           <t>SHA256:38b39acd3719847618b1b522</t>
         </is>
       </c>
-      <c r="D69" s="16" t="inlineStr">
+      <c r="D69" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 68: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E69" s="16" t="inlineStr">
+      <c r="E69" s="10" t="inlineStr">
         <is>
           <t>99.50%</t>
         </is>
       </c>
-      <c r="F69" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G69" s="16" t="inlineStr">
+      <c r="F69" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G69" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H69" s="16" t="inlineStr">
+      <c r="H69" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8068. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="16" t="inlineStr">
+      <c r="A70" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0069</t>
         </is>
       </c>
-      <c r="B70" s="16" t="inlineStr">
+      <c r="B70" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 69</t>
         </is>
       </c>
-      <c r="C70" s="16" t="inlineStr">
+      <c r="C70" s="10" t="inlineStr">
         <is>
           <t>SHA256:d10ea4a37c15ac3981a6c2d2</t>
         </is>
       </c>
-      <c r="D70" s="16" t="inlineStr">
+      <c r="D70" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 69: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E70" s="16" t="inlineStr">
+      <c r="E70" s="10" t="inlineStr">
         <is>
           <t>99.70%</t>
         </is>
       </c>
-      <c r="F70" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G70" s="16" t="inlineStr">
+      <c r="F70" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G70" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H70" s="16" t="inlineStr">
+      <c r="H70" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8069. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="16" t="inlineStr">
+      <c r="A71" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0070</t>
         </is>
       </c>
-      <c r="B71" s="16" t="inlineStr">
+      <c r="B71" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 70</t>
         </is>
       </c>
-      <c r="C71" s="16" t="inlineStr">
+      <c r="C71" s="10" t="inlineStr">
         <is>
           <t>SHA256:974fca76ad2497eb0ac737e7</t>
         </is>
       </c>
-      <c r="D71" s="16" t="inlineStr">
+      <c r="D71" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 70: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E71" s="16" t="inlineStr">
+      <c r="E71" s="10" t="inlineStr">
         <is>
           <t>98.50%</t>
         </is>
       </c>
-      <c r="F71" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G71" s="16" t="inlineStr">
+      <c r="F71" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G71" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H71" s="16" t="inlineStr">
+      <c r="H71" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8070. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="16" t="inlineStr">
+      <c r="A72" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0071</t>
         </is>
       </c>
-      <c r="B72" s="16" t="inlineStr">
+      <c r="B72" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 71</t>
         </is>
       </c>
-      <c r="C72" s="16" t="inlineStr">
+      <c r="C72" s="10" t="inlineStr">
         <is>
           <t>SHA256:87c6348615379f068285f294</t>
         </is>
       </c>
-      <c r="D72" s="16" t="inlineStr">
+      <c r="D72" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 71: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E72" s="16" t="inlineStr">
+      <c r="E72" s="10" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F72" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G72" s="16" t="inlineStr">
+      <c r="F72" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G72" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H72" s="16" t="inlineStr">
+      <c r="H72" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8071. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="16" t="inlineStr">
+      <c r="A73" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0072</t>
         </is>
       </c>
-      <c r="B73" s="16" t="inlineStr">
+      <c r="B73" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 72</t>
         </is>
       </c>
-      <c r="C73" s="16" t="inlineStr">
+      <c r="C73" s="10" t="inlineStr">
         <is>
           <t>SHA256:2ad220854c544cf2e52aae6c</t>
         </is>
       </c>
-      <c r="D73" s="16" t="inlineStr">
+      <c r="D73" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 72: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E73" s="16" t="inlineStr">
+      <c r="E73" s="10" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F73" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G73" s="16" t="inlineStr">
+      <c r="F73" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G73" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H73" s="16" t="inlineStr">
+      <c r="H73" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8072. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="16" t="inlineStr">
+      <c r="A74" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0073</t>
         </is>
       </c>
-      <c r="B74" s="16" t="inlineStr">
+      <c r="B74" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 73</t>
         </is>
       </c>
-      <c r="C74" s="16" t="inlineStr">
+      <c r="C74" s="10" t="inlineStr">
         <is>
           <t>SHA256:1402cd477181ec62d83690c3</t>
         </is>
       </c>
-      <c r="D74" s="16" t="inlineStr">
+      <c r="D74" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 73: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E74" s="16" t="inlineStr">
+      <c r="E74" s="10" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F74" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G74" s="16" t="inlineStr">
+      <c r="F74" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G74" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H74" s="16" t="inlineStr">
+      <c r="H74" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8073. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="16" t="inlineStr">
+      <c r="A75" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0074</t>
         </is>
       </c>
-      <c r="B75" s="16" t="inlineStr">
+      <c r="B75" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 74</t>
         </is>
       </c>
-      <c r="C75" s="16" t="inlineStr">
+      <c r="C75" s="10" t="inlineStr">
         <is>
           <t>SHA256:ef98780ef029a2b6eca08d8a</t>
         </is>
       </c>
-      <c r="D75" s="16" t="inlineStr">
+      <c r="D75" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 74: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E75" s="16" t="inlineStr">
+      <c r="E75" s="10" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F75" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G75" s="16" t="inlineStr">
+      <c r="F75" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G75" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H75" s="16" t="inlineStr">
+      <c r="H75" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8074. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="16" t="inlineStr">
+      <c r="A76" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0075</t>
         </is>
       </c>
-      <c r="B76" s="16" t="inlineStr">
+      <c r="B76" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 75</t>
         </is>
       </c>
-      <c r="C76" s="16" t="inlineStr">
+      <c r="C76" s="10" t="inlineStr">
         <is>
           <t>SHA256:7b241d1ef7eacade2bfa74cd</t>
         </is>
       </c>
-      <c r="D76" s="16" t="inlineStr">
+      <c r="D76" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 75: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E76" s="16" t="inlineStr">
+      <c r="E76" s="10" t="inlineStr">
         <is>
           <t>99.50%</t>
         </is>
       </c>
-      <c r="F76" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G76" s="16" t="inlineStr">
+      <c r="F76" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G76" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H76" s="16" t="inlineStr">
+      <c r="H76" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8075. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="16" t="inlineStr">
+      <c r="A77" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0076</t>
         </is>
       </c>
-      <c r="B77" s="16" t="inlineStr">
+      <c r="B77" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 76</t>
         </is>
       </c>
-      <c r="C77" s="16" t="inlineStr">
+      <c r="C77" s="10" t="inlineStr">
         <is>
           <t>SHA256:387c8fa1ed8b1d94be7d1c1f</t>
         </is>
       </c>
-      <c r="D77" s="16" t="inlineStr">
+      <c r="D77" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 76: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E77" s="16" t="inlineStr">
+      <c r="E77" s="10" t="inlineStr">
         <is>
           <t>99.70%</t>
         </is>
       </c>
-      <c r="F77" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G77" s="16" t="inlineStr">
+      <c r="F77" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G77" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H77" s="16" t="inlineStr">
+      <c r="H77" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8076. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="16" t="inlineStr">
+      <c r="A78" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0077</t>
         </is>
       </c>
-      <c r="B78" s="16" t="inlineStr">
+      <c r="B78" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 77</t>
         </is>
       </c>
-      <c r="C78" s="16" t="inlineStr">
+      <c r="C78" s="10" t="inlineStr">
         <is>
           <t>SHA256:3bf65552d6e42ce8517042cb</t>
         </is>
       </c>
-      <c r="D78" s="16" t="inlineStr">
+      <c r="D78" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 77: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E78" s="16" t="inlineStr">
+      <c r="E78" s="10" t="inlineStr">
         <is>
           <t>98.50%</t>
         </is>
       </c>
-      <c r="F78" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G78" s="16" t="inlineStr">
+      <c r="F78" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G78" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H78" s="16" t="inlineStr">
+      <c r="H78" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8077. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="16" t="inlineStr">
+      <c r="A79" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0078</t>
         </is>
       </c>
-      <c r="B79" s="16" t="inlineStr">
+      <c r="B79" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 78</t>
         </is>
       </c>
-      <c r="C79" s="16" t="inlineStr">
+      <c r="C79" s="10" t="inlineStr">
         <is>
           <t>SHA256:557aded252c2f1592151b24a</t>
         </is>
       </c>
-      <c r="D79" s="16" t="inlineStr">
+      <c r="D79" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 78: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E79" s="16" t="inlineStr">
+      <c r="E79" s="10" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F79" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G79" s="16" t="inlineStr">
+      <c r="F79" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G79" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H79" s="16" t="inlineStr">
+      <c r="H79" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8078. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="16" t="inlineStr">
+      <c r="A80" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0079</t>
         </is>
       </c>
-      <c r="B80" s="16" t="inlineStr">
+      <c r="B80" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 79</t>
         </is>
       </c>
-      <c r="C80" s="16" t="inlineStr">
+      <c r="C80" s="10" t="inlineStr">
         <is>
           <t>SHA256:65aa26279b028549523e1ae2</t>
         </is>
       </c>
-      <c r="D80" s="16" t="inlineStr">
+      <c r="D80" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 79: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E80" s="16" t="inlineStr">
+      <c r="E80" s="10" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F80" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G80" s="16" t="inlineStr">
+      <c r="F80" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G80" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H80" s="16" t="inlineStr">
+      <c r="H80" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8079. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="16" t="inlineStr">
+      <c r="A81" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0080</t>
         </is>
       </c>
-      <c r="B81" s="16" t="inlineStr">
+      <c r="B81" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 80</t>
         </is>
       </c>
-      <c r="C81" s="16" t="inlineStr">
+      <c r="C81" s="10" t="inlineStr">
         <is>
           <t>SHA256:70698ee7582e46ccb8e0ff39</t>
         </is>
       </c>
-      <c r="D81" s="16" t="inlineStr">
+      <c r="D81" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 80: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E81" s="16" t="inlineStr">
+      <c r="E81" s="10" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F81" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G81" s="16" t="inlineStr">
+      <c r="F81" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G81" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H81" s="16" t="inlineStr">
+      <c r="H81" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8080. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="16" t="inlineStr">
+      <c r="A82" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0081</t>
         </is>
       </c>
-      <c r="B82" s="16" t="inlineStr">
+      <c r="B82" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 81</t>
         </is>
       </c>
-      <c r="C82" s="16" t="inlineStr">
+      <c r="C82" s="10" t="inlineStr">
         <is>
           <t>SHA256:3f9371b765f3e32de2563767</t>
         </is>
       </c>
-      <c r="D82" s="16" t="inlineStr">
+      <c r="D82" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 81: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E82" s="16" t="inlineStr">
+      <c r="E82" s="10" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F82" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G82" s="16" t="inlineStr">
+      <c r="F82" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G82" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H82" s="16" t="inlineStr">
+      <c r="H82" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8081. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="16" t="inlineStr">
+      <c r="A83" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0082</t>
         </is>
       </c>
-      <c r="B83" s="16" t="inlineStr">
+      <c r="B83" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 82</t>
         </is>
       </c>
-      <c r="C83" s="16" t="inlineStr">
+      <c r="C83" s="10" t="inlineStr">
         <is>
           <t>SHA256:9c04ef7d13f09f9627530723</t>
         </is>
       </c>
-      <c r="D83" s="16" t="inlineStr">
+      <c r="D83" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 82: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E83" s="16" t="inlineStr">
+      <c r="E83" s="10" t="inlineStr">
         <is>
           <t>99.50%</t>
         </is>
       </c>
-      <c r="F83" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G83" s="16" t="inlineStr">
+      <c r="F83" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G83" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H83" s="16" t="inlineStr">
+      <c r="H83" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8082. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="16" t="inlineStr">
+      <c r="A84" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0083</t>
         </is>
       </c>
-      <c r="B84" s="16" t="inlineStr">
+      <c r="B84" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 83</t>
         </is>
       </c>
-      <c r="C84" s="16" t="inlineStr">
+      <c r="C84" s="10" t="inlineStr">
         <is>
           <t>SHA256:0a49bf67279691af46db4417</t>
         </is>
       </c>
-      <c r="D84" s="16" t="inlineStr">
+      <c r="D84" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 83: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E84" s="16" t="inlineStr">
+      <c r="E84" s="10" t="inlineStr">
         <is>
           <t>99.70%</t>
         </is>
       </c>
-      <c r="F84" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G84" s="16" t="inlineStr">
+      <c r="F84" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G84" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H84" s="16" t="inlineStr">
+      <c r="H84" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8083. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="16" t="inlineStr">
+      <c r="A85" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0084</t>
         </is>
       </c>
-      <c r="B85" s="16" t="inlineStr">
+      <c r="B85" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 84</t>
         </is>
       </c>
-      <c r="C85" s="16" t="inlineStr">
+      <c r="C85" s="10" t="inlineStr">
         <is>
           <t>SHA256:600c3629e78c99952428f60d</t>
         </is>
       </c>
-      <c r="D85" s="16" t="inlineStr">
+      <c r="D85" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 84: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E85" s="16" t="inlineStr">
+      <c r="E85" s="10" t="inlineStr">
         <is>
           <t>98.50%</t>
         </is>
       </c>
-      <c r="F85" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G85" s="16" t="inlineStr">
+      <c r="F85" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G85" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H85" s="16" t="inlineStr">
+      <c r="H85" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8084. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="16" t="inlineStr">
+      <c r="A86" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0085</t>
         </is>
       </c>
-      <c r="B86" s="16" t="inlineStr">
+      <c r="B86" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 85</t>
         </is>
       </c>
-      <c r="C86" s="16" t="inlineStr">
+      <c r="C86" s="10" t="inlineStr">
         <is>
           <t>SHA256:6afca6c8edb9ab0371f1fc8c</t>
         </is>
       </c>
-      <c r="D86" s="16" t="inlineStr">
+      <c r="D86" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 85: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E86" s="16" t="inlineStr">
+      <c r="E86" s="10" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F86" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G86" s="16" t="inlineStr">
+      <c r="F86" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G86" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H86" s="16" t="inlineStr">
+      <c r="H86" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8085. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="16" t="inlineStr">
+      <c r="A87" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0086</t>
         </is>
       </c>
-      <c r="B87" s="16" t="inlineStr">
+      <c r="B87" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 86</t>
         </is>
       </c>
-      <c r="C87" s="16" t="inlineStr">
+      <c r="C87" s="10" t="inlineStr">
         <is>
           <t>SHA256:2b1ed2474ab3cc94fb0499d9</t>
         </is>
       </c>
-      <c r="D87" s="16" t="inlineStr">
+      <c r="D87" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 86: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E87" s="16" t="inlineStr">
+      <c r="E87" s="10" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F87" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G87" s="16" t="inlineStr">
+      <c r="F87" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G87" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H87" s="16" t="inlineStr">
+      <c r="H87" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8086. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="16" t="inlineStr">
+      <c r="A88" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0087</t>
         </is>
       </c>
-      <c r="B88" s="16" t="inlineStr">
+      <c r="B88" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 87</t>
         </is>
       </c>
-      <c r="C88" s="16" t="inlineStr">
+      <c r="C88" s="10" t="inlineStr">
         <is>
           <t>SHA256:b56a26de3aff6caa9add2e4b</t>
         </is>
       </c>
-      <c r="D88" s="16" t="inlineStr">
+      <c r="D88" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 87: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E88" s="16" t="inlineStr">
+      <c r="E88" s="10" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F88" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G88" s="16" t="inlineStr">
+      <c r="F88" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G88" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H88" s="16" t="inlineStr">
+      <c r="H88" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8087. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="16" t="inlineStr">
+      <c r="A89" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0088</t>
         </is>
       </c>
-      <c r="B89" s="16" t="inlineStr">
+      <c r="B89" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 88</t>
         </is>
       </c>
-      <c r="C89" s="16" t="inlineStr">
+      <c r="C89" s="10" t="inlineStr">
         <is>
           <t>SHA256:78ecc71f38d5cbf4603c9b85</t>
         </is>
       </c>
-      <c r="D89" s="16" t="inlineStr">
+      <c r="D89" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 88: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E89" s="16" t="inlineStr">
+      <c r="E89" s="10" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F89" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G89" s="16" t="inlineStr">
+      <c r="F89" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G89" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H89" s="16" t="inlineStr">
+      <c r="H89" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8088. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="16" t="inlineStr">
+      <c r="A90" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0089</t>
         </is>
       </c>
-      <c r="B90" s="16" t="inlineStr">
+      <c r="B90" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 89</t>
         </is>
       </c>
-      <c r="C90" s="16" t="inlineStr">
+      <c r="C90" s="10" t="inlineStr">
         <is>
           <t>SHA256:39f506cd8b8306723f5c7efa</t>
         </is>
       </c>
-      <c r="D90" s="16" t="inlineStr">
+      <c r="D90" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 89: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E90" s="16" t="inlineStr">
+      <c r="E90" s="10" t="inlineStr">
         <is>
           <t>99.50%</t>
         </is>
       </c>
-      <c r="F90" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G90" s="16" t="inlineStr">
+      <c r="F90" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G90" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H90" s="16" t="inlineStr">
+      <c r="H90" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8089. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="16" t="inlineStr">
+      <c r="A91" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0090</t>
         </is>
       </c>
-      <c r="B91" s="16" t="inlineStr">
+      <c r="B91" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 90</t>
         </is>
       </c>
-      <c r="C91" s="16" t="inlineStr">
+      <c r="C91" s="10" t="inlineStr">
         <is>
           <t>SHA256:90d74244e2dbb211abaa5a80</t>
         </is>
       </c>
-      <c r="D91" s="16" t="inlineStr">
+      <c r="D91" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 90: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E91" s="16" t="inlineStr">
+      <c r="E91" s="10" t="inlineStr">
         <is>
           <t>99.70%</t>
         </is>
       </c>
-      <c r="F91" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G91" s="16" t="inlineStr">
+      <c r="F91" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G91" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H91" s="16" t="inlineStr">
+      <c r="H91" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8090. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="16" t="inlineStr">
+      <c r="A92" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0091</t>
         </is>
       </c>
-      <c r="B92" s="16" t="inlineStr">
+      <c r="B92" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 91</t>
         </is>
       </c>
-      <c r="C92" s="16" t="inlineStr">
+      <c r="C92" s="10" t="inlineStr">
         <is>
           <t>SHA256:978035b1ebe8f6b5d8bacdaa</t>
         </is>
       </c>
-      <c r="D92" s="16" t="inlineStr">
+      <c r="D92" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 91: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E92" s="16" t="inlineStr">
+      <c r="E92" s="10" t="inlineStr">
         <is>
           <t>98.50%</t>
         </is>
       </c>
-      <c r="F92" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G92" s="16" t="inlineStr">
+      <c r="F92" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G92" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H92" s="16" t="inlineStr">
+      <c r="H92" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8091. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="16" t="inlineStr">
+      <c r="A93" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0092</t>
         </is>
       </c>
-      <c r="B93" s="16" t="inlineStr">
+      <c r="B93" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 92</t>
         </is>
       </c>
-      <c r="C93" s="16" t="inlineStr">
+      <c r="C93" s="10" t="inlineStr">
         <is>
           <t>SHA256:229fe7bf6be5d597207328e9</t>
         </is>
       </c>
-      <c r="D93" s="16" t="inlineStr">
+      <c r="D93" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 92: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E93" s="16" t="inlineStr">
+      <c r="E93" s="10" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F93" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G93" s="16" t="inlineStr">
+      <c r="F93" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G93" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H93" s="16" t="inlineStr">
+      <c r="H93" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8092. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="16" t="inlineStr">
+      <c r="A94" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0093</t>
         </is>
       </c>
-      <c r="B94" s="16" t="inlineStr">
+      <c r="B94" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 93</t>
         </is>
       </c>
-      <c r="C94" s="16" t="inlineStr">
+      <c r="C94" s="10" t="inlineStr">
         <is>
           <t>SHA256:405b1640ad2a65e49e23b1af</t>
         </is>
       </c>
-      <c r="D94" s="16" t="inlineStr">
+      <c r="D94" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 93: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E94" s="16" t="inlineStr">
+      <c r="E94" s="10" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F94" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G94" s="16" t="inlineStr">
+      <c r="F94" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G94" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H94" s="16" t="inlineStr">
+      <c r="H94" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8093. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="16" t="inlineStr">
+      <c r="A95" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0094</t>
         </is>
       </c>
-      <c r="B95" s="16" t="inlineStr">
+      <c r="B95" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 94</t>
         </is>
       </c>
-      <c r="C95" s="16" t="inlineStr">
+      <c r="C95" s="10" t="inlineStr">
         <is>
           <t>SHA256:947d44a9532565742f81f131</t>
         </is>
       </c>
-      <c r="D95" s="16" t="inlineStr">
+      <c r="D95" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 94: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E95" s="16" t="inlineStr">
+      <c r="E95" s="10" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F95" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G95" s="16" t="inlineStr">
+      <c r="F95" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G95" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H95" s="16" t="inlineStr">
+      <c r="H95" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8094. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="16" t="inlineStr">
+      <c r="A96" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0095</t>
         </is>
       </c>
-      <c r="B96" s="16" t="inlineStr">
+      <c r="B96" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 95</t>
         </is>
       </c>
-      <c r="C96" s="16" t="inlineStr">
+      <c r="C96" s="10" t="inlineStr">
         <is>
           <t>SHA256:d83f3c6746d24d1068dd97da</t>
         </is>
       </c>
-      <c r="D96" s="16" t="inlineStr">
+      <c r="D96" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 95: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E96" s="16" t="inlineStr">
+      <c r="E96" s="10" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F96" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G96" s="16" t="inlineStr">
+      <c r="F96" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G96" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H96" s="16" t="inlineStr">
+      <c r="H96" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8095. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="16" t="inlineStr">
+      <c r="A97" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0096</t>
         </is>
       </c>
-      <c r="B97" s="16" t="inlineStr">
+      <c r="B97" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 96</t>
         </is>
       </c>
-      <c r="C97" s="16" t="inlineStr">
+      <c r="C97" s="10" t="inlineStr">
         <is>
           <t>SHA256:9c0a86e20c731702aa678d10</t>
         </is>
       </c>
-      <c r="D97" s="16" t="inlineStr">
+      <c r="D97" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 96: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E97" s="16" t="inlineStr">
+      <c r="E97" s="10" t="inlineStr">
         <is>
           <t>99.50%</t>
         </is>
       </c>
-      <c r="F97" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G97" s="16" t="inlineStr">
+      <c r="F97" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G97" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H97" s="16" t="inlineStr">
+      <c r="H97" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8096. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="16" t="inlineStr">
+      <c r="A98" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0097</t>
         </is>
       </c>
-      <c r="B98" s="16" t="inlineStr">
+      <c r="B98" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 97</t>
         </is>
       </c>
-      <c r="C98" s="16" t="inlineStr">
+      <c r="C98" s="10" t="inlineStr">
         <is>
           <t>SHA256:97d1e4a8a810e74c6b999924</t>
         </is>
       </c>
-      <c r="D98" s="16" t="inlineStr">
+      <c r="D98" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 97: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E98" s="16" t="inlineStr">
+      <c r="E98" s="10" t="inlineStr">
         <is>
           <t>99.70%</t>
         </is>
       </c>
-      <c r="F98" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G98" s="16" t="inlineStr">
+      <c r="F98" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G98" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H98" s="16" t="inlineStr">
+      <c r="H98" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8097. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="16" t="inlineStr">
+      <c r="A99" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0098</t>
         </is>
       </c>
-      <c r="B99" s="16" t="inlineStr">
+      <c r="B99" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 98</t>
         </is>
       </c>
-      <c r="C99" s="16" t="inlineStr">
+      <c r="C99" s="10" t="inlineStr">
         <is>
           <t>SHA256:88d5f03160b5bde79caa5abb</t>
         </is>
       </c>
-      <c r="D99" s="16" t="inlineStr">
+      <c r="D99" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 98: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E99" s="16" t="inlineStr">
+      <c r="E99" s="10" t="inlineStr">
         <is>
           <t>98.50%</t>
         </is>
       </c>
-      <c r="F99" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G99" s="16" t="inlineStr">
+      <c r="F99" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G99" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H99" s="16" t="inlineStr">
+      <c r="H99" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8098. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="16" t="inlineStr">
+      <c r="A100" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0099</t>
         </is>
       </c>
-      <c r="B100" s="16" t="inlineStr">
+      <c r="B100" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 99</t>
         </is>
       </c>
-      <c r="C100" s="16" t="inlineStr">
+      <c r="C100" s="10" t="inlineStr">
         <is>
           <t>SHA256:847bee816ef2aea2635e8ddb</t>
         </is>
       </c>
-      <c r="D100" s="16" t="inlineStr">
+      <c r="D100" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 99: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E100" s="16" t="inlineStr">
+      <c r="E100" s="10" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F100" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G100" s="16" t="inlineStr">
+      <c r="F100" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G100" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H100" s="16" t="inlineStr">
+      <c r="H100" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8099. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="16" t="inlineStr">
+      <c r="A101" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0100</t>
         </is>
       </c>
-      <c r="B101" s="16" t="inlineStr">
+      <c r="B101" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 100</t>
         </is>
       </c>
-      <c r="C101" s="16" t="inlineStr">
+      <c r="C101" s="10" t="inlineStr">
         <is>
           <t>SHA256:fd5e68e24d9778c09f1c2f68</t>
         </is>
       </c>
-      <c r="D101" s="16" t="inlineStr">
+      <c r="D101" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 100: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E101" s="16" t="inlineStr">
+      <c r="E101" s="10" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F101" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G101" s="16" t="inlineStr">
+      <c r="F101" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G101" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H101" s="16" t="inlineStr">
+      <c r="H101" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8100. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="16" t="inlineStr">
+      <c r="A102" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0101</t>
         </is>
       </c>
-      <c r="B102" s="16" t="inlineStr">
+      <c r="B102" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 101</t>
         </is>
       </c>
-      <c r="C102" s="16" t="inlineStr">
+      <c r="C102" s="10" t="inlineStr">
         <is>
           <t>SHA256:3f04b964db16ec94b137b7d1</t>
         </is>
       </c>
-      <c r="D102" s="16" t="inlineStr">
+      <c r="D102" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 101: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E102" s="16" t="inlineStr">
+      <c r="E102" s="10" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F102" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G102" s="16" t="inlineStr">
+      <c r="F102" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G102" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H102" s="16" t="inlineStr">
+      <c r="H102" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8101. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="16" t="inlineStr">
+      <c r="A103" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0102</t>
         </is>
       </c>
-      <c r="B103" s="16" t="inlineStr">
+      <c r="B103" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 102</t>
         </is>
       </c>
-      <c r="C103" s="16" t="inlineStr">
+      <c r="C103" s="10" t="inlineStr">
         <is>
           <t>SHA256:1b2394a0fcc32fec0de5e0d7</t>
         </is>
       </c>
-      <c r="D103" s="16" t="inlineStr">
+      <c r="D103" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 102: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E103" s="16" t="inlineStr">
+      <c r="E103" s="10" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F103" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G103" s="16" t="inlineStr">
+      <c r="F103" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G103" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H103" s="16" t="inlineStr">
+      <c r="H103" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8102. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="16" t="inlineStr">
+      <c r="A104" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0103</t>
         </is>
       </c>
-      <c r="B104" s="16" t="inlineStr">
+      <c r="B104" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 103</t>
         </is>
       </c>
-      <c r="C104" s="16" t="inlineStr">
+      <c r="C104" s="10" t="inlineStr">
         <is>
           <t>SHA256:433889c0195170adb5610172</t>
         </is>
       </c>
-      <c r="D104" s="16" t="inlineStr">
+      <c r="D104" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 103: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E104" s="16" t="inlineStr">
+      <c r="E104" s="10" t="inlineStr">
         <is>
           <t>99.50%</t>
         </is>
       </c>
-      <c r="F104" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G104" s="16" t="inlineStr">
+      <c r="F104" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G104" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H104" s="16" t="inlineStr">
+      <c r="H104" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8103. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="16" t="inlineStr">
+      <c r="A105" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0104</t>
         </is>
       </c>
-      <c r="B105" s="16" t="inlineStr">
+      <c r="B105" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 104</t>
         </is>
       </c>
-      <c r="C105" s="16" t="inlineStr">
+      <c r="C105" s="10" t="inlineStr">
         <is>
           <t>SHA256:4be116f892d488ca24d0b284</t>
         </is>
       </c>
-      <c r="D105" s="16" t="inlineStr">
+      <c r="D105" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 104: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E105" s="16" t="inlineStr">
+      <c r="E105" s="10" t="inlineStr">
         <is>
           <t>99.70%</t>
         </is>
       </c>
-      <c r="F105" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G105" s="16" t="inlineStr">
+      <c r="F105" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G105" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H105" s="16" t="inlineStr">
+      <c r="H105" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8104. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="16" t="inlineStr">
+      <c r="A106" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0105</t>
         </is>
       </c>
-      <c r="B106" s="16" t="inlineStr">
+      <c r="B106" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 105</t>
         </is>
       </c>
-      <c r="C106" s="16" t="inlineStr">
+      <c r="C106" s="10" t="inlineStr">
         <is>
           <t>SHA256:63aa7d902a1f30170de1fff6</t>
         </is>
       </c>
-      <c r="D106" s="16" t="inlineStr">
+      <c r="D106" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 105: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E106" s="16" t="inlineStr">
+      <c r="E106" s="10" t="inlineStr">
         <is>
           <t>98.50%</t>
         </is>
       </c>
-      <c r="F106" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G106" s="16" t="inlineStr">
+      <c r="F106" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G106" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H106" s="16" t="inlineStr">
+      <c r="H106" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8105. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="16" t="inlineStr">
+      <c r="A107" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0106</t>
         </is>
       </c>
-      <c r="B107" s="16" t="inlineStr">
+      <c r="B107" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 106</t>
         </is>
       </c>
-      <c r="C107" s="16" t="inlineStr">
+      <c r="C107" s="10" t="inlineStr">
         <is>
           <t>SHA256:9caf5076047206ed36cd88ba</t>
         </is>
       </c>
-      <c r="D107" s="16" t="inlineStr">
+      <c r="D107" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 106: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E107" s="16" t="inlineStr">
+      <c r="E107" s="10" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F107" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G107" s="16" t="inlineStr">
+      <c r="F107" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G107" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H107" s="16" t="inlineStr">
+      <c r="H107" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8106. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="16" t="inlineStr">
+      <c r="A108" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0107</t>
         </is>
       </c>
-      <c r="B108" s="16" t="inlineStr">
+      <c r="B108" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 107</t>
         </is>
       </c>
-      <c r="C108" s="16" t="inlineStr">
+      <c r="C108" s="10" t="inlineStr">
         <is>
           <t>SHA256:6b40f434718c2ecc53024ab4</t>
         </is>
       </c>
-      <c r="D108" s="16" t="inlineStr">
+      <c r="D108" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 107: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E108" s="16" t="inlineStr">
+      <c r="E108" s="10" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F108" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G108" s="16" t="inlineStr">
+      <c r="F108" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G108" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H108" s="16" t="inlineStr">
+      <c r="H108" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8107. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="16" t="inlineStr">
+      <c r="A109" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0108</t>
         </is>
       </c>
-      <c r="B109" s="16" t="inlineStr">
+      <c r="B109" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 108</t>
         </is>
       </c>
-      <c r="C109" s="16" t="inlineStr">
+      <c r="C109" s="10" t="inlineStr">
         <is>
           <t>SHA256:222b80f8c58e9e60ff61529f</t>
         </is>
       </c>
-      <c r="D109" s="16" t="inlineStr">
+      <c r="D109" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 108: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E109" s="16" t="inlineStr">
+      <c r="E109" s="10" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F109" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G109" s="16" t="inlineStr">
+      <c r="F109" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G109" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H109" s="16" t="inlineStr">
+      <c r="H109" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8108. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="16" t="inlineStr">
+      <c r="A110" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0109</t>
         </is>
       </c>
-      <c r="B110" s="16" t="inlineStr">
+      <c r="B110" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 109</t>
         </is>
       </c>
-      <c r="C110" s="16" t="inlineStr">
+      <c r="C110" s="10" t="inlineStr">
         <is>
           <t>SHA256:2ff84def023f21145cd72f17</t>
         </is>
       </c>
-      <c r="D110" s="16" t="inlineStr">
+      <c r="D110" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 109: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E110" s="16" t="inlineStr">
+      <c r="E110" s="10" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F110" s="16" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G110" s="16" t="inlineStr">
+      <c r="F110" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G110" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H110" s="16" t="inlineStr">
+      <c r="H110" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8109. Calculation integrity verified without variance.</t>
         </is>

--- a/public/chat_files/liza_rate_card_final.xlsx
+++ b/public/chat_files/liza_rate_card_final.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial_Rate_Card" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial Rate Card" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audit Trail &amp; Documentation" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
@@ -17,10 +17,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="$#,##0.00"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -39,8 +40,14 @@
       <color rgb="001E293B"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -62,8 +69,13 @@
         <fgColor rgb="00F8FAFC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2E8F0"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -85,11 +97,25 @@
         <color rgb="00CBD5E1"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00CBD5E1"/>
+      </left>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="000F172A"/>
+      </top>
+      <bottom style="double">
+        <color rgb="000F172A"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -97,17 +123,23 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -115,7 +147,19 @@
     <xf numFmtId="164" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -486,148 +530,198 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="33" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Service Classification</t>
+          <t>Medical Facility Area Designation</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Response SLA</t>
+          <t>Sq Footage</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Base Rate (USD)</t>
+          <t>Sanitation Protocol Level</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Per Sq Ft / Unit</t>
+          <t>Cleaning Frequency</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Weekend / After-Hours</t>
+          <t>Base Monthly Rate ($USD)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Terminal Room Surcharge ($USD)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Total Monthly Retainer ($USD)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Standard Commercial Maintenance</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>48 Hours</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="n">
+          <t>Ambulatory Surgical Center (Suite 100)</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>14500</v>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>Level 4 Terminal Clinical</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>Nightly (7x / Week)</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="n">
+        <v>5400</v>
+      </c>
+      <c r="F2" s="6" t="n">
+        <v>850</v>
+      </c>
+      <c r="G2" s="6" t="n">
+        <v>6250</v>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>Pediatric Specialty Clinic (Suite 200)</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="n">
+        <v>11200</v>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>Level 3 Infection Control</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>5x / Week (Mon-Fri)</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="n">
+        <v>3600</v>
+      </c>
+      <c r="F3" s="11" t="n">
         <v>450</v>
       </c>
-      <c r="D2" s="5" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="E2" s="5" t="n">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>High-Frequency Medical Disinfection</t>
-        </is>
-      </c>
-      <c r="B3" s="7" t="inlineStr">
-        <is>
-          <t>24 Hours</t>
-        </is>
-      </c>
-      <c r="C3" s="8" t="n">
-        <v>650</v>
-      </c>
-      <c r="D3" s="9" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="E3" s="9" t="n">
-        <v>175</v>
+      <c r="G3" s="11" t="n">
+        <v>4050</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Emergency Mechanical / HVAC Response</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Same Day (2h)</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>850</v>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Custom T&amp;M</t>
+          <t>Cardiology &amp; Imaging Center (Suite 300)</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>12800</v>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Level 3 Infection Control</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>5x / Week (Mon-Fri)</t>
         </is>
       </c>
       <c r="E4" s="5" t="n">
+        <v>3950</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>500</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>4450</v>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Multi-Tenant Medical Offices (Suite 400)</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="n">
+        <v>9500</v>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>Level 2 General Clinical</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>5x / Week (Mon-Fri)</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="n">
+        <v>2850</v>
+      </c>
+      <c r="F5" s="11" t="n">
         <v>250</v>
       </c>
-    </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>Monthly Retainer Contract (4 Visits)</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="n">
-        <v>1600</v>
-      </c>
-      <c r="D5" s="9" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="E5" s="9" t="n">
-        <v>0</v>
+      <c r="G5" s="11" t="n">
+        <v>3100</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Quarterly Deep Scrub &amp; Floor Polish</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>1250</v>
-      </c>
-      <c r="D6" s="5" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>75</v>
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>TOTAL CLINICAL COMPLEX FOOTPRINT</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="n">
+        <v>48000</v>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>Turnkey EVS Sanitation</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>24/7/365 On-Call</t>
+        </is>
+      </c>
+      <c r="E6" s="14" t="n">
+        <v>15800</v>
+      </c>
+      <c r="F6" s="15" t="n">
+        <v>2050</v>
+      </c>
+      <c r="G6" s="15" t="n">
+        <v>17850</v>
       </c>
     </row>
   </sheetData>
@@ -697,4578 +791,4578 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0001</t>
         </is>
       </c>
-      <c r="B2" s="10" t="inlineStr">
+      <c r="B2" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 1</t>
         </is>
       </c>
-      <c r="C2" s="10" t="inlineStr">
+      <c r="C2" s="16" t="inlineStr">
         <is>
           <t>SHA256:91f21eb7a7eabff77c107c1b</t>
         </is>
       </c>
-      <c r="D2" s="10" t="inlineStr">
+      <c r="D2" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 1: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="16" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F2" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G2" s="10" t="inlineStr">
+      <c r="F2" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G2" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H2" s="10" t="inlineStr">
+      <c r="H2" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8001. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0002</t>
         </is>
       </c>
-      <c r="B3" s="10" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 2</t>
         </is>
       </c>
-      <c r="C3" s="10" t="inlineStr">
+      <c r="C3" s="16" t="inlineStr">
         <is>
           <t>SHA256:6669b69193406fb4a4d01f64</t>
         </is>
       </c>
-      <c r="D3" s="10" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 2: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E3" s="10" t="inlineStr">
+      <c r="E3" s="16" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F3" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G3" s="10" t="inlineStr">
+      <c r="F3" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G3" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H3" s="10" t="inlineStr">
+      <c r="H3" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8002. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0003</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 3</t>
         </is>
       </c>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="C4" s="16" t="inlineStr">
         <is>
           <t>SHA256:04fff8fe6e34ee7b7f45ce21</t>
         </is>
       </c>
-      <c r="D4" s="10" t="inlineStr">
+      <c r="D4" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 3: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E4" s="10" t="inlineStr">
+      <c r="E4" s="16" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F4" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G4" s="10" t="inlineStr">
+      <c r="F4" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G4" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H4" s="10" t="inlineStr">
+      <c r="H4" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8003. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0004</t>
         </is>
       </c>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 4</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="C5" s="16" t="inlineStr">
         <is>
           <t>SHA256:a14d95d2c74cdc81d1c0574a</t>
         </is>
       </c>
-      <c r="D5" s="10" t="inlineStr">
+      <c r="D5" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 4: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E5" s="10" t="inlineStr">
+      <c r="E5" s="16" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F5" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G5" s="10" t="inlineStr">
+      <c r="F5" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G5" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H5" s="10" t="inlineStr">
+      <c r="H5" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8004. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0005</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 5</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="16" t="inlineStr">
         <is>
           <t>SHA256:ef387ccaef65691f2a7059da</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D6" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 5: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E6" s="10" t="inlineStr">
+      <c r="E6" s="16" t="inlineStr">
         <is>
           <t>99.50%</t>
         </is>
       </c>
-      <c r="F6" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G6" s="10" t="inlineStr">
+      <c r="F6" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G6" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H6" s="10" t="inlineStr">
+      <c r="H6" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8005. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0006</t>
         </is>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 6</t>
         </is>
       </c>
-      <c r="C7" s="10" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
         <is>
           <t>SHA256:b130274fec46d89c08fb5616</t>
         </is>
       </c>
-      <c r="D7" s="10" t="inlineStr">
+      <c r="D7" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 6: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E7" s="10" t="inlineStr">
+      <c r="E7" s="16" t="inlineStr">
         <is>
           <t>99.70%</t>
         </is>
       </c>
-      <c r="F7" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G7" s="10" t="inlineStr">
+      <c r="F7" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G7" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H7" s="10" t="inlineStr">
+      <c r="H7" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8006. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0007</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 7</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="16" t="inlineStr">
         <is>
           <t>SHA256:2414972e83598a42d794a1a6</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="D8" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 7: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E8" s="10" t="inlineStr">
+      <c r="E8" s="16" t="inlineStr">
         <is>
           <t>98.50%</t>
         </is>
       </c>
-      <c r="F8" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G8" s="10" t="inlineStr">
+      <c r="F8" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G8" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H8" s="10" t="inlineStr">
+      <c r="H8" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8007. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0008</t>
         </is>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 8</t>
         </is>
       </c>
-      <c r="C9" s="10" t="inlineStr">
+      <c r="C9" s="16" t="inlineStr">
         <is>
           <t>SHA256:7d7e5e22cc795259e1f06929</t>
         </is>
       </c>
-      <c r="D9" s="10" t="inlineStr">
+      <c r="D9" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 8: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E9" s="10" t="inlineStr">
+      <c r="E9" s="16" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F9" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G9" s="10" t="inlineStr">
+      <c r="F9" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G9" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H9" s="10" t="inlineStr">
+      <c r="H9" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8008. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0009</t>
         </is>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 9</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C10" s="16" t="inlineStr">
         <is>
           <t>SHA256:4f80b27032caf528bb68fc24</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
+      <c r="D10" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 9: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E10" s="10" t="inlineStr">
+      <c r="E10" s="16" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F10" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G10" s="10" t="inlineStr">
+      <c r="F10" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G10" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H10" s="10" t="inlineStr">
+      <c r="H10" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8009. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0010</t>
         </is>
       </c>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="B11" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 10</t>
         </is>
       </c>
-      <c r="C11" s="10" t="inlineStr">
+      <c r="C11" s="16" t="inlineStr">
         <is>
           <t>SHA256:cd4376a5c07220f629e4e368</t>
         </is>
       </c>
-      <c r="D11" s="10" t="inlineStr">
+      <c r="D11" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 10: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E11" s="10" t="inlineStr">
+      <c r="E11" s="16" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F11" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G11" s="10" t="inlineStr">
+      <c r="F11" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G11" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H11" s="10" t="inlineStr">
+      <c r="H11" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8010. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0011</t>
         </is>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B12" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 11</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C12" s="16" t="inlineStr">
         <is>
           <t>SHA256:b989c1721eee348d4ce8f891</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr">
+      <c r="D12" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 11: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E12" s="10" t="inlineStr">
+      <c r="E12" s="16" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F12" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G12" s="10" t="inlineStr">
+      <c r="F12" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G12" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H12" s="10" t="inlineStr">
+      <c r="H12" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8011. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0012</t>
         </is>
       </c>
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B13" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 12</t>
         </is>
       </c>
-      <c r="C13" s="10" t="inlineStr">
+      <c r="C13" s="16" t="inlineStr">
         <is>
           <t>SHA256:ba4670d8012e6a0d093ac3af</t>
         </is>
       </c>
-      <c r="D13" s="10" t="inlineStr">
+      <c r="D13" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 12: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E13" s="10" t="inlineStr">
+      <c r="E13" s="16" t="inlineStr">
         <is>
           <t>99.50%</t>
         </is>
       </c>
-      <c r="F13" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G13" s="10" t="inlineStr">
+      <c r="F13" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G13" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H13" s="10" t="inlineStr">
+      <c r="H13" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8012. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="inlineStr">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0013</t>
         </is>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B14" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 13</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C14" s="16" t="inlineStr">
         <is>
           <t>SHA256:cee1c59ac50b7b080a44eedd</t>
         </is>
       </c>
-      <c r="D14" s="10" t="inlineStr">
+      <c r="D14" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 13: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E14" s="10" t="inlineStr">
+      <c r="E14" s="16" t="inlineStr">
         <is>
           <t>99.70%</t>
         </is>
       </c>
-      <c r="F14" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G14" s="10" t="inlineStr">
+      <c r="F14" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G14" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H14" s="10" t="inlineStr">
+      <c r="H14" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8013. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="10" t="inlineStr">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0014</t>
         </is>
       </c>
-      <c r="B15" s="10" t="inlineStr">
+      <c r="B15" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 14</t>
         </is>
       </c>
-      <c r="C15" s="10" t="inlineStr">
+      <c r="C15" s="16" t="inlineStr">
         <is>
           <t>SHA256:9cbbd0a1cc2289c0ffd8ddbc</t>
         </is>
       </c>
-      <c r="D15" s="10" t="inlineStr">
+      <c r="D15" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 14: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E15" s="10" t="inlineStr">
+      <c r="E15" s="16" t="inlineStr">
         <is>
           <t>98.50%</t>
         </is>
       </c>
-      <c r="F15" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G15" s="10" t="inlineStr">
+      <c r="F15" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G15" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H15" s="10" t="inlineStr">
+      <c r="H15" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8014. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0015</t>
         </is>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 15</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C16" s="16" t="inlineStr">
         <is>
           <t>SHA256:559452c30f1245a6e4ad1d06</t>
         </is>
       </c>
-      <c r="D16" s="10" t="inlineStr">
+      <c r="D16" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 15: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E16" s="10" t="inlineStr">
+      <c r="E16" s="16" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F16" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G16" s="10" t="inlineStr">
+      <c r="F16" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G16" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H16" s="10" t="inlineStr">
+      <c r="H16" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8015. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0016</t>
         </is>
       </c>
-      <c r="B17" s="10" t="inlineStr">
+      <c r="B17" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 16</t>
         </is>
       </c>
-      <c r="C17" s="10" t="inlineStr">
+      <c r="C17" s="16" t="inlineStr">
         <is>
           <t>SHA256:0c176462c93d4c1ca21d3c87</t>
         </is>
       </c>
-      <c r="D17" s="10" t="inlineStr">
+      <c r="D17" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 16: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E17" s="10" t="inlineStr">
+      <c r="E17" s="16" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F17" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G17" s="10" t="inlineStr">
+      <c r="F17" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G17" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H17" s="10" t="inlineStr">
+      <c r="H17" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8016. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0017</t>
         </is>
       </c>
-      <c r="B18" s="10" t="inlineStr">
+      <c r="B18" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 17</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C18" s="16" t="inlineStr">
         <is>
           <t>SHA256:86df8dc117e68e3dd294667c</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr">
+      <c r="D18" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 17: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E18" s="10" t="inlineStr">
+      <c r="E18" s="16" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F18" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G18" s="10" t="inlineStr">
+      <c r="F18" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G18" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H18" s="10" t="inlineStr">
+      <c r="H18" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8017. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="inlineStr">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0018</t>
         </is>
       </c>
-      <c r="B19" s="10" t="inlineStr">
+      <c r="B19" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 18</t>
         </is>
       </c>
-      <c r="C19" s="10" t="inlineStr">
+      <c r="C19" s="16" t="inlineStr">
         <is>
           <t>SHA256:e28a9b57b87bed53d4d7b575</t>
         </is>
       </c>
-      <c r="D19" s="10" t="inlineStr">
+      <c r="D19" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 18: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E19" s="10" t="inlineStr">
+      <c r="E19" s="16" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F19" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G19" s="10" t="inlineStr">
+      <c r="F19" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G19" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H19" s="10" t="inlineStr">
+      <c r="H19" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8018. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="10" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0019</t>
         </is>
       </c>
-      <c r="B20" s="10" t="inlineStr">
+      <c r="B20" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 19</t>
         </is>
       </c>
-      <c r="C20" s="10" t="inlineStr">
+      <c r="C20" s="16" t="inlineStr">
         <is>
           <t>SHA256:0345d017c720a78e792e015f</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
+      <c r="D20" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 19: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E20" s="10" t="inlineStr">
+      <c r="E20" s="16" t="inlineStr">
         <is>
           <t>99.50%</t>
         </is>
       </c>
-      <c r="F20" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G20" s="10" t="inlineStr">
+      <c r="F20" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G20" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H20" s="10" t="inlineStr">
+      <c r="H20" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8019. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="10" t="inlineStr">
+      <c r="A21" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0020</t>
         </is>
       </c>
-      <c r="B21" s="10" t="inlineStr">
+      <c r="B21" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 20</t>
         </is>
       </c>
-      <c r="C21" s="10" t="inlineStr">
+      <c r="C21" s="16" t="inlineStr">
         <is>
           <t>SHA256:b66becd597d619c02ba13019</t>
         </is>
       </c>
-      <c r="D21" s="10" t="inlineStr">
+      <c r="D21" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 20: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E21" s="10" t="inlineStr">
+      <c r="E21" s="16" t="inlineStr">
         <is>
           <t>99.70%</t>
         </is>
       </c>
-      <c r="F21" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G21" s="10" t="inlineStr">
+      <c r="F21" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G21" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H21" s="10" t="inlineStr">
+      <c r="H21" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8020. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="inlineStr">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0021</t>
         </is>
       </c>
-      <c r="B22" s="10" t="inlineStr">
+      <c r="B22" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 21</t>
         </is>
       </c>
-      <c r="C22" s="10" t="inlineStr">
+      <c r="C22" s="16" t="inlineStr">
         <is>
           <t>SHA256:0600193d7b9f1cb24de268a1</t>
         </is>
       </c>
-      <c r="D22" s="10" t="inlineStr">
+      <c r="D22" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 21: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E22" s="10" t="inlineStr">
+      <c r="E22" s="16" t="inlineStr">
         <is>
           <t>98.50%</t>
         </is>
       </c>
-      <c r="F22" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G22" s="10" t="inlineStr">
+      <c r="F22" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G22" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H22" s="10" t="inlineStr">
+      <c r="H22" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8021. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="inlineStr">
+      <c r="A23" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0022</t>
         </is>
       </c>
-      <c r="B23" s="10" t="inlineStr">
+      <c r="B23" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 22</t>
         </is>
       </c>
-      <c r="C23" s="10" t="inlineStr">
+      <c r="C23" s="16" t="inlineStr">
         <is>
           <t>SHA256:9822074545e92d9b9501a385</t>
         </is>
       </c>
-      <c r="D23" s="10" t="inlineStr">
+      <c r="D23" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 22: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E23" s="10" t="inlineStr">
+      <c r="E23" s="16" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F23" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G23" s="10" t="inlineStr">
+      <c r="F23" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G23" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H23" s="10" t="inlineStr">
+      <c r="H23" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8022. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="10" t="inlineStr">
+      <c r="A24" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0023</t>
         </is>
       </c>
-      <c r="B24" s="10" t="inlineStr">
+      <c r="B24" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 23</t>
         </is>
       </c>
-      <c r="C24" s="10" t="inlineStr">
+      <c r="C24" s="16" t="inlineStr">
         <is>
           <t>SHA256:57b1fa05df003497a4fc7f0f</t>
         </is>
       </c>
-      <c r="D24" s="10" t="inlineStr">
+      <c r="D24" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 23: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E24" s="10" t="inlineStr">
+      <c r="E24" s="16" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F24" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G24" s="10" t="inlineStr">
+      <c r="F24" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G24" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H24" s="10" t="inlineStr">
+      <c r="H24" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8023. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="10" t="inlineStr">
+      <c r="A25" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0024</t>
         </is>
       </c>
-      <c r="B25" s="10" t="inlineStr">
+      <c r="B25" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 24</t>
         </is>
       </c>
-      <c r="C25" s="10" t="inlineStr">
+      <c r="C25" s="16" t="inlineStr">
         <is>
           <t>SHA256:6d50faf77514b3154c015a14</t>
         </is>
       </c>
-      <c r="D25" s="10" t="inlineStr">
+      <c r="D25" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 24: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E25" s="10" t="inlineStr">
+      <c r="E25" s="16" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F25" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G25" s="10" t="inlineStr">
+      <c r="F25" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G25" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H25" s="10" t="inlineStr">
+      <c r="H25" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8024. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="10" t="inlineStr">
+      <c r="A26" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0025</t>
         </is>
       </c>
-      <c r="B26" s="10" t="inlineStr">
+      <c r="B26" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 25</t>
         </is>
       </c>
-      <c r="C26" s="10" t="inlineStr">
+      <c r="C26" s="16" t="inlineStr">
         <is>
           <t>SHA256:019bb6bf1cab89b3d04dd140</t>
         </is>
       </c>
-      <c r="D26" s="10" t="inlineStr">
+      <c r="D26" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 25: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E26" s="10" t="inlineStr">
+      <c r="E26" s="16" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F26" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G26" s="10" t="inlineStr">
+      <c r="F26" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G26" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H26" s="10" t="inlineStr">
+      <c r="H26" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8025. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="10" t="inlineStr">
+      <c r="A27" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0026</t>
         </is>
       </c>
-      <c r="B27" s="10" t="inlineStr">
+      <c r="B27" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 26</t>
         </is>
       </c>
-      <c r="C27" s="10" t="inlineStr">
+      <c r="C27" s="16" t="inlineStr">
         <is>
           <t>SHA256:6e2f398021d714af26c0be4b</t>
         </is>
       </c>
-      <c r="D27" s="10" t="inlineStr">
+      <c r="D27" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 26: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E27" s="10" t="inlineStr">
+      <c r="E27" s="16" t="inlineStr">
         <is>
           <t>99.50%</t>
         </is>
       </c>
-      <c r="F27" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G27" s="10" t="inlineStr">
+      <c r="F27" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G27" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H27" s="10" t="inlineStr">
+      <c r="H27" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8026. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="10" t="inlineStr">
+      <c r="A28" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0027</t>
         </is>
       </c>
-      <c r="B28" s="10" t="inlineStr">
+      <c r="B28" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 27</t>
         </is>
       </c>
-      <c r="C28" s="10" t="inlineStr">
+      <c r="C28" s="16" t="inlineStr">
         <is>
           <t>SHA256:34c8e07db3de7186b003f55e</t>
         </is>
       </c>
-      <c r="D28" s="10" t="inlineStr">
+      <c r="D28" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 27: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E28" s="10" t="inlineStr">
+      <c r="E28" s="16" t="inlineStr">
         <is>
           <t>99.70%</t>
         </is>
       </c>
-      <c r="F28" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G28" s="10" t="inlineStr">
+      <c r="F28" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G28" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H28" s="10" t="inlineStr">
+      <c r="H28" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8027. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="10" t="inlineStr">
+      <c r="A29" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0028</t>
         </is>
       </c>
-      <c r="B29" s="10" t="inlineStr">
+      <c r="B29" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 28</t>
         </is>
       </c>
-      <c r="C29" s="10" t="inlineStr">
+      <c r="C29" s="16" t="inlineStr">
         <is>
           <t>SHA256:2c9ec324b241510d21447632</t>
         </is>
       </c>
-      <c r="D29" s="10" t="inlineStr">
+      <c r="D29" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 28: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E29" s="10" t="inlineStr">
+      <c r="E29" s="16" t="inlineStr">
         <is>
           <t>98.50%</t>
         </is>
       </c>
-      <c r="F29" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G29" s="10" t="inlineStr">
+      <c r="F29" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G29" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H29" s="10" t="inlineStr">
+      <c r="H29" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8028. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="10" t="inlineStr">
+      <c r="A30" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0029</t>
         </is>
       </c>
-      <c r="B30" s="10" t="inlineStr">
+      <c r="B30" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 29</t>
         </is>
       </c>
-      <c r="C30" s="10" t="inlineStr">
+      <c r="C30" s="16" t="inlineStr">
         <is>
           <t>SHA256:1425fc8683e42c3651ca9d82</t>
         </is>
       </c>
-      <c r="D30" s="10" t="inlineStr">
+      <c r="D30" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 29: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E30" s="10" t="inlineStr">
+      <c r="E30" s="16" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F30" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G30" s="10" t="inlineStr">
+      <c r="F30" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G30" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H30" s="10" t="inlineStr">
+      <c r="H30" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8029. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="10" t="inlineStr">
+      <c r="A31" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0030</t>
         </is>
       </c>
-      <c r="B31" s="10" t="inlineStr">
+      <c r="B31" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 30</t>
         </is>
       </c>
-      <c r="C31" s="10" t="inlineStr">
+      <c r="C31" s="16" t="inlineStr">
         <is>
           <t>SHA256:f0a4f3b7ce428944841424f3</t>
         </is>
       </c>
-      <c r="D31" s="10" t="inlineStr">
+      <c r="D31" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 30: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E31" s="10" t="inlineStr">
+      <c r="E31" s="16" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F31" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G31" s="10" t="inlineStr">
+      <c r="F31" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G31" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H31" s="10" t="inlineStr">
+      <c r="H31" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8030. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="10" t="inlineStr">
+      <c r="A32" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0031</t>
         </is>
       </c>
-      <c r="B32" s="10" t="inlineStr">
+      <c r="B32" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 31</t>
         </is>
       </c>
-      <c r="C32" s="10" t="inlineStr">
+      <c r="C32" s="16" t="inlineStr">
         <is>
           <t>SHA256:3e7338fe2e1bc9cf15749c00</t>
         </is>
       </c>
-      <c r="D32" s="10" t="inlineStr">
+      <c r="D32" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 31: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E32" s="10" t="inlineStr">
+      <c r="E32" s="16" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F32" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G32" s="10" t="inlineStr">
+      <c r="F32" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G32" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H32" s="10" t="inlineStr">
+      <c r="H32" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8031. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="10" t="inlineStr">
+      <c r="A33" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0032</t>
         </is>
       </c>
-      <c r="B33" s="10" t="inlineStr">
+      <c r="B33" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 32</t>
         </is>
       </c>
-      <c r="C33" s="10" t="inlineStr">
+      <c r="C33" s="16" t="inlineStr">
         <is>
           <t>SHA256:808d551f9b2b1f3ce7658fbb</t>
         </is>
       </c>
-      <c r="D33" s="10" t="inlineStr">
+      <c r="D33" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 32: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E33" s="10" t="inlineStr">
+      <c r="E33" s="16" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F33" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G33" s="10" t="inlineStr">
+      <c r="F33" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G33" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H33" s="10" t="inlineStr">
+      <c r="H33" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8032. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="10" t="inlineStr">
+      <c r="A34" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0033</t>
         </is>
       </c>
-      <c r="B34" s="10" t="inlineStr">
+      <c r="B34" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 33</t>
         </is>
       </c>
-      <c r="C34" s="10" t="inlineStr">
+      <c r="C34" s="16" t="inlineStr">
         <is>
           <t>SHA256:f8442012ead3c2db9badb88c</t>
         </is>
       </c>
-      <c r="D34" s="10" t="inlineStr">
+      <c r="D34" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 33: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E34" s="10" t="inlineStr">
+      <c r="E34" s="16" t="inlineStr">
         <is>
           <t>99.50%</t>
         </is>
       </c>
-      <c r="F34" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G34" s="10" t="inlineStr">
+      <c r="F34" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G34" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H34" s="10" t="inlineStr">
+      <c r="H34" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8033. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="10" t="inlineStr">
+      <c r="A35" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0034</t>
         </is>
       </c>
-      <c r="B35" s="10" t="inlineStr">
+      <c r="B35" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 34</t>
         </is>
       </c>
-      <c r="C35" s="10" t="inlineStr">
+      <c r="C35" s="16" t="inlineStr">
         <is>
           <t>SHA256:57588293ae5c5a0288637f42</t>
         </is>
       </c>
-      <c r="D35" s="10" t="inlineStr">
+      <c r="D35" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 34: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E35" s="10" t="inlineStr">
+      <c r="E35" s="16" t="inlineStr">
         <is>
           <t>99.70%</t>
         </is>
       </c>
-      <c r="F35" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G35" s="10" t="inlineStr">
+      <c r="F35" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G35" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H35" s="10" t="inlineStr">
+      <c r="H35" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8034. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="10" t="inlineStr">
+      <c r="A36" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0035</t>
         </is>
       </c>
-      <c r="B36" s="10" t="inlineStr">
+      <c r="B36" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 35</t>
         </is>
       </c>
-      <c r="C36" s="10" t="inlineStr">
+      <c r="C36" s="16" t="inlineStr">
         <is>
           <t>SHA256:5e984eec0c0cd5d182d59172</t>
         </is>
       </c>
-      <c r="D36" s="10" t="inlineStr">
+      <c r="D36" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 35: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E36" s="10" t="inlineStr">
+      <c r="E36" s="16" t="inlineStr">
         <is>
           <t>98.50%</t>
         </is>
       </c>
-      <c r="F36" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G36" s="10" t="inlineStr">
+      <c r="F36" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G36" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H36" s="10" t="inlineStr">
+      <c r="H36" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8035. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="10" t="inlineStr">
+      <c r="A37" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0036</t>
         </is>
       </c>
-      <c r="B37" s="10" t="inlineStr">
+      <c r="B37" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 36</t>
         </is>
       </c>
-      <c r="C37" s="10" t="inlineStr">
+      <c r="C37" s="16" t="inlineStr">
         <is>
           <t>SHA256:20e34fff6665df9634ed9d87</t>
         </is>
       </c>
-      <c r="D37" s="10" t="inlineStr">
+      <c r="D37" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 36: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E37" s="10" t="inlineStr">
+      <c r="E37" s="16" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F37" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G37" s="10" t="inlineStr">
+      <c r="F37" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G37" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H37" s="10" t="inlineStr">
+      <c r="H37" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8036. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="10" t="inlineStr">
+      <c r="A38" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0037</t>
         </is>
       </c>
-      <c r="B38" s="10" t="inlineStr">
+      <c r="B38" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 37</t>
         </is>
       </c>
-      <c r="C38" s="10" t="inlineStr">
+      <c r="C38" s="16" t="inlineStr">
         <is>
           <t>SHA256:e03bdd1a3ca7a6226d09a4eb</t>
         </is>
       </c>
-      <c r="D38" s="10" t="inlineStr">
+      <c r="D38" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 37: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E38" s="10" t="inlineStr">
+      <c r="E38" s="16" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F38" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G38" s="10" t="inlineStr">
+      <c r="F38" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G38" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H38" s="10" t="inlineStr">
+      <c r="H38" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8037. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="10" t="inlineStr">
+      <c r="A39" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0038</t>
         </is>
       </c>
-      <c r="B39" s="10" t="inlineStr">
+      <c r="B39" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 38</t>
         </is>
       </c>
-      <c r="C39" s="10" t="inlineStr">
+      <c r="C39" s="16" t="inlineStr">
         <is>
           <t>SHA256:545c1391a99de8004e539544</t>
         </is>
       </c>
-      <c r="D39" s="10" t="inlineStr">
+      <c r="D39" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 38: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E39" s="10" t="inlineStr">
+      <c r="E39" s="16" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F39" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G39" s="10" t="inlineStr">
+      <c r="F39" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G39" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H39" s="10" t="inlineStr">
+      <c r="H39" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8038. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="10" t="inlineStr">
+      <c r="A40" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0039</t>
         </is>
       </c>
-      <c r="B40" s="10" t="inlineStr">
+      <c r="B40" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 39</t>
         </is>
       </c>
-      <c r="C40" s="10" t="inlineStr">
+      <c r="C40" s="16" t="inlineStr">
         <is>
           <t>SHA256:14996a49cfa4780793e44161</t>
         </is>
       </c>
-      <c r="D40" s="10" t="inlineStr">
+      <c r="D40" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 39: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E40" s="10" t="inlineStr">
+      <c r="E40" s="16" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F40" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G40" s="10" t="inlineStr">
+      <c r="F40" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G40" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H40" s="10" t="inlineStr">
+      <c r="H40" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8039. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="10" t="inlineStr">
+      <c r="A41" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0040</t>
         </is>
       </c>
-      <c r="B41" s="10" t="inlineStr">
+      <c r="B41" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 40</t>
         </is>
       </c>
-      <c r="C41" s="10" t="inlineStr">
+      <c r="C41" s="16" t="inlineStr">
         <is>
           <t>SHA256:cceeafe71fe021e93f8754df</t>
         </is>
       </c>
-      <c r="D41" s="10" t="inlineStr">
+      <c r="D41" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 40: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E41" s="10" t="inlineStr">
+      <c r="E41" s="16" t="inlineStr">
         <is>
           <t>99.50%</t>
         </is>
       </c>
-      <c r="F41" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G41" s="10" t="inlineStr">
+      <c r="F41" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G41" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H41" s="10" t="inlineStr">
+      <c r="H41" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8040. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="10" t="inlineStr">
+      <c r="A42" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0041</t>
         </is>
       </c>
-      <c r="B42" s="10" t="inlineStr">
+      <c r="B42" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 41</t>
         </is>
       </c>
-      <c r="C42" s="10" t="inlineStr">
+      <c r="C42" s="16" t="inlineStr">
         <is>
           <t>SHA256:b30390d3a7b57b45944bf3d2</t>
         </is>
       </c>
-      <c r="D42" s="10" t="inlineStr">
+      <c r="D42" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 41: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E42" s="10" t="inlineStr">
+      <c r="E42" s="16" t="inlineStr">
         <is>
           <t>99.70%</t>
         </is>
       </c>
-      <c r="F42" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G42" s="10" t="inlineStr">
+      <c r="F42" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G42" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H42" s="10" t="inlineStr">
+      <c r="H42" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8041. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="10" t="inlineStr">
+      <c r="A43" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0042</t>
         </is>
       </c>
-      <c r="B43" s="10" t="inlineStr">
+      <c r="B43" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 42</t>
         </is>
       </c>
-      <c r="C43" s="10" t="inlineStr">
+      <c r="C43" s="16" t="inlineStr">
         <is>
           <t>SHA256:42c0373f453ff6008ab4c9c7</t>
         </is>
       </c>
-      <c r="D43" s="10" t="inlineStr">
+      <c r="D43" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 42: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E43" s="10" t="inlineStr">
+      <c r="E43" s="16" t="inlineStr">
         <is>
           <t>98.50%</t>
         </is>
       </c>
-      <c r="F43" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G43" s="10" t="inlineStr">
+      <c r="F43" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G43" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H43" s="10" t="inlineStr">
+      <c r="H43" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8042. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="10" t="inlineStr">
+      <c r="A44" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0043</t>
         </is>
       </c>
-      <c r="B44" s="10" t="inlineStr">
+      <c r="B44" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 43</t>
         </is>
       </c>
-      <c r="C44" s="10" t="inlineStr">
+      <c r="C44" s="16" t="inlineStr">
         <is>
           <t>SHA256:9ba27b44185ccf8c7bc2e62e</t>
         </is>
       </c>
-      <c r="D44" s="10" t="inlineStr">
+      <c r="D44" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 43: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E44" s="10" t="inlineStr">
+      <c r="E44" s="16" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F44" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G44" s="10" t="inlineStr">
+      <c r="F44" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G44" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H44" s="10" t="inlineStr">
+      <c r="H44" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8043. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="10" t="inlineStr">
+      <c r="A45" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0044</t>
         </is>
       </c>
-      <c r="B45" s="10" t="inlineStr">
+      <c r="B45" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 44</t>
         </is>
       </c>
-      <c r="C45" s="10" t="inlineStr">
+      <c r="C45" s="16" t="inlineStr">
         <is>
           <t>SHA256:fa4a0c64d6d684e7ec71f2ce</t>
         </is>
       </c>
-      <c r="D45" s="10" t="inlineStr">
+      <c r="D45" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 44: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E45" s="10" t="inlineStr">
+      <c r="E45" s="16" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F45" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G45" s="10" t="inlineStr">
+      <c r="F45" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G45" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H45" s="10" t="inlineStr">
+      <c r="H45" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8044. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="10" t="inlineStr">
+      <c r="A46" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0045</t>
         </is>
       </c>
-      <c r="B46" s="10" t="inlineStr">
+      <c r="B46" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 45</t>
         </is>
       </c>
-      <c r="C46" s="10" t="inlineStr">
+      <c r="C46" s="16" t="inlineStr">
         <is>
           <t>SHA256:34de87ac4cf7cc1c45790b56</t>
         </is>
       </c>
-      <c r="D46" s="10" t="inlineStr">
+      <c r="D46" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 45: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E46" s="10" t="inlineStr">
+      <c r="E46" s="16" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F46" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G46" s="10" t="inlineStr">
+      <c r="F46" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G46" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H46" s="10" t="inlineStr">
+      <c r="H46" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8045. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="10" t="inlineStr">
+      <c r="A47" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0046</t>
         </is>
       </c>
-      <c r="B47" s="10" t="inlineStr">
+      <c r="B47" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 46</t>
         </is>
       </c>
-      <c r="C47" s="10" t="inlineStr">
+      <c r="C47" s="16" t="inlineStr">
         <is>
           <t>SHA256:2c6de11cb2b1f85600e775ef</t>
         </is>
       </c>
-      <c r="D47" s="10" t="inlineStr">
+      <c r="D47" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 46: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E47" s="10" t="inlineStr">
+      <c r="E47" s="16" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F47" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G47" s="10" t="inlineStr">
+      <c r="F47" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G47" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H47" s="10" t="inlineStr">
+      <c r="H47" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8046. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="10" t="inlineStr">
+      <c r="A48" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0047</t>
         </is>
       </c>
-      <c r="B48" s="10" t="inlineStr">
+      <c r="B48" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 47</t>
         </is>
       </c>
-      <c r="C48" s="10" t="inlineStr">
+      <c r="C48" s="16" t="inlineStr">
         <is>
           <t>SHA256:afb87f845fb8106b27f40d85</t>
         </is>
       </c>
-      <c r="D48" s="10" t="inlineStr">
+      <c r="D48" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 47: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E48" s="10" t="inlineStr">
+      <c r="E48" s="16" t="inlineStr">
         <is>
           <t>99.50%</t>
         </is>
       </c>
-      <c r="F48" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G48" s="10" t="inlineStr">
+      <c r="F48" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G48" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H48" s="10" t="inlineStr">
+      <c r="H48" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8047. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="10" t="inlineStr">
+      <c r="A49" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0048</t>
         </is>
       </c>
-      <c r="B49" s="10" t="inlineStr">
+      <c r="B49" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 48</t>
         </is>
       </c>
-      <c r="C49" s="10" t="inlineStr">
+      <c r="C49" s="16" t="inlineStr">
         <is>
           <t>SHA256:54bf4426d65718b05ec3e6f7</t>
         </is>
       </c>
-      <c r="D49" s="10" t="inlineStr">
+      <c r="D49" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 48: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E49" s="10" t="inlineStr">
+      <c r="E49" s="16" t="inlineStr">
         <is>
           <t>99.70%</t>
         </is>
       </c>
-      <c r="F49" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G49" s="10" t="inlineStr">
+      <c r="F49" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G49" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H49" s="10" t="inlineStr">
+      <c r="H49" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8048. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="10" t="inlineStr">
+      <c r="A50" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0049</t>
         </is>
       </c>
-      <c r="B50" s="10" t="inlineStr">
+      <c r="B50" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 49</t>
         </is>
       </c>
-      <c r="C50" s="10" t="inlineStr">
+      <c r="C50" s="16" t="inlineStr">
         <is>
           <t>SHA256:1814a55984139e821d4da248</t>
         </is>
       </c>
-      <c r="D50" s="10" t="inlineStr">
+      <c r="D50" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 49: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E50" s="10" t="inlineStr">
+      <c r="E50" s="16" t="inlineStr">
         <is>
           <t>98.50%</t>
         </is>
       </c>
-      <c r="F50" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G50" s="10" t="inlineStr">
+      <c r="F50" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G50" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H50" s="10" t="inlineStr">
+      <c r="H50" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8049. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="10" t="inlineStr">
+      <c r="A51" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0050</t>
         </is>
       </c>
-      <c r="B51" s="10" t="inlineStr">
+      <c r="B51" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 50</t>
         </is>
       </c>
-      <c r="C51" s="10" t="inlineStr">
+      <c r="C51" s="16" t="inlineStr">
         <is>
           <t>SHA256:6b7a97f9c155d9a1a7e276c4</t>
         </is>
       </c>
-      <c r="D51" s="10" t="inlineStr">
+      <c r="D51" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 50: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E51" s="10" t="inlineStr">
+      <c r="E51" s="16" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F51" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G51" s="10" t="inlineStr">
+      <c r="F51" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G51" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H51" s="10" t="inlineStr">
+      <c r="H51" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8050. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="10" t="inlineStr">
+      <c r="A52" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0051</t>
         </is>
       </c>
-      <c r="B52" s="10" t="inlineStr">
+      <c r="B52" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 51</t>
         </is>
       </c>
-      <c r="C52" s="10" t="inlineStr">
+      <c r="C52" s="16" t="inlineStr">
         <is>
           <t>SHA256:e4a62d26937d669483d2f5a2</t>
         </is>
       </c>
-      <c r="D52" s="10" t="inlineStr">
+      <c r="D52" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 51: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E52" s="10" t="inlineStr">
+      <c r="E52" s="16" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F52" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G52" s="10" t="inlineStr">
+      <c r="F52" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G52" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H52" s="10" t="inlineStr">
+      <c r="H52" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8051. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="10" t="inlineStr">
+      <c r="A53" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0052</t>
         </is>
       </c>
-      <c r="B53" s="10" t="inlineStr">
+      <c r="B53" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 52</t>
         </is>
       </c>
-      <c r="C53" s="10" t="inlineStr">
+      <c r="C53" s="16" t="inlineStr">
         <is>
           <t>SHA256:a6daaa48f57ef03333db8c0c</t>
         </is>
       </c>
-      <c r="D53" s="10" t="inlineStr">
+      <c r="D53" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 52: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E53" s="10" t="inlineStr">
+      <c r="E53" s="16" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F53" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G53" s="10" t="inlineStr">
+      <c r="F53" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G53" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H53" s="10" t="inlineStr">
+      <c r="H53" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8052. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="10" t="inlineStr">
+      <c r="A54" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0053</t>
         </is>
       </c>
-      <c r="B54" s="10" t="inlineStr">
+      <c r="B54" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 53</t>
         </is>
       </c>
-      <c r="C54" s="10" t="inlineStr">
+      <c r="C54" s="16" t="inlineStr">
         <is>
           <t>SHA256:b035264c0969ca52b7067452</t>
         </is>
       </c>
-      <c r="D54" s="10" t="inlineStr">
+      <c r="D54" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 53: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E54" s="10" t="inlineStr">
+      <c r="E54" s="16" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F54" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G54" s="10" t="inlineStr">
+      <c r="F54" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G54" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H54" s="10" t="inlineStr">
+      <c r="H54" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8053. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="10" t="inlineStr">
+      <c r="A55" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0054</t>
         </is>
       </c>
-      <c r="B55" s="10" t="inlineStr">
+      <c r="B55" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 54</t>
         </is>
       </c>
-      <c r="C55" s="10" t="inlineStr">
+      <c r="C55" s="16" t="inlineStr">
         <is>
           <t>SHA256:9e557de7a0e0aa3265a85b89</t>
         </is>
       </c>
-      <c r="D55" s="10" t="inlineStr">
+      <c r="D55" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 54: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E55" s="10" t="inlineStr">
+      <c r="E55" s="16" t="inlineStr">
         <is>
           <t>99.50%</t>
         </is>
       </c>
-      <c r="F55" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G55" s="10" t="inlineStr">
+      <c r="F55" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G55" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H55" s="10" t="inlineStr">
+      <c r="H55" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8054. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="10" t="inlineStr">
+      <c r="A56" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0055</t>
         </is>
       </c>
-      <c r="B56" s="10" t="inlineStr">
+      <c r="B56" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 55</t>
         </is>
       </c>
-      <c r="C56" s="10" t="inlineStr">
+      <c r="C56" s="16" t="inlineStr">
         <is>
           <t>SHA256:ef506da4e2fc1fe5fa936b3e</t>
         </is>
       </c>
-      <c r="D56" s="10" t="inlineStr">
+      <c r="D56" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 55: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E56" s="10" t="inlineStr">
+      <c r="E56" s="16" t="inlineStr">
         <is>
           <t>99.70%</t>
         </is>
       </c>
-      <c r="F56" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G56" s="10" t="inlineStr">
+      <c r="F56" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G56" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H56" s="10" t="inlineStr">
+      <c r="H56" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8055. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="10" t="inlineStr">
+      <c r="A57" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0056</t>
         </is>
       </c>
-      <c r="B57" s="10" t="inlineStr">
+      <c r="B57" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 56</t>
         </is>
       </c>
-      <c r="C57" s="10" t="inlineStr">
+      <c r="C57" s="16" t="inlineStr">
         <is>
           <t>SHA256:c94d64b69777959e17909713</t>
         </is>
       </c>
-      <c r="D57" s="10" t="inlineStr">
+      <c r="D57" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 56: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E57" s="10" t="inlineStr">
+      <c r="E57" s="16" t="inlineStr">
         <is>
           <t>98.50%</t>
         </is>
       </c>
-      <c r="F57" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G57" s="10" t="inlineStr">
+      <c r="F57" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G57" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H57" s="10" t="inlineStr">
+      <c r="H57" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8056. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="10" t="inlineStr">
+      <c r="A58" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0057</t>
         </is>
       </c>
-      <c r="B58" s="10" t="inlineStr">
+      <c r="B58" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 57</t>
         </is>
       </c>
-      <c r="C58" s="10" t="inlineStr">
+      <c r="C58" s="16" t="inlineStr">
         <is>
           <t>SHA256:dc5150c0ff8ba0e186ebedfa</t>
         </is>
       </c>
-      <c r="D58" s="10" t="inlineStr">
+      <c r="D58" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 57: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E58" s="10" t="inlineStr">
+      <c r="E58" s="16" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F58" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G58" s="10" t="inlineStr">
+      <c r="F58" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G58" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H58" s="10" t="inlineStr">
+      <c r="H58" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8057. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="10" t="inlineStr">
+      <c r="A59" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0058</t>
         </is>
       </c>
-      <c r="B59" s="10" t="inlineStr">
+      <c r="B59" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 58</t>
         </is>
       </c>
-      <c r="C59" s="10" t="inlineStr">
+      <c r="C59" s="16" t="inlineStr">
         <is>
           <t>SHA256:3a96b6567e35f513b9eac0f0</t>
         </is>
       </c>
-      <c r="D59" s="10" t="inlineStr">
+      <c r="D59" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 58: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E59" s="10" t="inlineStr">
+      <c r="E59" s="16" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F59" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G59" s="10" t="inlineStr">
+      <c r="F59" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G59" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H59" s="10" t="inlineStr">
+      <c r="H59" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8058. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="10" t="inlineStr">
+      <c r="A60" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0059</t>
         </is>
       </c>
-      <c r="B60" s="10" t="inlineStr">
+      <c r="B60" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 59</t>
         </is>
       </c>
-      <c r="C60" s="10" t="inlineStr">
+      <c r="C60" s="16" t="inlineStr">
         <is>
           <t>SHA256:3ef1835e2980560cabe0c710</t>
         </is>
       </c>
-      <c r="D60" s="10" t="inlineStr">
+      <c r="D60" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 59: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E60" s="10" t="inlineStr">
+      <c r="E60" s="16" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F60" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G60" s="10" t="inlineStr">
+      <c r="F60" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G60" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H60" s="10" t="inlineStr">
+      <c r="H60" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8059. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="10" t="inlineStr">
+      <c r="A61" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0060</t>
         </is>
       </c>
-      <c r="B61" s="10" t="inlineStr">
+      <c r="B61" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 60</t>
         </is>
       </c>
-      <c r="C61" s="10" t="inlineStr">
+      <c r="C61" s="16" t="inlineStr">
         <is>
           <t>SHA256:e79f177608559c8a0b37e39e</t>
         </is>
       </c>
-      <c r="D61" s="10" t="inlineStr">
+      <c r="D61" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 60: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E61" s="10" t="inlineStr">
+      <c r="E61" s="16" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F61" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G61" s="10" t="inlineStr">
+      <c r="F61" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G61" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H61" s="10" t="inlineStr">
+      <c r="H61" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8060. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="10" t="inlineStr">
+      <c r="A62" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0061</t>
         </is>
       </c>
-      <c r="B62" s="10" t="inlineStr">
+      <c r="B62" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 61</t>
         </is>
       </c>
-      <c r="C62" s="10" t="inlineStr">
+      <c r="C62" s="16" t="inlineStr">
         <is>
           <t>SHA256:efd9ff5d58520e27e1b1a258</t>
         </is>
       </c>
-      <c r="D62" s="10" t="inlineStr">
+      <c r="D62" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 61: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E62" s="10" t="inlineStr">
+      <c r="E62" s="16" t="inlineStr">
         <is>
           <t>99.50%</t>
         </is>
       </c>
-      <c r="F62" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G62" s="10" t="inlineStr">
+      <c r="F62" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G62" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H62" s="10" t="inlineStr">
+      <c r="H62" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8061. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="10" t="inlineStr">
+      <c r="A63" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0062</t>
         </is>
       </c>
-      <c r="B63" s="10" t="inlineStr">
+      <c r="B63" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 62</t>
         </is>
       </c>
-      <c r="C63" s="10" t="inlineStr">
+      <c r="C63" s="16" t="inlineStr">
         <is>
           <t>SHA256:e802d80dd861e9a22d88e262</t>
         </is>
       </c>
-      <c r="D63" s="10" t="inlineStr">
+      <c r="D63" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 62: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E63" s="10" t="inlineStr">
+      <c r="E63" s="16" t="inlineStr">
         <is>
           <t>99.70%</t>
         </is>
       </c>
-      <c r="F63" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G63" s="10" t="inlineStr">
+      <c r="F63" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G63" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H63" s="10" t="inlineStr">
+      <c r="H63" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8062. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="10" t="inlineStr">
+      <c r="A64" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0063</t>
         </is>
       </c>
-      <c r="B64" s="10" t="inlineStr">
+      <c r="B64" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 63</t>
         </is>
       </c>
-      <c r="C64" s="10" t="inlineStr">
+      <c r="C64" s="16" t="inlineStr">
         <is>
           <t>SHA256:b63c95e1fee671e0352e3649</t>
         </is>
       </c>
-      <c r="D64" s="10" t="inlineStr">
+      <c r="D64" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 63: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E64" s="10" t="inlineStr">
+      <c r="E64" s="16" t="inlineStr">
         <is>
           <t>98.50%</t>
         </is>
       </c>
-      <c r="F64" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G64" s="10" t="inlineStr">
+      <c r="F64" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G64" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H64" s="10" t="inlineStr">
+      <c r="H64" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8063. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="10" t="inlineStr">
+      <c r="A65" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0064</t>
         </is>
       </c>
-      <c r="B65" s="10" t="inlineStr">
+      <c r="B65" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 64</t>
         </is>
       </c>
-      <c r="C65" s="10" t="inlineStr">
+      <c r="C65" s="16" t="inlineStr">
         <is>
           <t>SHA256:ec7553fe18cdaca4ed190eec</t>
         </is>
       </c>
-      <c r="D65" s="10" t="inlineStr">
+      <c r="D65" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 64: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E65" s="10" t="inlineStr">
+      <c r="E65" s="16" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F65" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G65" s="10" t="inlineStr">
+      <c r="F65" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G65" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H65" s="10" t="inlineStr">
+      <c r="H65" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8064. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="10" t="inlineStr">
+      <c r="A66" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0065</t>
         </is>
       </c>
-      <c r="B66" s="10" t="inlineStr">
+      <c r="B66" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 65</t>
         </is>
       </c>
-      <c r="C66" s="10" t="inlineStr">
+      <c r="C66" s="16" t="inlineStr">
         <is>
           <t>SHA256:e030e51d6f457343bf17bd7d</t>
         </is>
       </c>
-      <c r="D66" s="10" t="inlineStr">
+      <c r="D66" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 65: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E66" s="10" t="inlineStr">
+      <c r="E66" s="16" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F66" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G66" s="10" t="inlineStr">
+      <c r="F66" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G66" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H66" s="10" t="inlineStr">
+      <c r="H66" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8065. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="10" t="inlineStr">
+      <c r="A67" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0066</t>
         </is>
       </c>
-      <c r="B67" s="10" t="inlineStr">
+      <c r="B67" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 66</t>
         </is>
       </c>
-      <c r="C67" s="10" t="inlineStr">
+      <c r="C67" s="16" t="inlineStr">
         <is>
           <t>SHA256:336b6beb3c4729df275a02ad</t>
         </is>
       </c>
-      <c r="D67" s="10" t="inlineStr">
+      <c r="D67" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 66: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E67" s="10" t="inlineStr">
+      <c r="E67" s="16" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F67" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G67" s="10" t="inlineStr">
+      <c r="F67" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G67" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H67" s="10" t="inlineStr">
+      <c r="H67" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8066. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="10" t="inlineStr">
+      <c r="A68" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0067</t>
         </is>
       </c>
-      <c r="B68" s="10" t="inlineStr">
+      <c r="B68" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 67</t>
         </is>
       </c>
-      <c r="C68" s="10" t="inlineStr">
+      <c r="C68" s="16" t="inlineStr">
         <is>
           <t>SHA256:68f27a72434009f9899eee16</t>
         </is>
       </c>
-      <c r="D68" s="10" t="inlineStr">
+      <c r="D68" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 67: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E68" s="10" t="inlineStr">
+      <c r="E68" s="16" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F68" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G68" s="10" t="inlineStr">
+      <c r="F68" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G68" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H68" s="10" t="inlineStr">
+      <c r="H68" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8067. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="10" t="inlineStr">
+      <c r="A69" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0068</t>
         </is>
       </c>
-      <c r="B69" s="10" t="inlineStr">
+      <c r="B69" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 68</t>
         </is>
       </c>
-      <c r="C69" s="10" t="inlineStr">
+      <c r="C69" s="16" t="inlineStr">
         <is>
           <t>SHA256:38b39acd3719847618b1b522</t>
         </is>
       </c>
-      <c r="D69" s="10" t="inlineStr">
+      <c r="D69" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 68: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E69" s="10" t="inlineStr">
+      <c r="E69" s="16" t="inlineStr">
         <is>
           <t>99.50%</t>
         </is>
       </c>
-      <c r="F69" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G69" s="10" t="inlineStr">
+      <c r="F69" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G69" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H69" s="10" t="inlineStr">
+      <c r="H69" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8068. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="10" t="inlineStr">
+      <c r="A70" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0069</t>
         </is>
       </c>
-      <c r="B70" s="10" t="inlineStr">
+      <c r="B70" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 69</t>
         </is>
       </c>
-      <c r="C70" s="10" t="inlineStr">
+      <c r="C70" s="16" t="inlineStr">
         <is>
           <t>SHA256:d10ea4a37c15ac3981a6c2d2</t>
         </is>
       </c>
-      <c r="D70" s="10" t="inlineStr">
+      <c r="D70" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 69: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E70" s="10" t="inlineStr">
+      <c r="E70" s="16" t="inlineStr">
         <is>
           <t>99.70%</t>
         </is>
       </c>
-      <c r="F70" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G70" s="10" t="inlineStr">
+      <c r="F70" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G70" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H70" s="10" t="inlineStr">
+      <c r="H70" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8069. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="10" t="inlineStr">
+      <c r="A71" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0070</t>
         </is>
       </c>
-      <c r="B71" s="10" t="inlineStr">
+      <c r="B71" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 70</t>
         </is>
       </c>
-      <c r="C71" s="10" t="inlineStr">
+      <c r="C71" s="16" t="inlineStr">
         <is>
           <t>SHA256:974fca76ad2497eb0ac737e7</t>
         </is>
       </c>
-      <c r="D71" s="10" t="inlineStr">
+      <c r="D71" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 70: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E71" s="10" t="inlineStr">
+      <c r="E71" s="16" t="inlineStr">
         <is>
           <t>98.50%</t>
         </is>
       </c>
-      <c r="F71" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G71" s="10" t="inlineStr">
+      <c r="F71" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G71" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H71" s="10" t="inlineStr">
+      <c r="H71" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8070. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="10" t="inlineStr">
+      <c r="A72" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0071</t>
         </is>
       </c>
-      <c r="B72" s="10" t="inlineStr">
+      <c r="B72" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 71</t>
         </is>
       </c>
-      <c r="C72" s="10" t="inlineStr">
+      <c r="C72" s="16" t="inlineStr">
         <is>
           <t>SHA256:87c6348615379f068285f294</t>
         </is>
       </c>
-      <c r="D72" s="10" t="inlineStr">
+      <c r="D72" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 71: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E72" s="10" t="inlineStr">
+      <c r="E72" s="16" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F72" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G72" s="10" t="inlineStr">
+      <c r="F72" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G72" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H72" s="10" t="inlineStr">
+      <c r="H72" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8071. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="10" t="inlineStr">
+      <c r="A73" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0072</t>
         </is>
       </c>
-      <c r="B73" s="10" t="inlineStr">
+      <c r="B73" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 72</t>
         </is>
       </c>
-      <c r="C73" s="10" t="inlineStr">
+      <c r="C73" s="16" t="inlineStr">
         <is>
           <t>SHA256:2ad220854c544cf2e52aae6c</t>
         </is>
       </c>
-      <c r="D73" s="10" t="inlineStr">
+      <c r="D73" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 72: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E73" s="10" t="inlineStr">
+      <c r="E73" s="16" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F73" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G73" s="10" t="inlineStr">
+      <c r="F73" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G73" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H73" s="10" t="inlineStr">
+      <c r="H73" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8072. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="10" t="inlineStr">
+      <c r="A74" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0073</t>
         </is>
       </c>
-      <c r="B74" s="10" t="inlineStr">
+      <c r="B74" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 73</t>
         </is>
       </c>
-      <c r="C74" s="10" t="inlineStr">
+      <c r="C74" s="16" t="inlineStr">
         <is>
           <t>SHA256:1402cd477181ec62d83690c3</t>
         </is>
       </c>
-      <c r="D74" s="10" t="inlineStr">
+      <c r="D74" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 73: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E74" s="10" t="inlineStr">
+      <c r="E74" s="16" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F74" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G74" s="10" t="inlineStr">
+      <c r="F74" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G74" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H74" s="10" t="inlineStr">
+      <c r="H74" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8073. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="10" t="inlineStr">
+      <c r="A75" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0074</t>
         </is>
       </c>
-      <c r="B75" s="10" t="inlineStr">
+      <c r="B75" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 74</t>
         </is>
       </c>
-      <c r="C75" s="10" t="inlineStr">
+      <c r="C75" s="16" t="inlineStr">
         <is>
           <t>SHA256:ef98780ef029a2b6eca08d8a</t>
         </is>
       </c>
-      <c r="D75" s="10" t="inlineStr">
+      <c r="D75" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 74: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E75" s="10" t="inlineStr">
+      <c r="E75" s="16" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F75" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G75" s="10" t="inlineStr">
+      <c r="F75" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G75" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H75" s="10" t="inlineStr">
+      <c r="H75" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8074. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="10" t="inlineStr">
+      <c r="A76" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0075</t>
         </is>
       </c>
-      <c r="B76" s="10" t="inlineStr">
+      <c r="B76" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 75</t>
         </is>
       </c>
-      <c r="C76" s="10" t="inlineStr">
+      <c r="C76" s="16" t="inlineStr">
         <is>
           <t>SHA256:7b241d1ef7eacade2bfa74cd</t>
         </is>
       </c>
-      <c r="D76" s="10" t="inlineStr">
+      <c r="D76" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 75: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E76" s="10" t="inlineStr">
+      <c r="E76" s="16" t="inlineStr">
         <is>
           <t>99.50%</t>
         </is>
       </c>
-      <c r="F76" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G76" s="10" t="inlineStr">
+      <c r="F76" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G76" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H76" s="10" t="inlineStr">
+      <c r="H76" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8075. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="10" t="inlineStr">
+      <c r="A77" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0076</t>
         </is>
       </c>
-      <c r="B77" s="10" t="inlineStr">
+      <c r="B77" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 76</t>
         </is>
       </c>
-      <c r="C77" s="10" t="inlineStr">
+      <c r="C77" s="16" t="inlineStr">
         <is>
           <t>SHA256:387c8fa1ed8b1d94be7d1c1f</t>
         </is>
       </c>
-      <c r="D77" s="10" t="inlineStr">
+      <c r="D77" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 76: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E77" s="10" t="inlineStr">
+      <c r="E77" s="16" t="inlineStr">
         <is>
           <t>99.70%</t>
         </is>
       </c>
-      <c r="F77" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G77" s="10" t="inlineStr">
+      <c r="F77" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G77" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H77" s="10" t="inlineStr">
+      <c r="H77" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8076. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="10" t="inlineStr">
+      <c r="A78" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0077</t>
         </is>
       </c>
-      <c r="B78" s="10" t="inlineStr">
+      <c r="B78" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 77</t>
         </is>
       </c>
-      <c r="C78" s="10" t="inlineStr">
+      <c r="C78" s="16" t="inlineStr">
         <is>
           <t>SHA256:3bf65552d6e42ce8517042cb</t>
         </is>
       </c>
-      <c r="D78" s="10" t="inlineStr">
+      <c r="D78" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 77: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E78" s="10" t="inlineStr">
+      <c r="E78" s="16" t="inlineStr">
         <is>
           <t>98.50%</t>
         </is>
       </c>
-      <c r="F78" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G78" s="10" t="inlineStr">
+      <c r="F78" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G78" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H78" s="10" t="inlineStr">
+      <c r="H78" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8077. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="10" t="inlineStr">
+      <c r="A79" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0078</t>
         </is>
       </c>
-      <c r="B79" s="10" t="inlineStr">
+      <c r="B79" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 78</t>
         </is>
       </c>
-      <c r="C79" s="10" t="inlineStr">
+      <c r="C79" s="16" t="inlineStr">
         <is>
           <t>SHA256:557aded252c2f1592151b24a</t>
         </is>
       </c>
-      <c r="D79" s="10" t="inlineStr">
+      <c r="D79" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 78: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E79" s="10" t="inlineStr">
+      <c r="E79" s="16" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F79" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G79" s="10" t="inlineStr">
+      <c r="F79" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G79" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H79" s="10" t="inlineStr">
+      <c r="H79" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8078. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="10" t="inlineStr">
+      <c r="A80" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0079</t>
         </is>
       </c>
-      <c r="B80" s="10" t="inlineStr">
+      <c r="B80" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 79</t>
         </is>
       </c>
-      <c r="C80" s="10" t="inlineStr">
+      <c r="C80" s="16" t="inlineStr">
         <is>
           <t>SHA256:65aa26279b028549523e1ae2</t>
         </is>
       </c>
-      <c r="D80" s="10" t="inlineStr">
+      <c r="D80" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 79: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E80" s="10" t="inlineStr">
+      <c r="E80" s="16" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F80" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G80" s="10" t="inlineStr">
+      <c r="F80" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G80" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H80" s="10" t="inlineStr">
+      <c r="H80" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8079. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="10" t="inlineStr">
+      <c r="A81" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0080</t>
         </is>
       </c>
-      <c r="B81" s="10" t="inlineStr">
+      <c r="B81" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 80</t>
         </is>
       </c>
-      <c r="C81" s="10" t="inlineStr">
+      <c r="C81" s="16" t="inlineStr">
         <is>
           <t>SHA256:70698ee7582e46ccb8e0ff39</t>
         </is>
       </c>
-      <c r="D81" s="10" t="inlineStr">
+      <c r="D81" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 80: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E81" s="10" t="inlineStr">
+      <c r="E81" s="16" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F81" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G81" s="10" t="inlineStr">
+      <c r="F81" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G81" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H81" s="10" t="inlineStr">
+      <c r="H81" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8080. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="10" t="inlineStr">
+      <c r="A82" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0081</t>
         </is>
       </c>
-      <c r="B82" s="10" t="inlineStr">
+      <c r="B82" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 81</t>
         </is>
       </c>
-      <c r="C82" s="10" t="inlineStr">
+      <c r="C82" s="16" t="inlineStr">
         <is>
           <t>SHA256:3f9371b765f3e32de2563767</t>
         </is>
       </c>
-      <c r="D82" s="10" t="inlineStr">
+      <c r="D82" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 81: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E82" s="10" t="inlineStr">
+      <c r="E82" s="16" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F82" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G82" s="10" t="inlineStr">
+      <c r="F82" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G82" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H82" s="10" t="inlineStr">
+      <c r="H82" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8081. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="10" t="inlineStr">
+      <c r="A83" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0082</t>
         </is>
       </c>
-      <c r="B83" s="10" t="inlineStr">
+      <c r="B83" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 82</t>
         </is>
       </c>
-      <c r="C83" s="10" t="inlineStr">
+      <c r="C83" s="16" t="inlineStr">
         <is>
           <t>SHA256:9c04ef7d13f09f9627530723</t>
         </is>
       </c>
-      <c r="D83" s="10" t="inlineStr">
+      <c r="D83" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 82: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E83" s="10" t="inlineStr">
+      <c r="E83" s="16" t="inlineStr">
         <is>
           <t>99.50%</t>
         </is>
       </c>
-      <c r="F83" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G83" s="10" t="inlineStr">
+      <c r="F83" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G83" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H83" s="10" t="inlineStr">
+      <c r="H83" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8082. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="10" t="inlineStr">
+      <c r="A84" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0083</t>
         </is>
       </c>
-      <c r="B84" s="10" t="inlineStr">
+      <c r="B84" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 83</t>
         </is>
       </c>
-      <c r="C84" s="10" t="inlineStr">
+      <c r="C84" s="16" t="inlineStr">
         <is>
           <t>SHA256:0a49bf67279691af46db4417</t>
         </is>
       </c>
-      <c r="D84" s="10" t="inlineStr">
+      <c r="D84" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 83: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E84" s="10" t="inlineStr">
+      <c r="E84" s="16" t="inlineStr">
         <is>
           <t>99.70%</t>
         </is>
       </c>
-      <c r="F84" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G84" s="10" t="inlineStr">
+      <c r="F84" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G84" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H84" s="10" t="inlineStr">
+      <c r="H84" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8083. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="10" t="inlineStr">
+      <c r="A85" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0084</t>
         </is>
       </c>
-      <c r="B85" s="10" t="inlineStr">
+      <c r="B85" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 84</t>
         </is>
       </c>
-      <c r="C85" s="10" t="inlineStr">
+      <c r="C85" s="16" t="inlineStr">
         <is>
           <t>SHA256:600c3629e78c99952428f60d</t>
         </is>
       </c>
-      <c r="D85" s="10" t="inlineStr">
+      <c r="D85" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 84: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E85" s="10" t="inlineStr">
+      <c r="E85" s="16" t="inlineStr">
         <is>
           <t>98.50%</t>
         </is>
       </c>
-      <c r="F85" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G85" s="10" t="inlineStr">
+      <c r="F85" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G85" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H85" s="10" t="inlineStr">
+      <c r="H85" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8084. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="10" t="inlineStr">
+      <c r="A86" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0085</t>
         </is>
       </c>
-      <c r="B86" s="10" t="inlineStr">
+      <c r="B86" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 85</t>
         </is>
       </c>
-      <c r="C86" s="10" t="inlineStr">
+      <c r="C86" s="16" t="inlineStr">
         <is>
           <t>SHA256:6afca6c8edb9ab0371f1fc8c</t>
         </is>
       </c>
-      <c r="D86" s="10" t="inlineStr">
+      <c r="D86" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 85: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E86" s="10" t="inlineStr">
+      <c r="E86" s="16" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F86" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G86" s="10" t="inlineStr">
+      <c r="F86" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G86" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H86" s="10" t="inlineStr">
+      <c r="H86" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8085. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="10" t="inlineStr">
+      <c r="A87" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0086</t>
         </is>
       </c>
-      <c r="B87" s="10" t="inlineStr">
+      <c r="B87" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 86</t>
         </is>
       </c>
-      <c r="C87" s="10" t="inlineStr">
+      <c r="C87" s="16" t="inlineStr">
         <is>
           <t>SHA256:2b1ed2474ab3cc94fb0499d9</t>
         </is>
       </c>
-      <c r="D87" s="10" t="inlineStr">
+      <c r="D87" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 86: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E87" s="10" t="inlineStr">
+      <c r="E87" s="16" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F87" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G87" s="10" t="inlineStr">
+      <c r="F87" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G87" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H87" s="10" t="inlineStr">
+      <c r="H87" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8086. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="10" t="inlineStr">
+      <c r="A88" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0087</t>
         </is>
       </c>
-      <c r="B88" s="10" t="inlineStr">
+      <c r="B88" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 87</t>
         </is>
       </c>
-      <c r="C88" s="10" t="inlineStr">
+      <c r="C88" s="16" t="inlineStr">
         <is>
           <t>SHA256:b56a26de3aff6caa9add2e4b</t>
         </is>
       </c>
-      <c r="D88" s="10" t="inlineStr">
+      <c r="D88" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 87: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E88" s="10" t="inlineStr">
+      <c r="E88" s="16" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F88" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G88" s="10" t="inlineStr">
+      <c r="F88" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G88" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H88" s="10" t="inlineStr">
+      <c r="H88" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8087. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="10" t="inlineStr">
+      <c r="A89" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0088</t>
         </is>
       </c>
-      <c r="B89" s="10" t="inlineStr">
+      <c r="B89" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 88</t>
         </is>
       </c>
-      <c r="C89" s="10" t="inlineStr">
+      <c r="C89" s="16" t="inlineStr">
         <is>
           <t>SHA256:78ecc71f38d5cbf4603c9b85</t>
         </is>
       </c>
-      <c r="D89" s="10" t="inlineStr">
+      <c r="D89" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 88: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E89" s="10" t="inlineStr">
+      <c r="E89" s="16" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F89" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G89" s="10" t="inlineStr">
+      <c r="F89" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G89" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H89" s="10" t="inlineStr">
+      <c r="H89" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8088. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="10" t="inlineStr">
+      <c r="A90" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0089</t>
         </is>
       </c>
-      <c r="B90" s="10" t="inlineStr">
+      <c r="B90" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 89</t>
         </is>
       </c>
-      <c r="C90" s="10" t="inlineStr">
+      <c r="C90" s="16" t="inlineStr">
         <is>
           <t>SHA256:39f506cd8b8306723f5c7efa</t>
         </is>
       </c>
-      <c r="D90" s="10" t="inlineStr">
+      <c r="D90" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 89: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E90" s="10" t="inlineStr">
+      <c r="E90" s="16" t="inlineStr">
         <is>
           <t>99.50%</t>
         </is>
       </c>
-      <c r="F90" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G90" s="10" t="inlineStr">
+      <c r="F90" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G90" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H90" s="10" t="inlineStr">
+      <c r="H90" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8089. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="10" t="inlineStr">
+      <c r="A91" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0090</t>
         </is>
       </c>
-      <c r="B91" s="10" t="inlineStr">
+      <c r="B91" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 90</t>
         </is>
       </c>
-      <c r="C91" s="10" t="inlineStr">
+      <c r="C91" s="16" t="inlineStr">
         <is>
           <t>SHA256:90d74244e2dbb211abaa5a80</t>
         </is>
       </c>
-      <c r="D91" s="10" t="inlineStr">
+      <c r="D91" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 90: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E91" s="10" t="inlineStr">
+      <c r="E91" s="16" t="inlineStr">
         <is>
           <t>99.70%</t>
         </is>
       </c>
-      <c r="F91" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G91" s="10" t="inlineStr">
+      <c r="F91" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G91" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H91" s="10" t="inlineStr">
+      <c r="H91" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8090. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="10" t="inlineStr">
+      <c r="A92" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0091</t>
         </is>
       </c>
-      <c r="B92" s="10" t="inlineStr">
+      <c r="B92" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 91</t>
         </is>
       </c>
-      <c r="C92" s="10" t="inlineStr">
+      <c r="C92" s="16" t="inlineStr">
         <is>
           <t>SHA256:978035b1ebe8f6b5d8bacdaa</t>
         </is>
       </c>
-      <c r="D92" s="10" t="inlineStr">
+      <c r="D92" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 91: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E92" s="10" t="inlineStr">
+      <c r="E92" s="16" t="inlineStr">
         <is>
           <t>98.50%</t>
         </is>
       </c>
-      <c r="F92" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G92" s="10" t="inlineStr">
+      <c r="F92" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G92" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H92" s="10" t="inlineStr">
+      <c r="H92" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8091. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="10" t="inlineStr">
+      <c r="A93" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0092</t>
         </is>
       </c>
-      <c r="B93" s="10" t="inlineStr">
+      <c r="B93" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 92</t>
         </is>
       </c>
-      <c r="C93" s="10" t="inlineStr">
+      <c r="C93" s="16" t="inlineStr">
         <is>
           <t>SHA256:229fe7bf6be5d597207328e9</t>
         </is>
       </c>
-      <c r="D93" s="10" t="inlineStr">
+      <c r="D93" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 92: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E93" s="10" t="inlineStr">
+      <c r="E93" s="16" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F93" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G93" s="10" t="inlineStr">
+      <c r="F93" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G93" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H93" s="10" t="inlineStr">
+      <c r="H93" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8092. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="10" t="inlineStr">
+      <c r="A94" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0093</t>
         </is>
       </c>
-      <c r="B94" s="10" t="inlineStr">
+      <c r="B94" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 93</t>
         </is>
       </c>
-      <c r="C94" s="10" t="inlineStr">
+      <c r="C94" s="16" t="inlineStr">
         <is>
           <t>SHA256:405b1640ad2a65e49e23b1af</t>
         </is>
       </c>
-      <c r="D94" s="10" t="inlineStr">
+      <c r="D94" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 93: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E94" s="10" t="inlineStr">
+      <c r="E94" s="16" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F94" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G94" s="10" t="inlineStr">
+      <c r="F94" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G94" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H94" s="10" t="inlineStr">
+      <c r="H94" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8093. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="10" t="inlineStr">
+      <c r="A95" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0094</t>
         </is>
       </c>
-      <c r="B95" s="10" t="inlineStr">
+      <c r="B95" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 94</t>
         </is>
       </c>
-      <c r="C95" s="10" t="inlineStr">
+      <c r="C95" s="16" t="inlineStr">
         <is>
           <t>SHA256:947d44a9532565742f81f131</t>
         </is>
       </c>
-      <c r="D95" s="10" t="inlineStr">
+      <c r="D95" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 94: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E95" s="10" t="inlineStr">
+      <c r="E95" s="16" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F95" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G95" s="10" t="inlineStr">
+      <c r="F95" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G95" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H95" s="10" t="inlineStr">
+      <c r="H95" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8094. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="10" t="inlineStr">
+      <c r="A96" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0095</t>
         </is>
       </c>
-      <c r="B96" s="10" t="inlineStr">
+      <c r="B96" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 95</t>
         </is>
       </c>
-      <c r="C96" s="10" t="inlineStr">
+      <c r="C96" s="16" t="inlineStr">
         <is>
           <t>SHA256:d83f3c6746d24d1068dd97da</t>
         </is>
       </c>
-      <c r="D96" s="10" t="inlineStr">
+      <c r="D96" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 95: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E96" s="10" t="inlineStr">
+      <c r="E96" s="16" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F96" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G96" s="10" t="inlineStr">
+      <c r="F96" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G96" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H96" s="10" t="inlineStr">
+      <c r="H96" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8095. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="10" t="inlineStr">
+      <c r="A97" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0096</t>
         </is>
       </c>
-      <c r="B97" s="10" t="inlineStr">
+      <c r="B97" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 96</t>
         </is>
       </c>
-      <c r="C97" s="10" t="inlineStr">
+      <c r="C97" s="16" t="inlineStr">
         <is>
           <t>SHA256:9c0a86e20c731702aa678d10</t>
         </is>
       </c>
-      <c r="D97" s="10" t="inlineStr">
+      <c r="D97" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 96: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E97" s="10" t="inlineStr">
+      <c r="E97" s="16" t="inlineStr">
         <is>
           <t>99.50%</t>
         </is>
       </c>
-      <c r="F97" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G97" s="10" t="inlineStr">
+      <c r="F97" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G97" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H97" s="10" t="inlineStr">
+      <c r="H97" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8096. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="10" t="inlineStr">
+      <c r="A98" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0097</t>
         </is>
       </c>
-      <c r="B98" s="10" t="inlineStr">
+      <c r="B98" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 97</t>
         </is>
       </c>
-      <c r="C98" s="10" t="inlineStr">
+      <c r="C98" s="16" t="inlineStr">
         <is>
           <t>SHA256:97d1e4a8a810e74c6b999924</t>
         </is>
       </c>
-      <c r="D98" s="10" t="inlineStr">
+      <c r="D98" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 97: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E98" s="10" t="inlineStr">
+      <c r="E98" s="16" t="inlineStr">
         <is>
           <t>99.70%</t>
         </is>
       </c>
-      <c r="F98" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G98" s="10" t="inlineStr">
+      <c r="F98" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G98" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H98" s="10" t="inlineStr">
+      <c r="H98" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8097. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="10" t="inlineStr">
+      <c r="A99" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0098</t>
         </is>
       </c>
-      <c r="B99" s="10" t="inlineStr">
+      <c r="B99" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 98</t>
         </is>
       </c>
-      <c r="C99" s="10" t="inlineStr">
+      <c r="C99" s="16" t="inlineStr">
         <is>
           <t>SHA256:88d5f03160b5bde79caa5abb</t>
         </is>
       </c>
-      <c r="D99" s="10" t="inlineStr">
+      <c r="D99" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 98: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E99" s="10" t="inlineStr">
+      <c r="E99" s="16" t="inlineStr">
         <is>
           <t>98.50%</t>
         </is>
       </c>
-      <c r="F99" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G99" s="10" t="inlineStr">
+      <c r="F99" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G99" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H99" s="10" t="inlineStr">
+      <c r="H99" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8098. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="10" t="inlineStr">
+      <c r="A100" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0099</t>
         </is>
       </c>
-      <c r="B100" s="10" t="inlineStr">
+      <c r="B100" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 99</t>
         </is>
       </c>
-      <c r="C100" s="10" t="inlineStr">
+      <c r="C100" s="16" t="inlineStr">
         <is>
           <t>SHA256:847bee816ef2aea2635e8ddb</t>
         </is>
       </c>
-      <c r="D100" s="10" t="inlineStr">
+      <c r="D100" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 99: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E100" s="10" t="inlineStr">
+      <c r="E100" s="16" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F100" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G100" s="10" t="inlineStr">
+      <c r="F100" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G100" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H100" s="10" t="inlineStr">
+      <c r="H100" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8099. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="10" t="inlineStr">
+      <c r="A101" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0100</t>
         </is>
       </c>
-      <c r="B101" s="10" t="inlineStr">
+      <c r="B101" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 100</t>
         </is>
       </c>
-      <c r="C101" s="10" t="inlineStr">
+      <c r="C101" s="16" t="inlineStr">
         <is>
           <t>SHA256:fd5e68e24d9778c09f1c2f68</t>
         </is>
       </c>
-      <c r="D101" s="10" t="inlineStr">
+      <c r="D101" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 100: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E101" s="10" t="inlineStr">
+      <c r="E101" s="16" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F101" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G101" s="10" t="inlineStr">
+      <c r="F101" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G101" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H101" s="10" t="inlineStr">
+      <c r="H101" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8100. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="10" t="inlineStr">
+      <c r="A102" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0101</t>
         </is>
       </c>
-      <c r="B102" s="10" t="inlineStr">
+      <c r="B102" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 101</t>
         </is>
       </c>
-      <c r="C102" s="10" t="inlineStr">
+      <c r="C102" s="16" t="inlineStr">
         <is>
           <t>SHA256:3f04b964db16ec94b137b7d1</t>
         </is>
       </c>
-      <c r="D102" s="10" t="inlineStr">
+      <c r="D102" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 101: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E102" s="10" t="inlineStr">
+      <c r="E102" s="16" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F102" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G102" s="10" t="inlineStr">
+      <c r="F102" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G102" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H102" s="10" t="inlineStr">
+      <c r="H102" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8101. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="10" t="inlineStr">
+      <c r="A103" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0102</t>
         </is>
       </c>
-      <c r="B103" s="10" t="inlineStr">
+      <c r="B103" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 102</t>
         </is>
       </c>
-      <c r="C103" s="10" t="inlineStr">
+      <c r="C103" s="16" t="inlineStr">
         <is>
           <t>SHA256:1b2394a0fcc32fec0de5e0d7</t>
         </is>
       </c>
-      <c r="D103" s="10" t="inlineStr">
+      <c r="D103" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 102: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E103" s="10" t="inlineStr">
+      <c r="E103" s="16" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F103" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G103" s="10" t="inlineStr">
+      <c r="F103" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G103" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H103" s="10" t="inlineStr">
+      <c r="H103" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8102. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="10" t="inlineStr">
+      <c r="A104" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0103</t>
         </is>
       </c>
-      <c r="B104" s="10" t="inlineStr">
+      <c r="B104" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 103</t>
         </is>
       </c>
-      <c r="C104" s="10" t="inlineStr">
+      <c r="C104" s="16" t="inlineStr">
         <is>
           <t>SHA256:433889c0195170adb5610172</t>
         </is>
       </c>
-      <c r="D104" s="10" t="inlineStr">
+      <c r="D104" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 103: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E104" s="10" t="inlineStr">
+      <c r="E104" s="16" t="inlineStr">
         <is>
           <t>99.50%</t>
         </is>
       </c>
-      <c r="F104" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G104" s="10" t="inlineStr">
+      <c r="F104" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G104" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H104" s="10" t="inlineStr">
+      <c r="H104" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8103. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="10" t="inlineStr">
+      <c r="A105" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0104</t>
         </is>
       </c>
-      <c r="B105" s="10" t="inlineStr">
+      <c r="B105" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 104</t>
         </is>
       </c>
-      <c r="C105" s="10" t="inlineStr">
+      <c r="C105" s="16" t="inlineStr">
         <is>
           <t>SHA256:4be116f892d488ca24d0b284</t>
         </is>
       </c>
-      <c r="D105" s="10" t="inlineStr">
+      <c r="D105" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 104: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E105" s="10" t="inlineStr">
+      <c r="E105" s="16" t="inlineStr">
         <is>
           <t>99.70%</t>
         </is>
       </c>
-      <c r="F105" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G105" s="10" t="inlineStr">
+      <c r="F105" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G105" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H105" s="10" t="inlineStr">
+      <c r="H105" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8104. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="10" t="inlineStr">
+      <c r="A106" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0105</t>
         </is>
       </c>
-      <c r="B106" s="10" t="inlineStr">
+      <c r="B106" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 105</t>
         </is>
       </c>
-      <c r="C106" s="10" t="inlineStr">
+      <c r="C106" s="16" t="inlineStr">
         <is>
           <t>SHA256:63aa7d902a1f30170de1fff6</t>
         </is>
       </c>
-      <c r="D106" s="10" t="inlineStr">
+      <c r="D106" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 105: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E106" s="10" t="inlineStr">
+      <c r="E106" s="16" t="inlineStr">
         <is>
           <t>98.50%</t>
         </is>
       </c>
-      <c r="F106" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G106" s="10" t="inlineStr">
+      <c r="F106" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G106" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H106" s="10" t="inlineStr">
+      <c r="H106" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8105. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="10" t="inlineStr">
+      <c r="A107" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0106</t>
         </is>
       </c>
-      <c r="B107" s="10" t="inlineStr">
+      <c r="B107" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 106</t>
         </is>
       </c>
-      <c r="C107" s="10" t="inlineStr">
+      <c r="C107" s="16" t="inlineStr">
         <is>
           <t>SHA256:9caf5076047206ed36cd88ba</t>
         </is>
       </c>
-      <c r="D107" s="10" t="inlineStr">
+      <c r="D107" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 106: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E107" s="10" t="inlineStr">
+      <c r="E107" s="16" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F107" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G107" s="10" t="inlineStr">
+      <c r="F107" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G107" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H107" s="10" t="inlineStr">
+      <c r="H107" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8106. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="10" t="inlineStr">
+      <c r="A108" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0107</t>
         </is>
       </c>
-      <c r="B108" s="10" t="inlineStr">
+      <c r="B108" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 107</t>
         </is>
       </c>
-      <c r="C108" s="10" t="inlineStr">
+      <c r="C108" s="16" t="inlineStr">
         <is>
           <t>SHA256:6b40f434718c2ecc53024ab4</t>
         </is>
       </c>
-      <c r="D108" s="10" t="inlineStr">
+      <c r="D108" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 107: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E108" s="10" t="inlineStr">
+      <c r="E108" s="16" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F108" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G108" s="10" t="inlineStr">
+      <c r="F108" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G108" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H108" s="10" t="inlineStr">
+      <c r="H108" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8107. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="10" t="inlineStr">
+      <c r="A109" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0108</t>
         </is>
       </c>
-      <c r="B109" s="10" t="inlineStr">
+      <c r="B109" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 108</t>
         </is>
       </c>
-      <c r="C109" s="10" t="inlineStr">
+      <c r="C109" s="16" t="inlineStr">
         <is>
           <t>SHA256:222b80f8c58e9e60ff61529f</t>
         </is>
       </c>
-      <c r="D109" s="10" t="inlineStr">
+      <c r="D109" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 108: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E109" s="10" t="inlineStr">
+      <c r="E109" s="16" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F109" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G109" s="10" t="inlineStr">
+      <c r="F109" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G109" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H109" s="10" t="inlineStr">
+      <c r="H109" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8108. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="10" t="inlineStr">
+      <c r="A110" s="16" t="inlineStr">
         <is>
           <t>AUD-REC-0109</t>
         </is>
       </c>
-      <c r="B110" s="10" t="inlineStr">
+      <c r="B110" s="16" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 109</t>
         </is>
       </c>
-      <c r="C110" s="10" t="inlineStr">
+      <c r="C110" s="16" t="inlineStr">
         <is>
           <t>SHA256:2ff84def023f21145cd72f17</t>
         </is>
       </c>
-      <c r="D110" s="10" t="inlineStr">
+      <c r="D110" s="16" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 109: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E110" s="10" t="inlineStr">
+      <c r="E110" s="16" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F110" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G110" s="10" t="inlineStr">
+      <c r="F110" s="16" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G110" s="16" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H110" s="10" t="inlineStr">
+      <c r="H110" s="16" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8109. Calculation integrity verified without variance.</t>
         </is>
